--- a/artfynd/A 40826-2025 artfynd.xlsx
+++ b/artfynd/A 40826-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4114,6 +4114,4610 @@
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128085650</v>
+      </c>
+      <c r="B31" t="n">
+        <v>91822</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5467</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Kådvaxskinn</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Phlebia serialis</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Svarttjärnen S/V., Dls</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>316798</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6550432</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Bärljunbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128086988</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Svarttjärnen S/V., Dls</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>316819</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6550452</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Mosseljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128086910</v>
+      </c>
+      <c r="B33" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Svarttjärnen S/V., Dls</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>316813</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6550455</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Mosseljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128086622</v>
+      </c>
+      <c r="B34" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Svarttjärnen S/V., Dls</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>316857</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6550392</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Mosseljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128086358</v>
+      </c>
+      <c r="B35" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Svarttjärnen S/V., Dls</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>316837</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6550397</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Mosseljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128084900</v>
+      </c>
+      <c r="B36" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Ormetjärn V., Dls</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>317022</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6550471</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Bärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128087681</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Svarttjärnen S., Dls</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>316929</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6550454</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Mosseljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128085583</v>
+      </c>
+      <c r="B38" t="n">
+        <v>91822</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>5467</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Kådvaxskinn</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Phlebia serialis</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Svarttjärnen S/V., Dls</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>316856</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6550425</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Bärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128087374</v>
+      </c>
+      <c r="B39" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Svarttjärnen S/V., Dls</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>316861</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6550457</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Mosseljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128087074</v>
+      </c>
+      <c r="B40" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Svarttjärnen S/V., Dls</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>316863</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6550433</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Mosseljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128086155</v>
+      </c>
+      <c r="B41" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Svarttjärnen S/V., Dls</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>316836</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6550404</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Mosseljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128087033</v>
+      </c>
+      <c r="B42" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Svarttjärnen S/V., Dls</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>316848</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6550426</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Mosseljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128087641</v>
+      </c>
+      <c r="B43" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Svarttjärnen S/V., Dls</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>316887</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6550467</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Mosseljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128086546</v>
+      </c>
+      <c r="B44" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Svarttjärnen S/V., Dls</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>316848</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6550398</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Mosseljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128087244</v>
+      </c>
+      <c r="B45" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Svarttjärnen S/V., Dls</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>316867</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6550456</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Mosseljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128086710</v>
+      </c>
+      <c r="B46" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Svarttjärnen S/V., Dls</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>316825</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6550399</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Mosseljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128086451</v>
+      </c>
+      <c r="B47" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Svarttjärnen S/V., Dls</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>316834</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6550393</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Mosseljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128086825</v>
+      </c>
+      <c r="B48" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Svarttjärnen S/V., Dls</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>316809</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6550455</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Mosseljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>128086406</v>
+      </c>
+      <c r="B49" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Svarttjärnen S/V., Dls</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>316836</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6550393</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>Mosseljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128085493</v>
+      </c>
+      <c r="B50" t="n">
+        <v>91369</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Svarttjärnen S., Dls</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>316870</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6550378</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Bärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128084972</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79647</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Ormetjärn S/V., Dls</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>317017</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6550432</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>Bärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Stubbe # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128086997</v>
+      </c>
+      <c r="B52" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Svarttjärnen S/V., Dls</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>316832</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6550424</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Mosseljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128085763</v>
+      </c>
+      <c r="B53" t="n">
+        <v>91822</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>5467</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Kådvaxskinn</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Phlebia serialis</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Svarttjärnen S/V., Dls</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>316919</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6550474</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>Bärljunbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>128086772</v>
+      </c>
+      <c r="B54" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Svarttjärnen S/V., Dls</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>316809</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6550451</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>Mosseljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>128084916</v>
+      </c>
+      <c r="B55" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Ormetjärn S/V., Dls</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>317037</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6550398</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>Bärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>128085525</v>
+      </c>
+      <c r="B56" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Svarttjärnen S., Dls</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>316911</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6550369</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>Bärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Gadd # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>128084871</v>
+      </c>
+      <c r="B57" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Svarttjärnen O., Dls</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>316989</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6550551</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>Bärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Gadd # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>128086654</v>
+      </c>
+      <c r="B58" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Svarttjärnen S/V., Dls</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>316848</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6550409</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>Mosseljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>128086469</v>
+      </c>
+      <c r="B59" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Svarttjärnen S/V., Dls</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>316844</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6550394</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>Mosseljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>128086692</v>
+      </c>
+      <c r="B60" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Svarttjärnen S/V., Dls</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>316858</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6550418</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>Mosseljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>128087465</v>
+      </c>
+      <c r="B61" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Svarttjärnen S/V., Dls</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>316860</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6550480</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>Mosseljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>128085294</v>
+      </c>
+      <c r="B62" t="n">
+        <v>92832</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Ormetjärn S/V., Dls</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>317041</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6550370</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>Bärljungtallskog</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>128086718</v>
+      </c>
+      <c r="B63" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Svarttjärnen S/V., Dls</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>316821</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6550398</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>Mosseljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>128084637</v>
+      </c>
+      <c r="B64" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Svarttjärnen O., Dls</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>316984</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6550597</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>Bärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Gadd # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>128087606</v>
+      </c>
+      <c r="B65" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Svarttjärnen S/V., Dls</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>316877</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6550456</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>Mosseljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>128087506</v>
+      </c>
+      <c r="B66" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Svarttjärnen S/V., Dls</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>316865</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6550469</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>Mosseljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>128087411</v>
+      </c>
+      <c r="B67" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Svarttjärnen S/V., Dls</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>316858</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6550464</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>Mosseljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>128087295</v>
+      </c>
+      <c r="B68" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Svarttjärnen S/V., Dls</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>316868</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6550451</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>Mosseljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>128085956</v>
+      </c>
+      <c r="B69" t="n">
+        <v>97344</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Svarttjärnen S/V., Dls</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>316904</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6550464</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>Bärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>128086518</v>
+      </c>
+      <c r="B70" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Svarttjärnen S/V., Dls</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>316852</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6550388</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>Mosseljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40826-2025 artfynd.xlsx
+++ b/artfynd/A 40826-2025 artfynd.xlsx
@@ -4241,7 +4241,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128086988</v>
+        <v>128086622</v>
       </c>
       <c r="B32" t="n">
         <v>98467</v>
@@ -4284,10 +4284,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>316819</v>
+        <v>316857</v>
       </c>
       <c r="R32" t="n">
-        <v>6550452</v>
+        <v>6550392</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4352,7 +4352,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128086910</v>
+        <v>128086988</v>
       </c>
       <c r="B33" t="n">
         <v>98467</v>
@@ -4395,10 +4395,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>316813</v>
+        <v>316819</v>
       </c>
       <c r="R33" t="n">
-        <v>6550455</v>
+        <v>6550452</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4463,7 +4463,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128086622</v>
+        <v>128086910</v>
       </c>
       <c r="B34" t="n">
         <v>98467</v>
@@ -4506,10 +4506,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>316857</v>
+        <v>316813</v>
       </c>
       <c r="R34" t="n">
-        <v>6550392</v>
+        <v>6550455</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4574,53 +4574,54 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128086358</v>
+        <v>128084900</v>
       </c>
       <c r="B35" t="n">
-        <v>98467</v>
+        <v>8450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Svarttjärnen S/V., Dls</t>
+          <t>Ormetjärn V., Dls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>316837</v>
+        <v>317022</v>
       </c>
       <c r="R35" t="n">
-        <v>6550397</v>
+        <v>6550471</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4667,7 +4668,22 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Mosseljungbarrskog</t>
+          <t>Bärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4685,54 +4701,53 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128084900</v>
+        <v>128087681</v>
       </c>
       <c r="B36" t="n">
-        <v>8450</v>
+        <v>98467</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Ormetjärn V., Dls</t>
+          <t>Svarttjärnen S., Dls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>317022</v>
+        <v>316929</v>
       </c>
       <c r="R36" t="n">
-        <v>6550471</v>
+        <v>6550454</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4779,22 +4794,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Mosseljungbarrskog</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4812,7 +4812,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128087681</v>
+        <v>128086358</v>
       </c>
       <c r="B37" t="n">
         <v>98467</v>
@@ -4851,14 +4851,14 @@
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Svarttjärnen S., Dls</t>
+          <t>Svarttjärnen S/V., Dls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>316929</v>
+        <v>316837</v>
       </c>
       <c r="R37" t="n">
-        <v>6550454</v>
+        <v>6550397</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -5381,7 +5381,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128087033</v>
+        <v>128087641</v>
       </c>
       <c r="B42" t="n">
         <v>98467</v>
@@ -5424,10 +5424,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>316848</v>
+        <v>316887</v>
       </c>
       <c r="R42" t="n">
-        <v>6550426</v>
+        <v>6550467</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5492,7 +5492,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128087641</v>
+        <v>128087033</v>
       </c>
       <c r="B43" t="n">
         <v>98467</v>
@@ -5535,10 +5535,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>316887</v>
+        <v>316848</v>
       </c>
       <c r="R43" t="n">
-        <v>6550467</v>
+        <v>6550426</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5603,7 +5603,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128086546</v>
+        <v>128086710</v>
       </c>
       <c r="B44" t="n">
         <v>98467</v>
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>316848</v>
+        <v>316825</v>
       </c>
       <c r="R44" t="n">
-        <v>6550398</v>
+        <v>6550399</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5825,7 +5825,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128086710</v>
+        <v>128086546</v>
       </c>
       <c r="B46" t="n">
         <v>98467</v>
@@ -5868,10 +5868,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>316825</v>
+        <v>316848</v>
       </c>
       <c r="R46" t="n">
-        <v>6550399</v>
+        <v>6550398</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5936,7 +5936,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128086451</v>
+        <v>128086825</v>
       </c>
       <c r="B47" t="n">
         <v>98467</v>
@@ -5979,10 +5979,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>316834</v>
+        <v>316809</v>
       </c>
       <c r="R47" t="n">
-        <v>6550393</v>
+        <v>6550455</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6047,7 +6047,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128086825</v>
+        <v>128086406</v>
       </c>
       <c r="B48" t="n">
         <v>98467</v>
@@ -6090,10 +6090,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>316809</v>
+        <v>316836</v>
       </c>
       <c r="R48" t="n">
-        <v>6550455</v>
+        <v>6550393</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6158,7 +6158,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128086406</v>
+        <v>128086451</v>
       </c>
       <c r="B49" t="n">
         <v>98467</v>
@@ -6201,7 +6201,7 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>316836</v>
+        <v>316834</v>
       </c>
       <c r="R49" t="n">
         <v>6550393</v>
@@ -6523,42 +6523,41 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128086997</v>
+        <v>128085763</v>
       </c>
       <c r="B52" t="n">
-        <v>98467</v>
+        <v>91822</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>5467</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6566,10 +6565,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>316832</v>
+        <v>316919</v>
       </c>
       <c r="R52" t="n">
-        <v>6550424</v>
+        <v>6550474</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6616,7 +6615,22 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Mosseljungbarrskog</t>
+          <t>Bärljunbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6634,52 +6648,54 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128085763</v>
+        <v>128084916</v>
       </c>
       <c r="B53" t="n">
-        <v>91822</v>
+        <v>8450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5467</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Svarttjärnen S/V., Dls</t>
+          <t>Ormetjärn S/V., Dls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>316919</v>
+        <v>317037</v>
       </c>
       <c r="R53" t="n">
-        <v>6550474</v>
+        <v>6550398</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6726,7 +6742,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>Bärljunbarrskog</t>
+          <t>Bärljungbarrskog</t>
         </is>
       </c>
       <c r="AJ53" t="inlineStr">
@@ -6759,53 +6775,54 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128086772</v>
+        <v>128085525</v>
       </c>
       <c r="B54" t="n">
-        <v>98467</v>
+        <v>8450</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Svarttjärnen S/V., Dls</t>
+          <t>Svarttjärnen S., Dls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>316809</v>
+        <v>316911</v>
       </c>
       <c r="R54" t="n">
-        <v>6550451</v>
+        <v>6550369</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6852,7 +6869,22 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Mosseljungbarrskog</t>
+          <t>Bärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Gadd # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6870,54 +6902,53 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128084916</v>
+        <v>128086997</v>
       </c>
       <c r="B55" t="n">
-        <v>8450</v>
+        <v>98467</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Ormetjärn S/V., Dls</t>
+          <t>Svarttjärnen S/V., Dls</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>317037</v>
+        <v>316832</v>
       </c>
       <c r="R55" t="n">
-        <v>6550398</v>
+        <v>6550424</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6964,22 +6995,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Mosseljungbarrskog</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6997,54 +7013,53 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128085525</v>
+        <v>128086772</v>
       </c>
       <c r="B56" t="n">
-        <v>8450</v>
+        <v>98467</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Svarttjärnen S., Dls</t>
+          <t>Svarttjärnen S/V., Dls</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>316911</v>
+        <v>316809</v>
       </c>
       <c r="R56" t="n">
-        <v>6550369</v>
+        <v>6550451</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7091,22 +7106,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Gadd # Pinus sylvestris</t>
+          <t>Mosseljungbarrskog</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7584,53 +7584,52 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128087465</v>
+        <v>128085294</v>
       </c>
       <c r="B61" t="n">
-        <v>98467</v>
+        <v>92832</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Svarttjärnen S/V., Dls</t>
+          <t>Ormetjärn S/V., Dls</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>316860</v>
+        <v>317041</v>
       </c>
       <c r="R61" t="n">
-        <v>6550480</v>
+        <v>6550370</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7677,7 +7676,22 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Mosseljungbarrskog</t>
+          <t>Bärljungtallskog</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7695,52 +7709,53 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128085294</v>
+        <v>128087465</v>
       </c>
       <c r="B62" t="n">
-        <v>92832</v>
+        <v>98467</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2079</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Ormetjärn S/V., Dls</t>
+          <t>Svarttjärnen S/V., Dls</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>317041</v>
+        <v>316860</v>
       </c>
       <c r="R62" t="n">
-        <v>6550370</v>
+        <v>6550480</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7787,22 +7802,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>Bärljungtallskog</t>
-        </is>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Mosseljungbarrskog</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7931,54 +7931,53 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128084637</v>
+        <v>128087506</v>
       </c>
       <c r="B64" t="n">
-        <v>8450</v>
+        <v>98467</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Svarttjärnen O., Dls</t>
+          <t>Svarttjärnen S/V., Dls</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>316984</v>
+        <v>316865</v>
       </c>
       <c r="R64" t="n">
-        <v>6550597</v>
+        <v>6550469</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -8025,22 +8024,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Gadd # Pinus sylvestris</t>
+          <t>Mosseljungbarrskog</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8058,7 +8042,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128087606</v>
+        <v>128087411</v>
       </c>
       <c r="B65" t="n">
         <v>98467</v>
@@ -8101,10 +8085,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>316877</v>
+        <v>316858</v>
       </c>
       <c r="R65" t="n">
-        <v>6550456</v>
+        <v>6550464</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -8169,53 +8153,54 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128087506</v>
+        <v>128084637</v>
       </c>
       <c r="B66" t="n">
-        <v>98467</v>
+        <v>8450</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Svarttjärnen S/V., Dls</t>
+          <t>Svarttjärnen O., Dls</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>316865</v>
+        <v>316984</v>
       </c>
       <c r="R66" t="n">
-        <v>6550469</v>
+        <v>6550597</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -8262,7 +8247,22 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>Mosseljungbarrskog</t>
+          <t>Bärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Gadd # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8280,7 +8280,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128087411</v>
+        <v>128087606</v>
       </c>
       <c r="B67" t="n">
         <v>98467</v>
@@ -8323,10 +8323,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>316858</v>
+        <v>316877</v>
       </c>
       <c r="R67" t="n">
-        <v>6550464</v>
+        <v>6550456</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>

--- a/artfynd/A 40826-2025 artfynd.xlsx
+++ b/artfynd/A 40826-2025 artfynd.xlsx
@@ -4119,7 +4119,7 @@
         <v>128085650</v>
       </c>
       <c r="B31" t="n">
-        <v>91822</v>
+        <v>91823</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         <v>128086622</v>
       </c>
       <c r="B32" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>128086988</v>
       </c>
       <c r="B33" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         <v>128086910</v>
       </c>
       <c r="B34" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         <v>128087681</v>
       </c>
       <c r="B36" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>128086358</v>
       </c>
       <c r="B37" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>128085583</v>
       </c>
       <c r="B38" t="n">
-        <v>91822</v>
+        <v>91823</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>128087374</v>
       </c>
       <c r="B39" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5159,10 +5159,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128087074</v>
+        <v>128086155</v>
       </c>
       <c r="B40" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5202,10 +5202,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>316863</v>
+        <v>316836</v>
       </c>
       <c r="R40" t="n">
-        <v>6550433</v>
+        <v>6550404</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5270,10 +5270,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128086155</v>
+        <v>128087074</v>
       </c>
       <c r="B41" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5313,10 +5313,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>316836</v>
+        <v>316863</v>
       </c>
       <c r="R41" t="n">
-        <v>6550404</v>
+        <v>6550433</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5384,7 +5384,7 @@
         <v>128087641</v>
       </c>
       <c r="B42" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         <v>128087033</v>
       </c>
       <c r="B43" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>128086710</v>
       </c>
       <c r="B44" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         <v>128087244</v>
       </c>
       <c r="B45" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         <v>128086546</v>
       </c>
       <c r="B46" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         <v>128086825</v>
       </c>
       <c r="B47" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v>128086406</v>
       </c>
       <c r="B48" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>128086451</v>
       </c>
       <c r="B49" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6272,7 +6272,7 @@
         <v>128085493</v>
       </c>
       <c r="B50" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>128085763</v>
       </c>
       <c r="B52" t="n">
-        <v>91822</v>
+        <v>91823</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
         <v>128086997</v>
       </c>
       <c r="B55" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>128086772</v>
       </c>
       <c r="B56" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         <v>128086654</v>
       </c>
       <c r="B58" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7365,7 +7365,7 @@
         <v>128086469</v>
       </c>
       <c r="B59" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7476,7 +7476,7 @@
         <v>128086692</v>
       </c>
       <c r="B60" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         <v>128085294</v>
       </c>
       <c r="B61" t="n">
-        <v>92832</v>
+        <v>92833</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>128087465</v>
       </c>
       <c r="B62" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7823,7 +7823,7 @@
         <v>128086718</v>
       </c>
       <c r="B63" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7931,53 +7931,54 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128087506</v>
+        <v>128084637</v>
       </c>
       <c r="B64" t="n">
-        <v>98467</v>
+        <v>8450</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Svarttjärnen S/V., Dls</t>
+          <t>Svarttjärnen O., Dls</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>316865</v>
+        <v>316984</v>
       </c>
       <c r="R64" t="n">
-        <v>6550469</v>
+        <v>6550597</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -8024,7 +8025,22 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Mosseljungbarrskog</t>
+          <t>Bärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Gadd # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8042,10 +8058,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128087411</v>
+        <v>128087506</v>
       </c>
       <c r="B65" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8085,10 +8101,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>316858</v>
+        <v>316865</v>
       </c>
       <c r="R65" t="n">
-        <v>6550464</v>
+        <v>6550469</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -8153,54 +8169,53 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128084637</v>
+        <v>128087411</v>
       </c>
       <c r="B66" t="n">
-        <v>8450</v>
+        <v>98468</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Svarttjärnen O., Dls</t>
+          <t>Svarttjärnen S/V., Dls</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>316984</v>
+        <v>316858</v>
       </c>
       <c r="R66" t="n">
-        <v>6550597</v>
+        <v>6550464</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -8247,22 +8262,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Gadd # Pinus sylvestris</t>
+          <t>Mosseljungbarrskog</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8283,7 +8283,7 @@
         <v>128087606</v>
       </c>
       <c r="B67" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8394,7 +8394,7 @@
         <v>128087295</v>
       </c>
       <c r="B68" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8502,36 +8502,40 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128085956</v>
+        <v>128086518</v>
       </c>
       <c r="B69" t="n">
-        <v>97344</v>
+        <v>98468</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
@@ -8541,10 +8545,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>316904</v>
+        <v>316852</v>
       </c>
       <c r="R69" t="n">
-        <v>6550464</v>
+        <v>6550388</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8591,7 +8595,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
+          <t>Mosseljungbarrskog</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8609,40 +8613,36 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128086518</v>
+        <v>128085956</v>
       </c>
       <c r="B70" t="n">
-        <v>98467</v>
+        <v>97345</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
@@ -8652,10 +8652,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>316852</v>
+        <v>316904</v>
       </c>
       <c r="R70" t="n">
-        <v>6550388</v>
+        <v>6550464</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8702,7 +8702,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>Mosseljungbarrskog</t>
+          <t>Bärljungbarrskog</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>

--- a/artfynd/A 40826-2025 artfynd.xlsx
+++ b/artfynd/A 40826-2025 artfynd.xlsx
@@ -8502,40 +8502,36 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128086518</v>
+        <v>128085956</v>
       </c>
       <c r="B69" t="n">
-        <v>98468</v>
+        <v>97345</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
@@ -8545,10 +8541,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>316852</v>
+        <v>316904</v>
       </c>
       <c r="R69" t="n">
-        <v>6550388</v>
+        <v>6550464</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8595,7 +8591,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Mosseljungbarrskog</t>
+          <t>Bärljungbarrskog</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8613,36 +8609,40 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128085956</v>
+        <v>128086518</v>
       </c>
       <c r="B70" t="n">
-        <v>97345</v>
+        <v>98468</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
@@ -8652,10 +8652,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>316904</v>
+        <v>316852</v>
       </c>
       <c r="R70" t="n">
-        <v>6550464</v>
+        <v>6550388</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8702,7 +8702,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
+          <t>Mosseljungbarrskog</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>

--- a/artfynd/A 40826-2025 artfynd.xlsx
+++ b/artfynd/A 40826-2025 artfynd.xlsx
@@ -4119,7 +4119,7 @@
         <v>128085650</v>
       </c>
       <c r="B31" t="n">
-        <v>91823</v>
+        <v>91824</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         <v>128086622</v>
       </c>
       <c r="B32" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>128086988</v>
       </c>
       <c r="B33" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         <v>128086910</v>
       </c>
       <c r="B34" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         <v>128087681</v>
       </c>
       <c r="B36" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>128086358</v>
       </c>
       <c r="B37" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>128085583</v>
       </c>
       <c r="B38" t="n">
-        <v>91823</v>
+        <v>91824</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>128087374</v>
       </c>
       <c r="B39" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         <v>128086155</v>
       </c>
       <c r="B40" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         <v>128087074</v>
       </c>
       <c r="B41" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         <v>128087641</v>
       </c>
       <c r="B42" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         <v>128087033</v>
       </c>
       <c r="B43" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>128086710</v>
       </c>
       <c r="B44" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         <v>128087244</v>
       </c>
       <c r="B45" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         <v>128086546</v>
       </c>
       <c r="B46" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         <v>128086825</v>
       </c>
       <c r="B47" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v>128086406</v>
       </c>
       <c r="B48" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>128086451</v>
       </c>
       <c r="B49" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6272,7 +6272,7 @@
         <v>128085493</v>
       </c>
       <c r="B50" t="n">
-        <v>91370</v>
+        <v>91371</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6523,52 +6523,54 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128085763</v>
+        <v>128084916</v>
       </c>
       <c r="B52" t="n">
-        <v>91823</v>
+        <v>8450</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5467</v>
+        <v>106545</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Svarttjärnen S/V., Dls</t>
+          <t>Ormetjärn S/V., Dls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>316919</v>
+        <v>317037</v>
       </c>
       <c r="R52" t="n">
-        <v>6550474</v>
+        <v>6550398</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6615,7 +6617,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Bärljunbarrskog</t>
+          <t>Bärljungbarrskog</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
@@ -6648,7 +6650,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128084916</v>
+        <v>128085525</v>
       </c>
       <c r="B53" t="n">
         <v>8450</v>
@@ -6688,14 +6690,14 @@
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Ormetjärn S/V., Dls</t>
+          <t>Svarttjärnen S., Dls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>317037</v>
+        <v>316911</v>
       </c>
       <c r="R53" t="n">
-        <v>6550398</v>
+        <v>6550369</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6757,7 +6759,7 @@
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Gadd # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6775,54 +6777,53 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128085525</v>
+        <v>128086997</v>
       </c>
       <c r="B54" t="n">
-        <v>8450</v>
+        <v>98469</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Svarttjärnen S., Dls</t>
+          <t>Svarttjärnen S/V., Dls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>316911</v>
+        <v>316832</v>
       </c>
       <c r="R54" t="n">
-        <v>6550369</v>
+        <v>6550424</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6869,22 +6870,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Gadd # Pinus sylvestris</t>
+          <t>Mosseljungbarrskog</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6902,10 +6888,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128086997</v>
+        <v>128086772</v>
       </c>
       <c r="B55" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6945,10 +6931,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>316832</v>
+        <v>316809</v>
       </c>
       <c r="R55" t="n">
-        <v>6550424</v>
+        <v>6550451</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -7013,42 +6999,41 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128086772</v>
+        <v>128085763</v>
       </c>
       <c r="B56" t="n">
-        <v>98468</v>
+        <v>91824</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>5467</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7056,10 +7041,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>316809</v>
+        <v>316919</v>
       </c>
       <c r="R56" t="n">
-        <v>6550451</v>
+        <v>6550474</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7106,7 +7091,22 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Mosseljungbarrskog</t>
+          <t>Bärljunbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7254,7 +7254,7 @@
         <v>128086654</v>
       </c>
       <c r="B58" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7365,7 +7365,7 @@
         <v>128086469</v>
       </c>
       <c r="B59" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7476,7 +7476,7 @@
         <v>128086692</v>
       </c>
       <c r="B60" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         <v>128085294</v>
       </c>
       <c r="B61" t="n">
-        <v>92833</v>
+        <v>92834</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>128087465</v>
       </c>
       <c r="B62" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7823,7 +7823,7 @@
         <v>128086718</v>
       </c>
       <c r="B63" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8061,7 +8061,7 @@
         <v>128087506</v>
       </c>
       <c r="B65" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8172,7 +8172,7 @@
         <v>128087411</v>
       </c>
       <c r="B66" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>128087606</v>
       </c>
       <c r="B67" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8394,7 +8394,7 @@
         <v>128087295</v>
       </c>
       <c r="B68" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         <v>128085956</v>
       </c>
       <c r="B69" t="n">
-        <v>97345</v>
+        <v>97346</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>128086518</v>
       </c>
       <c r="B70" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 40826-2025 artfynd.xlsx
+++ b/artfynd/A 40826-2025 artfynd.xlsx
@@ -4119,7 +4119,7 @@
         <v>128085650</v>
       </c>
       <c r="B31" t="n">
-        <v>91824</v>
+        <v>91825</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4241,10 +4241,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128086622</v>
+        <v>128086988</v>
       </c>
       <c r="B32" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4284,10 +4284,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>316857</v>
+        <v>316819</v>
       </c>
       <c r="R32" t="n">
-        <v>6550392</v>
+        <v>6550452</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4352,10 +4352,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128086988</v>
+        <v>128086622</v>
       </c>
       <c r="B33" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4395,10 +4395,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>316819</v>
+        <v>316857</v>
       </c>
       <c r="R33" t="n">
-        <v>6550452</v>
+        <v>6550392</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4466,7 +4466,7 @@
         <v>128086910</v>
       </c>
       <c r="B34" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         <v>128087681</v>
       </c>
       <c r="B36" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>128086358</v>
       </c>
       <c r="B37" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>128085583</v>
       </c>
       <c r="B38" t="n">
-        <v>91824</v>
+        <v>91825</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>128087374</v>
       </c>
       <c r="B39" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         <v>128086155</v>
       </c>
       <c r="B40" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5270,10 +5270,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128087074</v>
+        <v>128087641</v>
       </c>
       <c r="B41" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5313,10 +5313,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>316863</v>
+        <v>316887</v>
       </c>
       <c r="R41" t="n">
-        <v>6550433</v>
+        <v>6550467</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5381,10 +5381,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128087641</v>
+        <v>128087074</v>
       </c>
       <c r="B42" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5424,10 +5424,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>316887</v>
+        <v>316863</v>
       </c>
       <c r="R42" t="n">
-        <v>6550467</v>
+        <v>6550433</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5495,7 +5495,7 @@
         <v>128087033</v>
       </c>
       <c r="B43" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>128086710</v>
       </c>
       <c r="B44" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         <v>128087244</v>
       </c>
       <c r="B45" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         <v>128086546</v>
       </c>
       <c r="B46" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         <v>128086825</v>
       </c>
       <c r="B47" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v>128086406</v>
       </c>
       <c r="B48" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>128086451</v>
       </c>
       <c r="B49" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6272,7 +6272,7 @@
         <v>128085493</v>
       </c>
       <c r="B50" t="n">
-        <v>91371</v>
+        <v>91372</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6523,54 +6523,52 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128084916</v>
+        <v>128085763</v>
       </c>
       <c r="B52" t="n">
-        <v>8450</v>
+        <v>91825</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>5467</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Ormetjärn S/V., Dls</t>
+          <t>Svarttjärnen S/V., Dls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>317037</v>
+        <v>316919</v>
       </c>
       <c r="R52" t="n">
-        <v>6550398</v>
+        <v>6550474</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6617,7 +6615,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
+          <t>Bärljunbarrskog</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
@@ -6650,7 +6648,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128085525</v>
+        <v>128084916</v>
       </c>
       <c r="B53" t="n">
         <v>8450</v>
@@ -6690,14 +6688,14 @@
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Svarttjärnen S., Dls</t>
+          <t>Ormetjärn S/V., Dls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>316911</v>
+        <v>317037</v>
       </c>
       <c r="R53" t="n">
-        <v>6550369</v>
+        <v>6550398</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6759,7 +6757,7 @@
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Gadd # Pinus sylvestris</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6777,53 +6775,54 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128086997</v>
+        <v>128085525</v>
       </c>
       <c r="B54" t="n">
-        <v>98469</v>
+        <v>8450</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Svarttjärnen S/V., Dls</t>
+          <t>Svarttjärnen S., Dls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>316832</v>
+        <v>316911</v>
       </c>
       <c r="R54" t="n">
-        <v>6550424</v>
+        <v>6550369</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6870,7 +6869,22 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Mosseljungbarrskog</t>
+          <t>Bärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Gadd # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6888,10 +6902,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128086772</v>
+        <v>128086997</v>
       </c>
       <c r="B55" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6931,10 +6945,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>316809</v>
+        <v>316832</v>
       </c>
       <c r="R55" t="n">
-        <v>6550451</v>
+        <v>6550424</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6999,41 +7013,42 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128085763</v>
+        <v>128086772</v>
       </c>
       <c r="B56" t="n">
-        <v>91824</v>
+        <v>98470</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5467</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7041,10 +7056,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>316919</v>
+        <v>316809</v>
       </c>
       <c r="R56" t="n">
-        <v>6550474</v>
+        <v>6550451</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7091,22 +7106,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Bärljunbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Mosseljungbarrskog</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7254,7 +7254,7 @@
         <v>128086654</v>
       </c>
       <c r="B58" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7365,7 +7365,7 @@
         <v>128086469</v>
       </c>
       <c r="B59" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7476,7 +7476,7 @@
         <v>128086692</v>
       </c>
       <c r="B60" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         <v>128085294</v>
       </c>
       <c r="B61" t="n">
-        <v>92834</v>
+        <v>92835</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>128087465</v>
       </c>
       <c r="B62" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7823,7 +7823,7 @@
         <v>128086718</v>
       </c>
       <c r="B63" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8061,7 +8061,7 @@
         <v>128087506</v>
       </c>
       <c r="B65" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8172,7 +8172,7 @@
         <v>128087411</v>
       </c>
       <c r="B66" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>128087606</v>
       </c>
       <c r="B67" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8394,7 +8394,7 @@
         <v>128087295</v>
       </c>
       <c r="B68" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8502,36 +8502,40 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128085956</v>
+        <v>128086518</v>
       </c>
       <c r="B69" t="n">
-        <v>97346</v>
+        <v>98470</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
@@ -8541,10 +8545,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>316904</v>
+        <v>316852</v>
       </c>
       <c r="R69" t="n">
-        <v>6550464</v>
+        <v>6550388</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8591,7 +8595,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
+          <t>Mosseljungbarrskog</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8609,40 +8613,36 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128086518</v>
+        <v>128085956</v>
       </c>
       <c r="B70" t="n">
-        <v>98469</v>
+        <v>97347</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
@@ -8652,10 +8652,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>316852</v>
+        <v>316904</v>
       </c>
       <c r="R70" t="n">
-        <v>6550388</v>
+        <v>6550464</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8702,7 +8702,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>Mosseljungbarrskog</t>
+          <t>Bärljungbarrskog</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>

--- a/artfynd/A 40826-2025 artfynd.xlsx
+++ b/artfynd/A 40826-2025 artfynd.xlsx
@@ -4241,7 +4241,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128086988</v>
+        <v>128086622</v>
       </c>
       <c r="B32" t="n">
         <v>98470</v>
@@ -4284,10 +4284,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>316819</v>
+        <v>316857</v>
       </c>
       <c r="R32" t="n">
-        <v>6550452</v>
+        <v>6550392</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4352,7 +4352,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128086622</v>
+        <v>128086988</v>
       </c>
       <c r="B33" t="n">
         <v>98470</v>
@@ -4395,10 +4395,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>316857</v>
+        <v>316819</v>
       </c>
       <c r="R33" t="n">
-        <v>6550392</v>
+        <v>6550452</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -5270,7 +5270,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128087641</v>
+        <v>128087074</v>
       </c>
       <c r="B41" t="n">
         <v>98470</v>
@@ -5313,10 +5313,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>316887</v>
+        <v>316863</v>
       </c>
       <c r="R41" t="n">
-        <v>6550467</v>
+        <v>6550433</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5381,7 +5381,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128087074</v>
+        <v>128087641</v>
       </c>
       <c r="B42" t="n">
         <v>98470</v>
@@ -5424,10 +5424,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>316863</v>
+        <v>316887</v>
       </c>
       <c r="R42" t="n">
-        <v>6550433</v>
+        <v>6550467</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -6523,41 +6523,42 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128085763</v>
+        <v>128086997</v>
       </c>
       <c r="B52" t="n">
-        <v>91825</v>
+        <v>98470</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5467</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6565,10 +6566,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>316919</v>
+        <v>316832</v>
       </c>
       <c r="R52" t="n">
-        <v>6550474</v>
+        <v>6550424</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6615,22 +6616,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Bärljunbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Mosseljungbarrskog</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6648,54 +6634,53 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128084916</v>
+        <v>128086772</v>
       </c>
       <c r="B53" t="n">
-        <v>8450</v>
+        <v>98470</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Ormetjärn S/V., Dls</t>
+          <t>Svarttjärnen S/V., Dls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>317037</v>
+        <v>316809</v>
       </c>
       <c r="R53" t="n">
-        <v>6550398</v>
+        <v>6550451</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6742,22 +6727,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Mosseljungbarrskog</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6775,54 +6745,52 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128085525</v>
+        <v>128085763</v>
       </c>
       <c r="B54" t="n">
-        <v>8450</v>
+        <v>91825</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>5467</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Svarttjärnen S., Dls</t>
+          <t>Svarttjärnen S/V., Dls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>316911</v>
+        <v>316919</v>
       </c>
       <c r="R54" t="n">
-        <v>6550369</v>
+        <v>6550474</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6869,7 +6837,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
+          <t>Bärljunbarrskog</t>
         </is>
       </c>
       <c r="AJ54" t="inlineStr">
@@ -6884,7 +6852,7 @@
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Gadd # Pinus sylvestris</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6902,53 +6870,54 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128086997</v>
+        <v>128084916</v>
       </c>
       <c r="B55" t="n">
-        <v>98470</v>
+        <v>8450</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Svarttjärnen S/V., Dls</t>
+          <t>Ormetjärn S/V., Dls</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>316832</v>
+        <v>317037</v>
       </c>
       <c r="R55" t="n">
-        <v>6550424</v>
+        <v>6550398</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6995,7 +6964,22 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Mosseljungbarrskog</t>
+          <t>Bärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7013,53 +6997,54 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128086772</v>
+        <v>128085525</v>
       </c>
       <c r="B56" t="n">
-        <v>98470</v>
+        <v>8450</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Svarttjärnen S/V., Dls</t>
+          <t>Svarttjärnen S., Dls</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>316809</v>
+        <v>316911</v>
       </c>
       <c r="R56" t="n">
-        <v>6550451</v>
+        <v>6550369</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7106,7 +7091,22 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Mosseljungbarrskog</t>
+          <t>Bärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Gadd # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7931,54 +7931,53 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128084637</v>
+        <v>128087506</v>
       </c>
       <c r="B64" t="n">
-        <v>8450</v>
+        <v>98470</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Svarttjärnen O., Dls</t>
+          <t>Svarttjärnen S/V., Dls</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>316984</v>
+        <v>316865</v>
       </c>
       <c r="R64" t="n">
-        <v>6550597</v>
+        <v>6550469</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -8025,22 +8024,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Gadd # Pinus sylvestris</t>
+          <t>Mosseljungbarrskog</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8058,7 +8042,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128087506</v>
+        <v>128087411</v>
       </c>
       <c r="B65" t="n">
         <v>98470</v>
@@ -8101,10 +8085,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>316865</v>
+        <v>316858</v>
       </c>
       <c r="R65" t="n">
-        <v>6550469</v>
+        <v>6550464</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -8169,7 +8153,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128087411</v>
+        <v>128087606</v>
       </c>
       <c r="B66" t="n">
         <v>98470</v>
@@ -8212,10 +8196,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>316858</v>
+        <v>316877</v>
       </c>
       <c r="R66" t="n">
-        <v>6550464</v>
+        <v>6550456</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -8280,53 +8264,54 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128087606</v>
+        <v>128084637</v>
       </c>
       <c r="B67" t="n">
-        <v>98470</v>
+        <v>8450</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Svarttjärnen S/V., Dls</t>
+          <t>Svarttjärnen O., Dls</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>316877</v>
+        <v>316984</v>
       </c>
       <c r="R67" t="n">
-        <v>6550456</v>
+        <v>6550597</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -8373,7 +8358,22 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Mosseljungbarrskog</t>
+          <t>Bärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Gadd # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>

--- a/artfynd/A 40826-2025 artfynd.xlsx
+++ b/artfynd/A 40826-2025 artfynd.xlsx
@@ -7584,52 +7584,53 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128085294</v>
+        <v>128087465</v>
       </c>
       <c r="B61" t="n">
-        <v>92835</v>
+        <v>98470</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2079</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Ormetjärn S/V., Dls</t>
+          <t>Svarttjärnen S/V., Dls</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>317041</v>
+        <v>316860</v>
       </c>
       <c r="R61" t="n">
-        <v>6550370</v>
+        <v>6550480</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7676,22 +7677,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Bärljungtallskog</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Mosseljungbarrskog</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7709,7 +7695,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128087465</v>
+        <v>128086718</v>
       </c>
       <c r="B62" t="n">
         <v>98470</v>
@@ -7752,10 +7738,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>316860</v>
+        <v>316821</v>
       </c>
       <c r="R62" t="n">
-        <v>6550480</v>
+        <v>6550398</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7820,53 +7806,52 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128086718</v>
+        <v>128085294</v>
       </c>
       <c r="B63" t="n">
-        <v>98470</v>
+        <v>92835</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Svarttjärnen S/V., Dls</t>
+          <t>Ormetjärn S/V., Dls</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>316821</v>
+        <v>317041</v>
       </c>
       <c r="R63" t="n">
-        <v>6550398</v>
+        <v>6550370</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7913,7 +7898,22 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>Mosseljungbarrskog</t>
+          <t>Bärljungtallskog</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>

--- a/artfynd/A 40826-2025 artfynd.xlsx
+++ b/artfynd/A 40826-2025 artfynd.xlsx
@@ -6523,42 +6523,41 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128086997</v>
+        <v>128085763</v>
       </c>
       <c r="B52" t="n">
-        <v>98470</v>
+        <v>91825</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>5467</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6566,10 +6565,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>316832</v>
+        <v>316919</v>
       </c>
       <c r="R52" t="n">
-        <v>6550424</v>
+        <v>6550474</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6616,7 +6615,22 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Mosseljungbarrskog</t>
+          <t>Bärljunbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6634,53 +6648,54 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128086772</v>
+        <v>128084916</v>
       </c>
       <c r="B53" t="n">
-        <v>98470</v>
+        <v>8450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Svarttjärnen S/V., Dls</t>
+          <t>Ormetjärn S/V., Dls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>316809</v>
+        <v>317037</v>
       </c>
       <c r="R53" t="n">
-        <v>6550451</v>
+        <v>6550398</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6727,7 +6742,22 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>Mosseljungbarrskog</t>
+          <t>Bärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6745,52 +6775,54 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128085763</v>
+        <v>128085525</v>
       </c>
       <c r="B54" t="n">
-        <v>91825</v>
+        <v>8450</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5467</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Svarttjärnen S/V., Dls</t>
+          <t>Svarttjärnen S., Dls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>316919</v>
+        <v>316911</v>
       </c>
       <c r="R54" t="n">
-        <v>6550474</v>
+        <v>6550369</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6837,7 +6869,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Bärljunbarrskog</t>
+          <t>Bärljungbarrskog</t>
         </is>
       </c>
       <c r="AJ54" t="inlineStr">
@@ -6852,7 +6884,7 @@
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Gadd # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6870,54 +6902,53 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128084916</v>
+        <v>128086997</v>
       </c>
       <c r="B55" t="n">
-        <v>8450</v>
+        <v>98470</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Ormetjärn S/V., Dls</t>
+          <t>Svarttjärnen S/V., Dls</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>317037</v>
+        <v>316832</v>
       </c>
       <c r="R55" t="n">
-        <v>6550398</v>
+        <v>6550424</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6964,22 +6995,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Mosseljungbarrskog</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6997,54 +7013,53 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128085525</v>
+        <v>128086772</v>
       </c>
       <c r="B56" t="n">
-        <v>8450</v>
+        <v>98470</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Svarttjärnen S., Dls</t>
+          <t>Svarttjärnen S/V., Dls</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>316911</v>
+        <v>316809</v>
       </c>
       <c r="R56" t="n">
-        <v>6550369</v>
+        <v>6550451</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7091,22 +7106,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Gadd # Pinus sylvestris</t>
+          <t>Mosseljungbarrskog</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>

--- a/artfynd/A 40826-2025 artfynd.xlsx
+++ b/artfynd/A 40826-2025 artfynd.xlsx
@@ -6523,41 +6523,42 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128085763</v>
+        <v>128086997</v>
       </c>
       <c r="B52" t="n">
-        <v>91825</v>
+        <v>98470</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5467</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6565,10 +6566,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>316919</v>
+        <v>316832</v>
       </c>
       <c r="R52" t="n">
-        <v>6550474</v>
+        <v>6550424</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6615,22 +6616,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Bärljunbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Mosseljungbarrskog</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6648,54 +6634,53 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128084916</v>
+        <v>128086772</v>
       </c>
       <c r="B53" t="n">
-        <v>8450</v>
+        <v>98470</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Ormetjärn S/V., Dls</t>
+          <t>Svarttjärnen S/V., Dls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>317037</v>
+        <v>316809</v>
       </c>
       <c r="R53" t="n">
-        <v>6550398</v>
+        <v>6550451</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6742,22 +6727,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Mosseljungbarrskog</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6775,54 +6745,52 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128085525</v>
+        <v>128085763</v>
       </c>
       <c r="B54" t="n">
-        <v>8450</v>
+        <v>91825</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>5467</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Svarttjärnen S., Dls</t>
+          <t>Svarttjärnen S/V., Dls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>316911</v>
+        <v>316919</v>
       </c>
       <c r="R54" t="n">
-        <v>6550369</v>
+        <v>6550474</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6869,7 +6837,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
+          <t>Bärljunbarrskog</t>
         </is>
       </c>
       <c r="AJ54" t="inlineStr">
@@ -6884,7 +6852,7 @@
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Gadd # Pinus sylvestris</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6902,53 +6870,54 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128086997</v>
+        <v>128084916</v>
       </c>
       <c r="B55" t="n">
-        <v>98470</v>
+        <v>8450</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Svarttjärnen S/V., Dls</t>
+          <t>Ormetjärn S/V., Dls</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>316832</v>
+        <v>317037</v>
       </c>
       <c r="R55" t="n">
-        <v>6550424</v>
+        <v>6550398</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6995,7 +6964,22 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Mosseljungbarrskog</t>
+          <t>Bärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7013,53 +6997,54 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128086772</v>
+        <v>128085525</v>
       </c>
       <c r="B56" t="n">
-        <v>98470</v>
+        <v>8450</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Svarttjärnen S/V., Dls</t>
+          <t>Svarttjärnen S., Dls</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>316809</v>
+        <v>316911</v>
       </c>
       <c r="R56" t="n">
-        <v>6550451</v>
+        <v>6550369</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7106,7 +7091,22 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Mosseljungbarrskog</t>
+          <t>Bärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Gadd # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>

--- a/artfynd/A 40826-2025 artfynd.xlsx
+++ b/artfynd/A 40826-2025 artfynd.xlsx
@@ -7584,53 +7584,52 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128087465</v>
+        <v>128085294</v>
       </c>
       <c r="B61" t="n">
-        <v>98470</v>
+        <v>92835</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Svarttjärnen S/V., Dls</t>
+          <t>Ormetjärn S/V., Dls</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>316860</v>
+        <v>317041</v>
       </c>
       <c r="R61" t="n">
-        <v>6550480</v>
+        <v>6550370</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7677,7 +7676,22 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Mosseljungbarrskog</t>
+          <t>Bärljungtallskog</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7695,7 +7709,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128086718</v>
+        <v>128087465</v>
       </c>
       <c r="B62" t="n">
         <v>98470</v>
@@ -7738,10 +7752,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>316821</v>
+        <v>316860</v>
       </c>
       <c r="R62" t="n">
-        <v>6550398</v>
+        <v>6550480</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7806,52 +7820,53 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128085294</v>
+        <v>128086718</v>
       </c>
       <c r="B63" t="n">
-        <v>92835</v>
+        <v>98470</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2079</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Ormetjärn S/V., Dls</t>
+          <t>Svarttjärnen S/V., Dls</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>317041</v>
+        <v>316821</v>
       </c>
       <c r="R63" t="n">
-        <v>6550370</v>
+        <v>6550398</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7898,22 +7913,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>Bärljungtallskog</t>
-        </is>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Mosseljungbarrskog</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7931,53 +7931,54 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128087506</v>
+        <v>128084637</v>
       </c>
       <c r="B64" t="n">
-        <v>98470</v>
+        <v>8450</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Svarttjärnen S/V., Dls</t>
+          <t>Svarttjärnen O., Dls</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>316865</v>
+        <v>316984</v>
       </c>
       <c r="R64" t="n">
-        <v>6550469</v>
+        <v>6550597</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -8024,7 +8025,22 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Mosseljungbarrskog</t>
+          <t>Bärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Gadd # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8042,7 +8058,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128087411</v>
+        <v>128087506</v>
       </c>
       <c r="B65" t="n">
         <v>98470</v>
@@ -8085,10 +8101,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>316858</v>
+        <v>316865</v>
       </c>
       <c r="R65" t="n">
-        <v>6550464</v>
+        <v>6550469</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -8153,7 +8169,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128087606</v>
+        <v>128087411</v>
       </c>
       <c r="B66" t="n">
         <v>98470</v>
@@ -8196,10 +8212,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>316877</v>
+        <v>316858</v>
       </c>
       <c r="R66" t="n">
-        <v>6550456</v>
+        <v>6550464</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -8264,54 +8280,53 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128084637</v>
+        <v>128087606</v>
       </c>
       <c r="B67" t="n">
-        <v>8450</v>
+        <v>98470</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Svarttjärnen O., Dls</t>
+          <t>Svarttjärnen S/V., Dls</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>316984</v>
+        <v>316877</v>
       </c>
       <c r="R67" t="n">
-        <v>6550597</v>
+        <v>6550456</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -8358,22 +8373,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Gadd # Pinus sylvestris</t>
+          <t>Mosseljungbarrskog</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>

--- a/artfynd/A 40826-2025 artfynd.xlsx
+++ b/artfynd/A 40826-2025 artfynd.xlsx
@@ -4116,41 +4116,42 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128085650</v>
+        <v>128086988</v>
       </c>
       <c r="B31" t="n">
-        <v>91825</v>
+        <v>98478</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5467</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4158,10 +4159,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>316798</v>
+        <v>316819</v>
       </c>
       <c r="R31" t="n">
-        <v>6550432</v>
+        <v>6550452</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4208,22 +4209,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Bärljunbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Mosseljungbarrskog</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4241,10 +4227,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128086622</v>
+        <v>128086910</v>
       </c>
       <c r="B32" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4284,10 +4270,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>316857</v>
+        <v>316813</v>
       </c>
       <c r="R32" t="n">
-        <v>6550392</v>
+        <v>6550455</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4352,10 +4338,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128086988</v>
+        <v>128086622</v>
       </c>
       <c r="B33" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4395,10 +4381,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>316819</v>
+        <v>316857</v>
       </c>
       <c r="R33" t="n">
-        <v>6550452</v>
+        <v>6550392</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4463,42 +4449,41 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128086910</v>
+        <v>128085650</v>
       </c>
       <c r="B34" t="n">
-        <v>98470</v>
+        <v>91833</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>5467</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4506,10 +4491,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>316813</v>
+        <v>316798</v>
       </c>
       <c r="R34" t="n">
-        <v>6550455</v>
+        <v>6550432</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4556,7 +4541,22 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Mosseljungbarrskog</t>
+          <t>Bärljunbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4704,7 +4704,7 @@
         <v>128087681</v>
       </c>
       <c r="B36" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>128086358</v>
       </c>
       <c r="B37" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>128085583</v>
       </c>
       <c r="B38" t="n">
-        <v>91825</v>
+        <v>91833</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>128087374</v>
       </c>
       <c r="B39" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5159,10 +5159,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128086155</v>
+        <v>128087033</v>
       </c>
       <c r="B40" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5202,10 +5202,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>316836</v>
+        <v>316848</v>
       </c>
       <c r="R40" t="n">
-        <v>6550404</v>
+        <v>6550426</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5270,10 +5270,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128087074</v>
+        <v>128086155</v>
       </c>
       <c r="B41" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5313,10 +5313,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>316863</v>
+        <v>316836</v>
       </c>
       <c r="R41" t="n">
-        <v>6550433</v>
+        <v>6550404</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5381,10 +5381,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128087641</v>
+        <v>128087074</v>
       </c>
       <c r="B42" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5424,10 +5424,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>316887</v>
+        <v>316863</v>
       </c>
       <c r="R42" t="n">
-        <v>6550467</v>
+        <v>6550433</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5492,10 +5492,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128087033</v>
+        <v>128087641</v>
       </c>
       <c r="B43" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5535,10 +5535,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>316848</v>
+        <v>316887</v>
       </c>
       <c r="R43" t="n">
-        <v>6550426</v>
+        <v>6550467</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5606,7 +5606,7 @@
         <v>128086710</v>
       </c>
       <c r="B44" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         <v>128087244</v>
       </c>
       <c r="B45" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         <v>128086546</v>
       </c>
       <c r="B46" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5936,10 +5936,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128086825</v>
+        <v>128086406</v>
       </c>
       <c r="B47" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5979,10 +5979,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>316809</v>
+        <v>316836</v>
       </c>
       <c r="R47" t="n">
-        <v>6550455</v>
+        <v>6550393</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6047,10 +6047,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128086406</v>
+        <v>128086825</v>
       </c>
       <c r="B48" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6090,10 +6090,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>316836</v>
+        <v>316809</v>
       </c>
       <c r="R48" t="n">
-        <v>6550393</v>
+        <v>6550455</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6161,7 +6161,7 @@
         <v>128086451</v>
       </c>
       <c r="B49" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6272,7 +6272,7 @@
         <v>128085493</v>
       </c>
       <c r="B50" t="n">
-        <v>91372</v>
+        <v>91380</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6401,7 +6401,7 @@
         <v>128084972</v>
       </c>
       <c r="B51" t="n">
-        <v>79647</v>
+        <v>79650</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6523,52 +6523,54 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128085763</v>
+        <v>128084916</v>
       </c>
       <c r="B52" t="n">
-        <v>91825</v>
+        <v>8450</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5467</v>
+        <v>106545</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Svarttjärnen S/V., Dls</t>
+          <t>Ormetjärn S/V., Dls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>316919</v>
+        <v>317037</v>
       </c>
       <c r="R52" t="n">
-        <v>6550474</v>
+        <v>6550398</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6615,7 +6617,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Bärljunbarrskog</t>
+          <t>Bärljungbarrskog</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
@@ -6648,7 +6650,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128084916</v>
+        <v>128085525</v>
       </c>
       <c r="B53" t="n">
         <v>8450</v>
@@ -6688,14 +6690,14 @@
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Ormetjärn S/V., Dls</t>
+          <t>Svarttjärnen S., Dls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>317037</v>
+        <v>316911</v>
       </c>
       <c r="R53" t="n">
-        <v>6550398</v>
+        <v>6550369</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6757,7 +6759,7 @@
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Gadd # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6775,54 +6777,53 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128085525</v>
+        <v>128086997</v>
       </c>
       <c r="B54" t="n">
-        <v>8450</v>
+        <v>98478</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Svarttjärnen S., Dls</t>
+          <t>Svarttjärnen S/V., Dls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>316911</v>
+        <v>316832</v>
       </c>
       <c r="R54" t="n">
-        <v>6550369</v>
+        <v>6550424</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6869,22 +6870,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Gadd # Pinus sylvestris</t>
+          <t>Mosseljungbarrskog</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6902,10 +6888,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128086997</v>
+        <v>128086772</v>
       </c>
       <c r="B55" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6945,10 +6931,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>316832</v>
+        <v>316809</v>
       </c>
       <c r="R55" t="n">
-        <v>6550424</v>
+        <v>6550451</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -7013,42 +6999,41 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128086772</v>
+        <v>128085763</v>
       </c>
       <c r="B56" t="n">
-        <v>98470</v>
+        <v>91833</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>5467</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7056,10 +7041,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>316809</v>
+        <v>316919</v>
       </c>
       <c r="R56" t="n">
-        <v>6550451</v>
+        <v>6550474</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7106,7 +7091,22 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Mosseljungbarrskog</t>
+          <t>Bärljunbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7254,7 +7254,7 @@
         <v>128086654</v>
       </c>
       <c r="B58" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7365,7 +7365,7 @@
         <v>128086469</v>
       </c>
       <c r="B59" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7476,7 +7476,7 @@
         <v>128086692</v>
       </c>
       <c r="B60" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         <v>128085294</v>
       </c>
       <c r="B61" t="n">
-        <v>92835</v>
+        <v>92843</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>128087465</v>
       </c>
       <c r="B62" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7823,7 +7823,7 @@
         <v>128086718</v>
       </c>
       <c r="B63" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7931,54 +7931,53 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128084637</v>
+        <v>128087411</v>
       </c>
       <c r="B64" t="n">
-        <v>8450</v>
+        <v>98478</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Svarttjärnen O., Dls</t>
+          <t>Svarttjärnen S/V., Dls</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>316984</v>
+        <v>316858</v>
       </c>
       <c r="R64" t="n">
-        <v>6550597</v>
+        <v>6550464</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -8025,22 +8024,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Gadd # Pinus sylvestris</t>
+          <t>Mosseljungbarrskog</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8058,10 +8042,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128087506</v>
+        <v>128087606</v>
       </c>
       <c r="B65" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8101,10 +8085,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>316865</v>
+        <v>316877</v>
       </c>
       <c r="R65" t="n">
-        <v>6550469</v>
+        <v>6550456</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -8169,10 +8153,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128087411</v>
+        <v>128087506</v>
       </c>
       <c r="B66" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8212,10 +8196,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>316858</v>
+        <v>316865</v>
       </c>
       <c r="R66" t="n">
-        <v>6550464</v>
+        <v>6550469</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -8280,53 +8264,54 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128087606</v>
+        <v>128084637</v>
       </c>
       <c r="B67" t="n">
-        <v>98470</v>
+        <v>8450</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Svarttjärnen S/V., Dls</t>
+          <t>Svarttjärnen O., Dls</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>316877</v>
+        <v>316984</v>
       </c>
       <c r="R67" t="n">
-        <v>6550456</v>
+        <v>6550597</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -8373,7 +8358,22 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Mosseljungbarrskog</t>
+          <t>Bärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Gadd # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8394,7 +8394,7 @@
         <v>128087295</v>
       </c>
       <c r="B68" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8502,40 +8502,36 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128086518</v>
+        <v>128085956</v>
       </c>
       <c r="B69" t="n">
-        <v>98470</v>
+        <v>97355</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
@@ -8545,10 +8541,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>316852</v>
+        <v>316904</v>
       </c>
       <c r="R69" t="n">
-        <v>6550388</v>
+        <v>6550464</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8595,7 +8591,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Mosseljungbarrskog</t>
+          <t>Bärljungbarrskog</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8613,36 +8609,40 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128085956</v>
+        <v>128086518</v>
       </c>
       <c r="B70" t="n">
-        <v>97347</v>
+        <v>98478</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
@@ -8652,10 +8652,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>316904</v>
+        <v>316852</v>
       </c>
       <c r="R70" t="n">
-        <v>6550464</v>
+        <v>6550388</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8702,7 +8702,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
+          <t>Mosseljungbarrskog</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>

--- a/artfynd/A 40826-2025 artfynd.xlsx
+++ b/artfynd/A 40826-2025 artfynd.xlsx
@@ -4116,10 +4116,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128086988</v>
+        <v>128086622</v>
       </c>
       <c r="B31" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4159,10 +4159,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>316819</v>
+        <v>316857</v>
       </c>
       <c r="R31" t="n">
-        <v>6550452</v>
+        <v>6550392</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4227,10 +4227,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128086910</v>
+        <v>128086988</v>
       </c>
       <c r="B32" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4270,10 +4270,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>316813</v>
+        <v>316819</v>
       </c>
       <c r="R32" t="n">
-        <v>6550455</v>
+        <v>6550452</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4338,10 +4338,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128086622</v>
+        <v>128086910</v>
       </c>
       <c r="B33" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4381,10 +4381,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>316857</v>
+        <v>316813</v>
       </c>
       <c r="R33" t="n">
-        <v>6550392</v>
+        <v>6550455</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4452,7 +4452,7 @@
         <v>128085650</v>
       </c>
       <c r="B34" t="n">
-        <v>91833</v>
+        <v>91925</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         <v>128087681</v>
       </c>
       <c r="B36" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>128086358</v>
       </c>
       <c r="B37" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>128085583</v>
       </c>
       <c r="B38" t="n">
-        <v>91833</v>
+        <v>91925</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>128087374</v>
       </c>
       <c r="B39" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5159,10 +5159,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128087033</v>
+        <v>128086155</v>
       </c>
       <c r="B40" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5202,10 +5202,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>316848</v>
+        <v>316836</v>
       </c>
       <c r="R40" t="n">
-        <v>6550426</v>
+        <v>6550404</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5270,10 +5270,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128086155</v>
+        <v>128087074</v>
       </c>
       <c r="B41" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5313,10 +5313,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>316836</v>
+        <v>316863</v>
       </c>
       <c r="R41" t="n">
-        <v>6550404</v>
+        <v>6550433</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5381,10 +5381,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128087074</v>
+        <v>128087641</v>
       </c>
       <c r="B42" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5424,10 +5424,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>316863</v>
+        <v>316887</v>
       </c>
       <c r="R42" t="n">
-        <v>6550433</v>
+        <v>6550467</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5492,10 +5492,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128087641</v>
+        <v>128087033</v>
       </c>
       <c r="B43" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5535,10 +5535,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>316887</v>
+        <v>316848</v>
       </c>
       <c r="R43" t="n">
-        <v>6550467</v>
+        <v>6550426</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5606,7 +5606,7 @@
         <v>128086710</v>
       </c>
       <c r="B44" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         <v>128087244</v>
       </c>
       <c r="B45" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         <v>128086546</v>
       </c>
       <c r="B46" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5936,10 +5936,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128086406</v>
+        <v>128086825</v>
       </c>
       <c r="B47" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5979,10 +5979,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>316836</v>
+        <v>316809</v>
       </c>
       <c r="R47" t="n">
-        <v>6550393</v>
+        <v>6550455</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6047,10 +6047,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128086825</v>
+        <v>128086406</v>
       </c>
       <c r="B48" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6090,10 +6090,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>316809</v>
+        <v>316836</v>
       </c>
       <c r="R48" t="n">
-        <v>6550455</v>
+        <v>6550393</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6161,7 +6161,7 @@
         <v>128086451</v>
       </c>
       <c r="B49" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6272,7 +6272,7 @@
         <v>128085493</v>
       </c>
       <c r="B50" t="n">
-        <v>91380</v>
+        <v>91472</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6401,7 +6401,7 @@
         <v>128084972</v>
       </c>
       <c r="B51" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6523,54 +6523,52 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128084916</v>
+        <v>128085763</v>
       </c>
       <c r="B52" t="n">
-        <v>8450</v>
+        <v>91925</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>5467</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Ormetjärn S/V., Dls</t>
+          <t>Svarttjärnen S/V., Dls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>317037</v>
+        <v>316919</v>
       </c>
       <c r="R52" t="n">
-        <v>6550398</v>
+        <v>6550474</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6617,7 +6615,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
+          <t>Bärljunbarrskog</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
@@ -6650,7 +6648,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128085525</v>
+        <v>128084916</v>
       </c>
       <c r="B53" t="n">
         <v>8450</v>
@@ -6690,14 +6688,14 @@
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Svarttjärnen S., Dls</t>
+          <t>Ormetjärn S/V., Dls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>316911</v>
+        <v>317037</v>
       </c>
       <c r="R53" t="n">
-        <v>6550369</v>
+        <v>6550398</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6759,7 +6757,7 @@
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Gadd # Pinus sylvestris</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6777,53 +6775,54 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128086997</v>
+        <v>128085525</v>
       </c>
       <c r="B54" t="n">
-        <v>98478</v>
+        <v>8450</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Svarttjärnen S/V., Dls</t>
+          <t>Svarttjärnen S., Dls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>316832</v>
+        <v>316911</v>
       </c>
       <c r="R54" t="n">
-        <v>6550424</v>
+        <v>6550369</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6870,7 +6869,22 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Mosseljungbarrskog</t>
+          <t>Bärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Gadd # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6888,10 +6902,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128086772</v>
+        <v>128086997</v>
       </c>
       <c r="B55" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6931,10 +6945,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>316809</v>
+        <v>316832</v>
       </c>
       <c r="R55" t="n">
-        <v>6550451</v>
+        <v>6550424</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6999,41 +7013,42 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128085763</v>
+        <v>128086772</v>
       </c>
       <c r="B56" t="n">
-        <v>91833</v>
+        <v>98571</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5467</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7041,10 +7056,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>316919</v>
+        <v>316809</v>
       </c>
       <c r="R56" t="n">
-        <v>6550474</v>
+        <v>6550451</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7091,22 +7106,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Bärljunbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Mosseljungbarrskog</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7254,7 +7254,7 @@
         <v>128086654</v>
       </c>
       <c r="B58" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7365,7 +7365,7 @@
         <v>128086469</v>
       </c>
       <c r="B59" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7476,7 +7476,7 @@
         <v>128086692</v>
       </c>
       <c r="B60" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         <v>128085294</v>
       </c>
       <c r="B61" t="n">
-        <v>92843</v>
+        <v>92935</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>128087465</v>
       </c>
       <c r="B62" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7823,7 +7823,7 @@
         <v>128086718</v>
       </c>
       <c r="B63" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7931,53 +7931,54 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128087411</v>
+        <v>128084637</v>
       </c>
       <c r="B64" t="n">
-        <v>98478</v>
+        <v>8450</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Svarttjärnen S/V., Dls</t>
+          <t>Svarttjärnen O., Dls</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>316858</v>
+        <v>316984</v>
       </c>
       <c r="R64" t="n">
-        <v>6550464</v>
+        <v>6550597</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -8024,7 +8025,22 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Mosseljungbarrskog</t>
+          <t>Bärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Gadd # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8042,10 +8058,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128087606</v>
+        <v>128087506</v>
       </c>
       <c r="B65" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8085,10 +8101,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>316877</v>
+        <v>316865</v>
       </c>
       <c r="R65" t="n">
-        <v>6550456</v>
+        <v>6550469</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -8153,10 +8169,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128087506</v>
+        <v>128087411</v>
       </c>
       <c r="B66" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8196,10 +8212,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>316865</v>
+        <v>316858</v>
       </c>
       <c r="R66" t="n">
-        <v>6550469</v>
+        <v>6550464</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -8264,54 +8280,53 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128084637</v>
+        <v>128087606</v>
       </c>
       <c r="B67" t="n">
-        <v>8450</v>
+        <v>98571</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Svarttjärnen O., Dls</t>
+          <t>Svarttjärnen S/V., Dls</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>316984</v>
+        <v>316877</v>
       </c>
       <c r="R67" t="n">
-        <v>6550597</v>
+        <v>6550456</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -8358,22 +8373,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Gadd # Pinus sylvestris</t>
+          <t>Mosseljungbarrskog</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8394,7 +8394,7 @@
         <v>128087295</v>
       </c>
       <c r="B68" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8502,36 +8502,40 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128085956</v>
+        <v>128086518</v>
       </c>
       <c r="B69" t="n">
-        <v>97355</v>
+        <v>98571</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
@@ -8541,10 +8545,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>316904</v>
+        <v>316852</v>
       </c>
       <c r="R69" t="n">
-        <v>6550464</v>
+        <v>6550388</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8591,7 +8595,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
+          <t>Mosseljungbarrskog</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8609,40 +8613,36 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128086518</v>
+        <v>128085956</v>
       </c>
       <c r="B70" t="n">
-        <v>98478</v>
+        <v>97448</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
@@ -8652,10 +8652,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>316852</v>
+        <v>316904</v>
       </c>
       <c r="R70" t="n">
-        <v>6550388</v>
+        <v>6550464</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8702,7 +8702,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>Mosseljungbarrskog</t>
+          <t>Bärljungbarrskog</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>

--- a/artfynd/A 40826-2025 artfynd.xlsx
+++ b/artfynd/A 40826-2025 artfynd.xlsx
@@ -4116,42 +4116,41 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128086622</v>
+        <v>128085650</v>
       </c>
       <c r="B31" t="n">
-        <v>98571</v>
+        <v>91925</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>5467</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4159,10 +4158,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>316857</v>
+        <v>316798</v>
       </c>
       <c r="R31" t="n">
-        <v>6550392</v>
+        <v>6550432</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4209,7 +4208,22 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Mosseljungbarrskog</t>
+          <t>Bärljunbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4227,7 +4241,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128086988</v>
+        <v>128086622</v>
       </c>
       <c r="B32" t="n">
         <v>98571</v>
@@ -4270,10 +4284,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>316819</v>
+        <v>316857</v>
       </c>
       <c r="R32" t="n">
-        <v>6550452</v>
+        <v>6550392</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4338,7 +4352,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128086910</v>
+        <v>128086988</v>
       </c>
       <c r="B33" t="n">
         <v>98571</v>
@@ -4381,10 +4395,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>316813</v>
+        <v>316819</v>
       </c>
       <c r="R33" t="n">
-        <v>6550455</v>
+        <v>6550452</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4449,41 +4463,42 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128085650</v>
+        <v>128086910</v>
       </c>
       <c r="B34" t="n">
-        <v>91925</v>
+        <v>98571</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5467</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4491,10 +4506,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>316798</v>
+        <v>316813</v>
       </c>
       <c r="R34" t="n">
-        <v>6550432</v>
+        <v>6550455</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4541,22 +4556,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Bärljunbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Mosseljungbarrskog</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4574,54 +4574,53 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128084900</v>
+        <v>128087681</v>
       </c>
       <c r="B35" t="n">
-        <v>8450</v>
+        <v>98571</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Ormetjärn V., Dls</t>
+          <t>Svarttjärnen S., Dls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>317022</v>
+        <v>316929</v>
       </c>
       <c r="R35" t="n">
-        <v>6550471</v>
+        <v>6550454</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4668,22 +4667,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Mosseljungbarrskog</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4701,7 +4685,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128087681</v>
+        <v>128086358</v>
       </c>
       <c r="B36" t="n">
         <v>98571</v>
@@ -4740,14 +4724,14 @@
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Svarttjärnen S., Dls</t>
+          <t>Svarttjärnen S/V., Dls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>316929</v>
+        <v>316837</v>
       </c>
       <c r="R36" t="n">
-        <v>6550454</v>
+        <v>6550397</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4812,53 +4796,54 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128086358</v>
+        <v>128084900</v>
       </c>
       <c r="B37" t="n">
-        <v>98571</v>
+        <v>8450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Svarttjärnen S/V., Dls</t>
+          <t>Ormetjärn V., Dls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>316837</v>
+        <v>317022</v>
       </c>
       <c r="R37" t="n">
-        <v>6550397</v>
+        <v>6550471</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4905,7 +4890,22 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Mosseljungbarrskog</t>
+          <t>Bärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -6523,52 +6523,54 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128085763</v>
+        <v>128084916</v>
       </c>
       <c r="B52" t="n">
-        <v>91925</v>
+        <v>8450</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5467</v>
+        <v>106545</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Svarttjärnen S/V., Dls</t>
+          <t>Ormetjärn S/V., Dls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>316919</v>
+        <v>317037</v>
       </c>
       <c r="R52" t="n">
-        <v>6550474</v>
+        <v>6550398</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6615,7 +6617,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Bärljunbarrskog</t>
+          <t>Bärljungbarrskog</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
@@ -6648,7 +6650,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128084916</v>
+        <v>128085525</v>
       </c>
       <c r="B53" t="n">
         <v>8450</v>
@@ -6688,14 +6690,14 @@
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Ormetjärn S/V., Dls</t>
+          <t>Svarttjärnen S., Dls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>317037</v>
+        <v>316911</v>
       </c>
       <c r="R53" t="n">
-        <v>6550398</v>
+        <v>6550369</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6757,7 +6759,7 @@
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Gadd # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6775,54 +6777,53 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128085525</v>
+        <v>128086997</v>
       </c>
       <c r="B54" t="n">
-        <v>8450</v>
+        <v>98571</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Svarttjärnen S., Dls</t>
+          <t>Svarttjärnen S/V., Dls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>316911</v>
+        <v>316832</v>
       </c>
       <c r="R54" t="n">
-        <v>6550369</v>
+        <v>6550424</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6869,22 +6870,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Gadd # Pinus sylvestris</t>
+          <t>Mosseljungbarrskog</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6902,7 +6888,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128086997</v>
+        <v>128086772</v>
       </c>
       <c r="B55" t="n">
         <v>98571</v>
@@ -6945,10 +6931,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>316832</v>
+        <v>316809</v>
       </c>
       <c r="R55" t="n">
-        <v>6550424</v>
+        <v>6550451</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -7013,42 +6999,41 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128086772</v>
+        <v>128085763</v>
       </c>
       <c r="B56" t="n">
-        <v>98571</v>
+        <v>91925</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>5467</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7056,10 +7041,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>316809</v>
+        <v>316919</v>
       </c>
       <c r="R56" t="n">
-        <v>6550451</v>
+        <v>6550474</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7106,7 +7091,22 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Mosseljungbarrskog</t>
+          <t>Bärljunbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7584,52 +7584,53 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128085294</v>
+        <v>128087465</v>
       </c>
       <c r="B61" t="n">
-        <v>92935</v>
+        <v>98571</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2079</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Ormetjärn S/V., Dls</t>
+          <t>Svarttjärnen S/V., Dls</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>317041</v>
+        <v>316860</v>
       </c>
       <c r="R61" t="n">
-        <v>6550370</v>
+        <v>6550480</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7676,22 +7677,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Bärljungtallskog</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Mosseljungbarrskog</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7709,7 +7695,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128087465</v>
+        <v>128086718</v>
       </c>
       <c r="B62" t="n">
         <v>98571</v>
@@ -7752,10 +7738,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>316860</v>
+        <v>316821</v>
       </c>
       <c r="R62" t="n">
-        <v>6550480</v>
+        <v>6550398</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7820,53 +7806,52 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128086718</v>
+        <v>128085294</v>
       </c>
       <c r="B63" t="n">
-        <v>98571</v>
+        <v>92935</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Svarttjärnen S/V., Dls</t>
+          <t>Ormetjärn S/V., Dls</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>316821</v>
+        <v>317041</v>
       </c>
       <c r="R63" t="n">
-        <v>6550398</v>
+        <v>6550370</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7913,7 +7898,22 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>Mosseljungbarrskog</t>
+          <t>Bärljungtallskog</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>

--- a/artfynd/A 40826-2025 artfynd.xlsx
+++ b/artfynd/A 40826-2025 artfynd.xlsx
@@ -4241,7 +4241,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128086622</v>
+        <v>128086988</v>
       </c>
       <c r="B32" t="n">
         <v>98571</v>
@@ -4284,10 +4284,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>316857</v>
+        <v>316819</v>
       </c>
       <c r="R32" t="n">
-        <v>6550392</v>
+        <v>6550452</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4352,7 +4352,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128086988</v>
+        <v>128086622</v>
       </c>
       <c r="B33" t="n">
         <v>98571</v>
@@ -4395,10 +4395,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>316819</v>
+        <v>316857</v>
       </c>
       <c r="R33" t="n">
-        <v>6550452</v>
+        <v>6550392</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4574,53 +4574,54 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128087681</v>
+        <v>128084900</v>
       </c>
       <c r="B35" t="n">
-        <v>98571</v>
+        <v>8450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Svarttjärnen S., Dls</t>
+          <t>Ormetjärn V., Dls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>316929</v>
+        <v>317022</v>
       </c>
       <c r="R35" t="n">
-        <v>6550454</v>
+        <v>6550471</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4667,7 +4668,22 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Mosseljungbarrskog</t>
+          <t>Bärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4685,7 +4701,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128086358</v>
+        <v>128087681</v>
       </c>
       <c r="B36" t="n">
         <v>98571</v>
@@ -4724,14 +4740,14 @@
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Svarttjärnen S/V., Dls</t>
+          <t>Svarttjärnen S., Dls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>316837</v>
+        <v>316929</v>
       </c>
       <c r="R36" t="n">
-        <v>6550397</v>
+        <v>6550454</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4796,54 +4812,53 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128084900</v>
+        <v>128086358</v>
       </c>
       <c r="B37" t="n">
-        <v>8450</v>
+        <v>98571</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Ormetjärn V., Dls</t>
+          <t>Svarttjärnen S/V., Dls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>317022</v>
+        <v>316837</v>
       </c>
       <c r="R37" t="n">
-        <v>6550471</v>
+        <v>6550397</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4890,22 +4905,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Mosseljungbarrskog</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -6523,54 +6523,52 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128084916</v>
+        <v>128085763</v>
       </c>
       <c r="B52" t="n">
-        <v>8450</v>
+        <v>91925</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>5467</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Ormetjärn S/V., Dls</t>
+          <t>Svarttjärnen S/V., Dls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>317037</v>
+        <v>316919</v>
       </c>
       <c r="R52" t="n">
-        <v>6550398</v>
+        <v>6550474</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6617,7 +6615,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
+          <t>Bärljunbarrskog</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
@@ -6650,54 +6648,53 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128085525</v>
+        <v>128086997</v>
       </c>
       <c r="B53" t="n">
-        <v>8450</v>
+        <v>98571</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Svarttjärnen S., Dls</t>
+          <t>Svarttjärnen S/V., Dls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>316911</v>
+        <v>316832</v>
       </c>
       <c r="R53" t="n">
-        <v>6550369</v>
+        <v>6550424</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6744,22 +6741,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Gadd # Pinus sylvestris</t>
+          <t>Mosseljungbarrskog</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6777,7 +6759,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128086997</v>
+        <v>128086772</v>
       </c>
       <c r="B54" t="n">
         <v>98571</v>
@@ -6820,10 +6802,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>316832</v>
+        <v>316809</v>
       </c>
       <c r="R54" t="n">
-        <v>6550424</v>
+        <v>6550451</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6888,53 +6870,54 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128086772</v>
+        <v>128084916</v>
       </c>
       <c r="B55" t="n">
-        <v>98571</v>
+        <v>8450</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Svarttjärnen S/V., Dls</t>
+          <t>Ormetjärn S/V., Dls</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>316809</v>
+        <v>317037</v>
       </c>
       <c r="R55" t="n">
-        <v>6550451</v>
+        <v>6550398</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6981,7 +6964,22 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Mosseljungbarrskog</t>
+          <t>Bärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6999,52 +6997,54 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128085763</v>
+        <v>128085525</v>
       </c>
       <c r="B56" t="n">
-        <v>91925</v>
+        <v>8450</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5467</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Svarttjärnen S/V., Dls</t>
+          <t>Svarttjärnen S., Dls</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>316919</v>
+        <v>316911</v>
       </c>
       <c r="R56" t="n">
-        <v>6550474</v>
+        <v>6550369</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Bärljunbarrskog</t>
+          <t>Bärljungbarrskog</t>
         </is>
       </c>
       <c r="AJ56" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Gadd # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7584,53 +7584,52 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128087465</v>
+        <v>128085294</v>
       </c>
       <c r="B61" t="n">
-        <v>98571</v>
+        <v>92935</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Svarttjärnen S/V., Dls</t>
+          <t>Ormetjärn S/V., Dls</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>316860</v>
+        <v>317041</v>
       </c>
       <c r="R61" t="n">
-        <v>6550480</v>
+        <v>6550370</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7677,7 +7676,22 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Mosseljungbarrskog</t>
+          <t>Bärljungtallskog</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7695,7 +7709,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128086718</v>
+        <v>128087465</v>
       </c>
       <c r="B62" t="n">
         <v>98571</v>
@@ -7738,10 +7752,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>316821</v>
+        <v>316860</v>
       </c>
       <c r="R62" t="n">
-        <v>6550398</v>
+        <v>6550480</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7806,52 +7820,53 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128085294</v>
+        <v>128086718</v>
       </c>
       <c r="B63" t="n">
-        <v>92935</v>
+        <v>98571</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2079</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Ormetjärn S/V., Dls</t>
+          <t>Svarttjärnen S/V., Dls</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>317041</v>
+        <v>316821</v>
       </c>
       <c r="R63" t="n">
-        <v>6550370</v>
+        <v>6550398</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7898,22 +7913,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>Bärljungtallskog</t>
-        </is>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Mosseljungbarrskog</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8502,40 +8502,36 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128086518</v>
+        <v>128085956</v>
       </c>
       <c r="B69" t="n">
-        <v>98571</v>
+        <v>97448</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
@@ -8545,10 +8541,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>316852</v>
+        <v>316904</v>
       </c>
       <c r="R69" t="n">
-        <v>6550388</v>
+        <v>6550464</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8595,7 +8591,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Mosseljungbarrskog</t>
+          <t>Bärljungbarrskog</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8613,36 +8609,40 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128085956</v>
+        <v>128086518</v>
       </c>
       <c r="B70" t="n">
-        <v>97448</v>
+        <v>98571</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
@@ -8652,10 +8652,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>316904</v>
+        <v>316852</v>
       </c>
       <c r="R70" t="n">
-        <v>6550464</v>
+        <v>6550388</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8702,7 +8702,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
+          <t>Mosseljungbarrskog</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>

--- a/artfynd/A 40826-2025 artfynd.xlsx
+++ b/artfynd/A 40826-2025 artfynd.xlsx
@@ -4241,7 +4241,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128086988</v>
+        <v>128086622</v>
       </c>
       <c r="B32" t="n">
         <v>98571</v>
@@ -4284,10 +4284,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>316819</v>
+        <v>316857</v>
       </c>
       <c r="R32" t="n">
-        <v>6550452</v>
+        <v>6550392</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4352,7 +4352,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128086622</v>
+        <v>128086988</v>
       </c>
       <c r="B33" t="n">
         <v>98571</v>
@@ -4395,10 +4395,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>316857</v>
+        <v>316819</v>
       </c>
       <c r="R33" t="n">
-        <v>6550392</v>
+        <v>6550452</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -8502,36 +8502,40 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128085956</v>
+        <v>128086518</v>
       </c>
       <c r="B69" t="n">
-        <v>97448</v>
+        <v>98571</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
@@ -8541,10 +8545,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>316904</v>
+        <v>316852</v>
       </c>
       <c r="R69" t="n">
-        <v>6550464</v>
+        <v>6550388</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8591,7 +8595,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
+          <t>Mosseljungbarrskog</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8609,40 +8613,36 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128086518</v>
+        <v>128085956</v>
       </c>
       <c r="B70" t="n">
-        <v>98571</v>
+        <v>97448</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
@@ -8652,10 +8652,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>316852</v>
+        <v>316904</v>
       </c>
       <c r="R70" t="n">
-        <v>6550388</v>
+        <v>6550464</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8702,7 +8702,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>Mosseljungbarrskog</t>
+          <t>Bärljungbarrskog</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>

--- a/artfynd/A 40826-2025 artfynd.xlsx
+++ b/artfynd/A 40826-2025 artfynd.xlsx
@@ -4119,7 +4119,7 @@
         <v>128085650</v>
       </c>
       <c r="B31" t="n">
-        <v>91925</v>
+        <v>91937</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         <v>128086622</v>
       </c>
       <c r="B32" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>128086988</v>
       </c>
       <c r="B33" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         <v>128086910</v>
       </c>
       <c r="B34" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         <v>128087681</v>
       </c>
       <c r="B36" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>128086358</v>
       </c>
       <c r="B37" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>128085583</v>
       </c>
       <c r="B38" t="n">
-        <v>91925</v>
+        <v>91937</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>128087374</v>
       </c>
       <c r="B39" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         <v>128086155</v>
       </c>
       <c r="B40" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5270,10 +5270,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128087074</v>
+        <v>128087641</v>
       </c>
       <c r="B41" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5313,10 +5313,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>316863</v>
+        <v>316887</v>
       </c>
       <c r="R41" t="n">
-        <v>6550433</v>
+        <v>6550467</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5381,10 +5381,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128087641</v>
+        <v>128087033</v>
       </c>
       <c r="B42" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5424,10 +5424,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>316887</v>
+        <v>316848</v>
       </c>
       <c r="R42" t="n">
-        <v>6550467</v>
+        <v>6550426</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5492,10 +5492,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128087033</v>
+        <v>128087074</v>
       </c>
       <c r="B43" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5535,10 +5535,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>316848</v>
+        <v>316863</v>
       </c>
       <c r="R43" t="n">
-        <v>6550426</v>
+        <v>6550433</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5606,7 +5606,7 @@
         <v>128086710</v>
       </c>
       <c r="B44" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         <v>128087244</v>
       </c>
       <c r="B45" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         <v>128086546</v>
       </c>
       <c r="B46" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5936,10 +5936,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128086825</v>
+        <v>128086406</v>
       </c>
       <c r="B47" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5979,10 +5979,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>316809</v>
+        <v>316836</v>
       </c>
       <c r="R47" t="n">
-        <v>6550455</v>
+        <v>6550393</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6047,10 +6047,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128086406</v>
+        <v>128086451</v>
       </c>
       <c r="B48" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>316836</v>
+        <v>316834</v>
       </c>
       <c r="R48" t="n">
         <v>6550393</v>
@@ -6158,10 +6158,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128086451</v>
+        <v>128086825</v>
       </c>
       <c r="B49" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>316834</v>
+        <v>316809</v>
       </c>
       <c r="R49" t="n">
-        <v>6550393</v>
+        <v>6550455</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6272,7 +6272,7 @@
         <v>128085493</v>
       </c>
       <c r="B50" t="n">
-        <v>91472</v>
+        <v>91484</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6401,7 +6401,7 @@
         <v>128084972</v>
       </c>
       <c r="B51" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6523,52 +6523,54 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128085763</v>
+        <v>128084916</v>
       </c>
       <c r="B52" t="n">
-        <v>91925</v>
+        <v>8450</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5467</v>
+        <v>106545</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Svarttjärnen S/V., Dls</t>
+          <t>Ormetjärn S/V., Dls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>316919</v>
+        <v>317037</v>
       </c>
       <c r="R52" t="n">
-        <v>6550474</v>
+        <v>6550398</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6615,7 +6617,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Bärljunbarrskog</t>
+          <t>Bärljungbarrskog</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
@@ -6648,53 +6650,54 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128086997</v>
+        <v>128085525</v>
       </c>
       <c r="B53" t="n">
-        <v>98571</v>
+        <v>8450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Svarttjärnen S/V., Dls</t>
+          <t>Svarttjärnen S., Dls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>316832</v>
+        <v>316911</v>
       </c>
       <c r="R53" t="n">
-        <v>6550424</v>
+        <v>6550369</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6741,7 +6744,22 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>Mosseljungbarrskog</t>
+          <t>Bärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Gadd # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6759,42 +6777,41 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128086772</v>
+        <v>128085763</v>
       </c>
       <c r="B54" t="n">
-        <v>98571</v>
+        <v>91937</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>5467</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6802,10 +6819,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>316809</v>
+        <v>316919</v>
       </c>
       <c r="R54" t="n">
-        <v>6550451</v>
+        <v>6550474</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6852,7 +6869,22 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Mosseljungbarrskog</t>
+          <t>Bärljunbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6870,54 +6902,53 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128084916</v>
+        <v>128086997</v>
       </c>
       <c r="B55" t="n">
-        <v>8450</v>
+        <v>98585</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Ormetjärn S/V., Dls</t>
+          <t>Svarttjärnen S/V., Dls</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>317037</v>
+        <v>316832</v>
       </c>
       <c r="R55" t="n">
-        <v>6550398</v>
+        <v>6550424</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6964,22 +6995,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Mosseljungbarrskog</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6997,54 +7013,53 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128085525</v>
+        <v>128086772</v>
       </c>
       <c r="B56" t="n">
-        <v>8450</v>
+        <v>98585</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Svarttjärnen S., Dls</t>
+          <t>Svarttjärnen S/V., Dls</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>316911</v>
+        <v>316809</v>
       </c>
       <c r="R56" t="n">
-        <v>6550369</v>
+        <v>6550451</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7091,22 +7106,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Gadd # Pinus sylvestris</t>
+          <t>Mosseljungbarrskog</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7254,7 +7254,7 @@
         <v>128086654</v>
       </c>
       <c r="B58" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7365,7 +7365,7 @@
         <v>128086469</v>
       </c>
       <c r="B59" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7476,7 +7476,7 @@
         <v>128086692</v>
       </c>
       <c r="B60" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         <v>128085294</v>
       </c>
       <c r="B61" t="n">
-        <v>92935</v>
+        <v>92947</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>128087465</v>
       </c>
       <c r="B62" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7823,7 +7823,7 @@
         <v>128086718</v>
       </c>
       <c r="B63" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8061,7 +8061,7 @@
         <v>128087506</v>
       </c>
       <c r="B65" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8172,7 +8172,7 @@
         <v>128087411</v>
       </c>
       <c r="B66" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>128087606</v>
       </c>
       <c r="B67" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8394,7 +8394,7 @@
         <v>128087295</v>
       </c>
       <c r="B68" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         <v>128086518</v>
       </c>
       <c r="B69" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8616,7 +8616,7 @@
         <v>128085956</v>
       </c>
       <c r="B70" t="n">
-        <v>97448</v>
+        <v>97460</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 40826-2025 artfynd.xlsx
+++ b/artfynd/A 40826-2025 artfynd.xlsx
@@ -4116,41 +4116,42 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128085650</v>
+        <v>128086622</v>
       </c>
       <c r="B31" t="n">
-        <v>91937</v>
+        <v>98585</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5467</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4158,10 +4159,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>316798</v>
+        <v>316857</v>
       </c>
       <c r="R31" t="n">
-        <v>6550432</v>
+        <v>6550392</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4208,22 +4209,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Bärljunbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Mosseljungbarrskog</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4241,7 +4227,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128086622</v>
+        <v>128086988</v>
       </c>
       <c r="B32" t="n">
         <v>98585</v>
@@ -4284,10 +4270,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>316857</v>
+        <v>316819</v>
       </c>
       <c r="R32" t="n">
-        <v>6550392</v>
+        <v>6550452</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4352,42 +4338,41 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128086988</v>
+        <v>128085650</v>
       </c>
       <c r="B33" t="n">
-        <v>98585</v>
+        <v>91937</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>5467</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4395,10 +4380,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>316819</v>
+        <v>316798</v>
       </c>
       <c r="R33" t="n">
-        <v>6550452</v>
+        <v>6550432</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4445,7 +4430,22 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Mosseljungbarrskog</t>
+          <t>Bärljunbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5936,7 +5936,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128086406</v>
+        <v>128086825</v>
       </c>
       <c r="B47" t="n">
         <v>98585</v>
@@ -5979,10 +5979,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>316836</v>
+        <v>316809</v>
       </c>
       <c r="R47" t="n">
-        <v>6550393</v>
+        <v>6550455</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6047,7 +6047,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128086451</v>
+        <v>128086406</v>
       </c>
       <c r="B48" t="n">
         <v>98585</v>
@@ -6090,7 +6090,7 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>316834</v>
+        <v>316836</v>
       </c>
       <c r="R48" t="n">
         <v>6550393</v>
@@ -6158,7 +6158,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128086825</v>
+        <v>128086451</v>
       </c>
       <c r="B49" t="n">
         <v>98585</v>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>316809</v>
+        <v>316834</v>
       </c>
       <c r="R49" t="n">
-        <v>6550455</v>
+        <v>6550393</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>

--- a/artfynd/A 40826-2025 artfynd.xlsx
+++ b/artfynd/A 40826-2025 artfynd.xlsx
@@ -4116,10 +4116,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128086622</v>
+        <v>128086988</v>
       </c>
       <c r="B31" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4159,10 +4159,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>316857</v>
+        <v>316819</v>
       </c>
       <c r="R31" t="n">
-        <v>6550392</v>
+        <v>6550452</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4227,10 +4227,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128086988</v>
+        <v>128086622</v>
       </c>
       <c r="B32" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4270,10 +4270,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>316819</v>
+        <v>316857</v>
       </c>
       <c r="R32" t="n">
-        <v>6550452</v>
+        <v>6550392</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4341,7 +4341,7 @@
         <v>128085650</v>
       </c>
       <c r="B33" t="n">
-        <v>91937</v>
+        <v>91939</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         <v>128086910</v>
       </c>
       <c r="B34" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4574,54 +4574,53 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128084900</v>
+        <v>128087681</v>
       </c>
       <c r="B35" t="n">
-        <v>8450</v>
+        <v>98591</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Ormetjärn V., Dls</t>
+          <t>Svarttjärnen S., Dls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>317022</v>
+        <v>316929</v>
       </c>
       <c r="R35" t="n">
-        <v>6550471</v>
+        <v>6550454</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4668,22 +4667,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Mosseljungbarrskog</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4701,10 +4685,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128087681</v>
+        <v>128086358</v>
       </c>
       <c r="B36" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4740,14 +4724,14 @@
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Svarttjärnen S., Dls</t>
+          <t>Svarttjärnen S/V., Dls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>316929</v>
+        <v>316837</v>
       </c>
       <c r="R36" t="n">
-        <v>6550454</v>
+        <v>6550397</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4812,53 +4796,54 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128086358</v>
+        <v>128084900</v>
       </c>
       <c r="B37" t="n">
-        <v>98585</v>
+        <v>8450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Svarttjärnen S/V., Dls</t>
+          <t>Ormetjärn V., Dls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>316837</v>
+        <v>317022</v>
       </c>
       <c r="R37" t="n">
-        <v>6550397</v>
+        <v>6550471</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4905,7 +4890,22 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Mosseljungbarrskog</t>
+          <t>Bärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4926,7 +4926,7 @@
         <v>128085583</v>
       </c>
       <c r="B38" t="n">
-        <v>91937</v>
+        <v>91939</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>128087374</v>
       </c>
       <c r="B39" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5159,10 +5159,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128086155</v>
+        <v>128087033</v>
       </c>
       <c r="B40" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5202,10 +5202,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>316836</v>
+        <v>316848</v>
       </c>
       <c r="R40" t="n">
-        <v>6550404</v>
+        <v>6550426</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5270,10 +5270,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128087641</v>
+        <v>128086155</v>
       </c>
       <c r="B41" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5313,10 +5313,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>316887</v>
+        <v>316836</v>
       </c>
       <c r="R41" t="n">
-        <v>6550467</v>
+        <v>6550404</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5381,10 +5381,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128087033</v>
+        <v>128087074</v>
       </c>
       <c r="B42" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5424,10 +5424,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>316848</v>
+        <v>316863</v>
       </c>
       <c r="R42" t="n">
-        <v>6550426</v>
+        <v>6550433</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5492,10 +5492,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128087074</v>
+        <v>128087641</v>
       </c>
       <c r="B43" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5535,10 +5535,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>316863</v>
+        <v>316887</v>
       </c>
       <c r="R43" t="n">
-        <v>6550433</v>
+        <v>6550467</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5606,7 +5606,7 @@
         <v>128086710</v>
       </c>
       <c r="B44" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         <v>128087244</v>
       </c>
       <c r="B45" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         <v>128086546</v>
       </c>
       <c r="B46" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5936,10 +5936,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128086825</v>
+        <v>128086451</v>
       </c>
       <c r="B47" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5979,10 +5979,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>316809</v>
+        <v>316834</v>
       </c>
       <c r="R47" t="n">
-        <v>6550455</v>
+        <v>6550393</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6050,7 +6050,7 @@
         <v>128086406</v>
       </c>
       <c r="B48" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6158,10 +6158,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128086451</v>
+        <v>128086825</v>
       </c>
       <c r="B49" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>316834</v>
+        <v>316809</v>
       </c>
       <c r="R49" t="n">
-        <v>6550393</v>
+        <v>6550455</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6272,7 +6272,7 @@
         <v>128085493</v>
       </c>
       <c r="B50" t="n">
-        <v>91484</v>
+        <v>91486</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6401,7 +6401,7 @@
         <v>128084972</v>
       </c>
       <c r="B51" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6523,54 +6523,52 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128084916</v>
+        <v>128085763</v>
       </c>
       <c r="B52" t="n">
-        <v>8450</v>
+        <v>91939</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>5467</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Ormetjärn S/V., Dls</t>
+          <t>Svarttjärnen S/V., Dls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>317037</v>
+        <v>316919</v>
       </c>
       <c r="R52" t="n">
-        <v>6550398</v>
+        <v>6550474</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6617,7 +6615,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
+          <t>Bärljunbarrskog</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
@@ -6777,41 +6775,42 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128085763</v>
+        <v>128086997</v>
       </c>
       <c r="B54" t="n">
-        <v>91937</v>
+        <v>98591</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5467</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6819,10 +6818,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>316919</v>
+        <v>316832</v>
       </c>
       <c r="R54" t="n">
-        <v>6550474</v>
+        <v>6550424</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6869,22 +6868,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Bärljunbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Mosseljungbarrskog</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6902,10 +6886,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128086997</v>
+        <v>128086772</v>
       </c>
       <c r="B55" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6945,10 +6929,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>316832</v>
+        <v>316809</v>
       </c>
       <c r="R55" t="n">
-        <v>6550424</v>
+        <v>6550451</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -7013,53 +6997,54 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128086772</v>
+        <v>128084916</v>
       </c>
       <c r="B56" t="n">
-        <v>98585</v>
+        <v>8450</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Svarttjärnen S/V., Dls</t>
+          <t>Ormetjärn S/V., Dls</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>316809</v>
+        <v>317037</v>
       </c>
       <c r="R56" t="n">
-        <v>6550451</v>
+        <v>6550398</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7106,7 +7091,22 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Mosseljungbarrskog</t>
+          <t>Bärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7254,7 +7254,7 @@
         <v>128086654</v>
       </c>
       <c r="B58" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7365,7 +7365,7 @@
         <v>128086469</v>
       </c>
       <c r="B59" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7476,7 +7476,7 @@
         <v>128086692</v>
       </c>
       <c r="B60" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         <v>128085294</v>
       </c>
       <c r="B61" t="n">
-        <v>92947</v>
+        <v>92949</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>128087465</v>
       </c>
       <c r="B62" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7823,7 +7823,7 @@
         <v>128086718</v>
       </c>
       <c r="B63" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8058,10 +8058,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128087506</v>
+        <v>128087411</v>
       </c>
       <c r="B65" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8101,10 +8101,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>316865</v>
+        <v>316858</v>
       </c>
       <c r="R65" t="n">
-        <v>6550469</v>
+        <v>6550464</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -8169,10 +8169,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128087411</v>
+        <v>128087606</v>
       </c>
       <c r="B66" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8212,10 +8212,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>316858</v>
+        <v>316877</v>
       </c>
       <c r="R66" t="n">
-        <v>6550464</v>
+        <v>6550456</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -8280,10 +8280,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128087606</v>
+        <v>128087506</v>
       </c>
       <c r="B67" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8323,10 +8323,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>316877</v>
+        <v>316865</v>
       </c>
       <c r="R67" t="n">
-        <v>6550456</v>
+        <v>6550469</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -8394,7 +8394,7 @@
         <v>128087295</v>
       </c>
       <c r="B68" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         <v>128086518</v>
       </c>
       <c r="B69" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8616,7 +8616,7 @@
         <v>128085956</v>
       </c>
       <c r="B70" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 40826-2025 artfynd.xlsx
+++ b/artfynd/A 40826-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY70"/>
+  <dimension ref="A1:AY105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8718,6 +8718,3521 @@
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>128931880</v>
+      </c>
+      <c r="B71" t="n">
+        <v>96878</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>53</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>316881</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6550407</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>128931877</v>
+      </c>
+      <c r="B72" t="n">
+        <v>91277</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>316908</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6550462</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>128931865</v>
+      </c>
+      <c r="B73" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>317048</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6550340</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>128931859</v>
+      </c>
+      <c r="B74" t="n">
+        <v>90282</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>1596</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Jättemusseron</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Tricholoma colossus</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>316972</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6550656</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>128931870</v>
+      </c>
+      <c r="B75" t="n">
+        <v>96914</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>316962</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6550379</v>
+      </c>
+      <c r="S75" t="n">
+        <v>5</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>128931881</v>
+      </c>
+      <c r="B76" t="n">
+        <v>96914</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>316881</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6550407</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>128931883</v>
+      </c>
+      <c r="B77" t="n">
+        <v>96914</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>316864</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6550421</v>
+      </c>
+      <c r="S77" t="n">
+        <v>5</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>128931887</v>
+      </c>
+      <c r="B78" t="n">
+        <v>96914</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>316894</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6550382</v>
+      </c>
+      <c r="S78" t="n">
+        <v>5</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>128931827</v>
+      </c>
+      <c r="B79" t="n">
+        <v>98632</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>316833</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6550435</v>
+      </c>
+      <c r="S79" t="n">
+        <v>5</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>128931860</v>
+      </c>
+      <c r="B80" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>316968</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6550604</v>
+      </c>
+      <c r="S80" t="n">
+        <v>5</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>128931857</v>
+      </c>
+      <c r="B81" t="n">
+        <v>92794</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>316962</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6550668</v>
+      </c>
+      <c r="S81" t="n">
+        <v>5</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>128931869</v>
+      </c>
+      <c r="B82" t="n">
+        <v>96878</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>53</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>316962</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6550379</v>
+      </c>
+      <c r="S82" t="n">
+        <v>5</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>128931825</v>
+      </c>
+      <c r="B83" t="n">
+        <v>96914</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>316831</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6550424</v>
+      </c>
+      <c r="S83" t="n">
+        <v>5</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>128931874</v>
+      </c>
+      <c r="B84" t="n">
+        <v>96914</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>316914</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6550458</v>
+      </c>
+      <c r="S84" t="n">
+        <v>5</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>128931878</v>
+      </c>
+      <c r="B85" t="n">
+        <v>96878</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>53</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>316896</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6550430</v>
+      </c>
+      <c r="S85" t="n">
+        <v>5</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>128931873</v>
+      </c>
+      <c r="B86" t="n">
+        <v>96878</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>53</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>316914</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6550458</v>
+      </c>
+      <c r="S86" t="n">
+        <v>5</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>128931864</v>
+      </c>
+      <c r="B87" t="n">
+        <v>92832</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>317043</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6550355</v>
+      </c>
+      <c r="S87" t="n">
+        <v>5</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>128931886</v>
+      </c>
+      <c r="B88" t="n">
+        <v>96878</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>53</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>316894</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6550382</v>
+      </c>
+      <c r="S88" t="n">
+        <v>5</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>128931871</v>
+      </c>
+      <c r="B89" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>316944</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6550472</v>
+      </c>
+      <c r="S89" t="n">
+        <v>5</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>128931872</v>
+      </c>
+      <c r="B90" t="n">
+        <v>96914</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>316937</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6550476</v>
+      </c>
+      <c r="S90" t="n">
+        <v>5</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>128931856</v>
+      </c>
+      <c r="B91" t="n">
+        <v>92794</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>316947</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6550667</v>
+      </c>
+      <c r="S91" t="n">
+        <v>5</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>128931863</v>
+      </c>
+      <c r="B92" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>317035</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6550369</v>
+      </c>
+      <c r="S92" t="n">
+        <v>5</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>128931868</v>
+      </c>
+      <c r="B93" t="n">
+        <v>96914</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>317023</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6550315</v>
+      </c>
+      <c r="S93" t="n">
+        <v>5</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>128931879</v>
+      </c>
+      <c r="B94" t="n">
+        <v>96914</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>316896</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6550430</v>
+      </c>
+      <c r="S94" t="n">
+        <v>5</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>128931828</v>
+      </c>
+      <c r="B95" t="n">
+        <v>96914</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>316830</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6550440</v>
+      </c>
+      <c r="S95" t="n">
+        <v>5</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>128931826</v>
+      </c>
+      <c r="B96" t="n">
+        <v>98632</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>316835</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6550425</v>
+      </c>
+      <c r="S96" t="n">
+        <v>5</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>128931885</v>
+      </c>
+      <c r="B97" t="n">
+        <v>96878</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>53</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>316872</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6550383</v>
+      </c>
+      <c r="S97" t="n">
+        <v>5</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>128931876</v>
+      </c>
+      <c r="B98" t="n">
+        <v>4779</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>316911</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6550465</v>
+      </c>
+      <c r="S98" t="n">
+        <v>5</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>128931861</v>
+      </c>
+      <c r="B99" t="n">
+        <v>92794</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>317004</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6550507</v>
+      </c>
+      <c r="S99" t="n">
+        <v>5</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>128931884</v>
+      </c>
+      <c r="B100" t="n">
+        <v>96914</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>316872</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6550383</v>
+      </c>
+      <c r="S100" t="n">
+        <v>5</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>128931866</v>
+      </c>
+      <c r="B101" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>317035</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6550330</v>
+      </c>
+      <c r="S101" t="n">
+        <v>5</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>128931829</v>
+      </c>
+      <c r="B102" t="n">
+        <v>98632</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>316816</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6550435</v>
+      </c>
+      <c r="S102" t="n">
+        <v>5</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>128931862</v>
+      </c>
+      <c r="B103" t="n">
+        <v>92832</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>317008</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6550497</v>
+      </c>
+      <c r="S103" t="n">
+        <v>5</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>128931882</v>
+      </c>
+      <c r="B104" t="n">
+        <v>96878</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>53</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>316864</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6550421</v>
+      </c>
+      <c r="S104" t="n">
+        <v>5</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>128931855</v>
+      </c>
+      <c r="B105" t="n">
+        <v>90282</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>1596</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Jättemusseron</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Tricholoma colossus</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>316943</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6550676</v>
+      </c>
+      <c r="S105" t="n">
+        <v>5</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40826-2025 artfynd.xlsx
+++ b/artfynd/A 40826-2025 artfynd.xlsx
@@ -8720,32 +8720,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128931880</v>
+        <v>128931859</v>
       </c>
       <c r="B71" t="n">
-        <v>96878</v>
+        <v>90286</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>53</v>
+        <v>1596</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8755,10 +8755,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>316881</v>
+        <v>316972</v>
       </c>
       <c r="R71" t="n">
-        <v>6550407</v>
+        <v>6550656</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8820,7 +8820,7 @@
         <v>128931877</v>
       </c>
       <c r="B72" t="n">
-        <v>91277</v>
+        <v>91281</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8914,50 +8914,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128931865</v>
+        <v>128931880</v>
       </c>
       <c r="B73" t="n">
-        <v>8450</v>
+        <v>96882</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>317048</v>
+        <v>316881</v>
       </c>
       <c r="R73" t="n">
-        <v>6550340</v>
+        <v>6550407</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -9000,21 +8995,6 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -9031,45 +9011,50 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128931859</v>
+        <v>128931865</v>
       </c>
       <c r="B74" t="n">
-        <v>90282</v>
+        <v>8450</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1596</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>316972</v>
+        <v>317048</v>
       </c>
       <c r="R74" t="n">
-        <v>6550656</v>
+        <v>6550340</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9112,6 +9097,21 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -9131,7 +9131,7 @@
         <v>128931870</v>
       </c>
       <c r="B75" t="n">
-        <v>96914</v>
+        <v>96918</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         <v>128931881</v>
       </c>
       <c r="B76" t="n">
-        <v>96914</v>
+        <v>96918</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9322,10 +9322,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128931883</v>
+        <v>128931860</v>
       </c>
       <c r="B77" t="n">
-        <v>96914</v>
+        <v>8450</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9333,34 +9333,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>316864</v>
+        <v>316968</v>
       </c>
       <c r="R77" t="n">
-        <v>6550421</v>
+        <v>6550604</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9403,6 +9408,21 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -9419,32 +9439,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128931887</v>
+        <v>128931827</v>
       </c>
       <c r="B78" t="n">
-        <v>96914</v>
+        <v>98636</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2590</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9454,10 +9474,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>316894</v>
+        <v>316833</v>
       </c>
       <c r="R78" t="n">
-        <v>6550382</v>
+        <v>6550435</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9516,32 +9536,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128931827</v>
+        <v>128931883</v>
       </c>
       <c r="B79" t="n">
-        <v>98632</v>
+        <v>96918</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>2590</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9551,10 +9571,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>316833</v>
+        <v>316864</v>
       </c>
       <c r="R79" t="n">
-        <v>6550435</v>
+        <v>6550421</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9613,10 +9633,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128931860</v>
+        <v>128931887</v>
       </c>
       <c r="B80" t="n">
-        <v>8450</v>
+        <v>96918</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9624,39 +9644,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>316968</v>
+        <v>316894</v>
       </c>
       <c r="R80" t="n">
-        <v>6550604</v>
+        <v>6550382</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9699,21 +9714,6 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -9730,32 +9730,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128931857</v>
+        <v>128931869</v>
       </c>
       <c r="B81" t="n">
-        <v>92794</v>
+        <v>96882</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9768,7 +9768,7 @@
         <v>316962</v>
       </c>
       <c r="R81" t="n">
-        <v>6550668</v>
+        <v>6550379</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9827,32 +9827,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128931869</v>
+        <v>128931857</v>
       </c>
       <c r="B82" t="n">
-        <v>96878</v>
+        <v>92798</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9865,7 +9865,7 @@
         <v>316962</v>
       </c>
       <c r="R82" t="n">
-        <v>6550379</v>
+        <v>6550668</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9924,32 +9924,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128931825</v>
+        <v>128931878</v>
       </c>
       <c r="B83" t="n">
-        <v>96914</v>
+        <v>96882</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2590</v>
+        <v>53</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9959,10 +9959,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>316831</v>
+        <v>316896</v>
       </c>
       <c r="R83" t="n">
-        <v>6550424</v>
+        <v>6550430</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -10021,10 +10021,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128931874</v>
+        <v>128931825</v>
       </c>
       <c r="B84" t="n">
-        <v>96914</v>
+        <v>96918</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10056,10 +10056,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>316914</v>
+        <v>316831</v>
       </c>
       <c r="R84" t="n">
-        <v>6550458</v>
+        <v>6550424</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -10118,32 +10118,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128931878</v>
+        <v>128931874</v>
       </c>
       <c r="B85" t="n">
-        <v>96878</v>
+        <v>96918</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>53</v>
+        <v>2590</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10153,10 +10153,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>316896</v>
+        <v>316914</v>
       </c>
       <c r="R85" t="n">
-        <v>6550430</v>
+        <v>6550458</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -10215,10 +10215,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128931873</v>
+        <v>128931864</v>
       </c>
       <c r="B86" t="n">
-        <v>96878</v>
+        <v>92836</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10226,21 +10226,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>53</v>
+        <v>5966</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10250,10 +10250,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>316914</v>
+        <v>317043</v>
       </c>
       <c r="R86" t="n">
-        <v>6550458</v>
+        <v>6550355</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10312,10 +10312,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128931864</v>
+        <v>128931873</v>
       </c>
       <c r="B87" t="n">
-        <v>92832</v>
+        <v>96882</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10323,21 +10323,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5966</v>
+        <v>53</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10347,10 +10347,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>317043</v>
+        <v>316914</v>
       </c>
       <c r="R87" t="n">
-        <v>6550355</v>
+        <v>6550458</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10412,7 +10412,7 @@
         <v>128931886</v>
       </c>
       <c r="B88" t="n">
-        <v>96878</v>
+        <v>96882</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>128931872</v>
       </c>
       <c r="B90" t="n">
-        <v>96914</v>
+        <v>96918</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10723,7 +10723,7 @@
         <v>128931856</v>
       </c>
       <c r="B91" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10817,10 +10817,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128931863</v>
+        <v>128931868</v>
       </c>
       <c r="B92" t="n">
-        <v>8450</v>
+        <v>96918</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10828,39 +10828,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>317035</v>
+        <v>317023</v>
       </c>
       <c r="R92" t="n">
-        <v>6550369</v>
+        <v>6550315</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10903,21 +10898,6 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ92" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK92" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO92" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
@@ -10934,10 +10914,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128931868</v>
+        <v>128931863</v>
       </c>
       <c r="B93" t="n">
-        <v>96914</v>
+        <v>8450</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10945,34 +10925,39 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>317023</v>
+        <v>317035</v>
       </c>
       <c r="R93" t="n">
-        <v>6550315</v>
+        <v>6550369</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -11015,6 +11000,21 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
@@ -11034,7 +11034,7 @@
         <v>128931879</v>
       </c>
       <c r="B94" t="n">
-        <v>96914</v>
+        <v>96918</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11131,7 +11131,7 @@
         <v>128931828</v>
       </c>
       <c r="B95" t="n">
-        <v>96914</v>
+        <v>96918</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>128931826</v>
       </c>
       <c r="B96" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>128931885</v>
       </c>
       <c r="B97" t="n">
-        <v>96878</v>
+        <v>96882</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11419,10 +11419,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128931876</v>
+        <v>128931861</v>
       </c>
       <c r="B98" t="n">
-        <v>4779</v>
+        <v>92798</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11430,39 +11430,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>102306</v>
+        <v>4364</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>316911</v>
+        <v>317004</v>
       </c>
       <c r="R98" t="n">
-        <v>6550465</v>
+        <v>6550507</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11505,21 +11500,6 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ98" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK98" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO98" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
@@ -11536,10 +11516,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128931861</v>
+        <v>128931876</v>
       </c>
       <c r="B99" t="n">
-        <v>92794</v>
+        <v>4779</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11547,34 +11527,39 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4364</v>
+        <v>102306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>317004</v>
+        <v>316911</v>
       </c>
       <c r="R99" t="n">
-        <v>6550507</v>
+        <v>6550465</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11617,6 +11602,21 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
@@ -11636,7 +11636,7 @@
         <v>128931884</v>
       </c>
       <c r="B100" t="n">
-        <v>96914</v>
+        <v>96918</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11850,7 +11850,7 @@
         <v>128931829</v>
       </c>
       <c r="B102" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11944,32 +11944,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128931862</v>
+        <v>128931855</v>
       </c>
       <c r="B103" t="n">
-        <v>92832</v>
+        <v>90286</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5966</v>
+        <v>1596</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11979,10 +11979,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>317008</v>
+        <v>316943</v>
       </c>
       <c r="R103" t="n">
-        <v>6550497</v>
+        <v>6550676</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -12044,7 +12044,7 @@
         <v>128931882</v>
       </c>
       <c r="B104" t="n">
-        <v>96878</v>
+        <v>96882</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12138,32 +12138,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128931855</v>
+        <v>128931862</v>
       </c>
       <c r="B105" t="n">
-        <v>90282</v>
+        <v>92836</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1596</v>
+        <v>5966</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12173,10 +12173,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>316943</v>
+        <v>317008</v>
       </c>
       <c r="R105" t="n">
-        <v>6550676</v>
+        <v>6550497</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>

--- a/artfynd/A 40826-2025 artfynd.xlsx
+++ b/artfynd/A 40826-2025 artfynd.xlsx
@@ -8720,32 +8720,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128931859</v>
+        <v>128931880</v>
       </c>
       <c r="B71" t="n">
-        <v>90286</v>
+        <v>96882</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1596</v>
+        <v>53</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8755,10 +8755,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>316972</v>
+        <v>316881</v>
       </c>
       <c r="R71" t="n">
-        <v>6550656</v>
+        <v>6550407</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8914,45 +8914,50 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128931880</v>
+        <v>128931865</v>
       </c>
       <c r="B73" t="n">
-        <v>96882</v>
+        <v>8450</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>316881</v>
+        <v>317048</v>
       </c>
       <c r="R73" t="n">
-        <v>6550407</v>
+        <v>6550340</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8995,6 +9000,21 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -9011,50 +9031,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128931865</v>
+        <v>128931859</v>
       </c>
       <c r="B74" t="n">
-        <v>8450</v>
+        <v>90286</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>1596</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>317048</v>
+        <v>316972</v>
       </c>
       <c r="R74" t="n">
-        <v>6550340</v>
+        <v>6550656</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9097,21 +9112,6 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -9322,10 +9322,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128931860</v>
+        <v>128931883</v>
       </c>
       <c r="B77" t="n">
-        <v>8450</v>
+        <v>96918</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9333,39 +9333,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>316968</v>
+        <v>316864</v>
       </c>
       <c r="R77" t="n">
-        <v>6550604</v>
+        <v>6550421</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9408,21 +9403,6 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -9439,32 +9419,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128931827</v>
+        <v>128931887</v>
       </c>
       <c r="B78" t="n">
-        <v>98636</v>
+        <v>96918</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>2590</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9474,10 +9454,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>316833</v>
+        <v>316894</v>
       </c>
       <c r="R78" t="n">
-        <v>6550435</v>
+        <v>6550382</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9536,10 +9516,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128931883</v>
+        <v>128931860</v>
       </c>
       <c r="B79" t="n">
-        <v>96918</v>
+        <v>8450</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9547,34 +9527,39 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>316864</v>
+        <v>316968</v>
       </c>
       <c r="R79" t="n">
-        <v>6550421</v>
+        <v>6550604</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9617,6 +9602,21 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -9633,32 +9633,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128931887</v>
+        <v>128931827</v>
       </c>
       <c r="B80" t="n">
-        <v>96918</v>
+        <v>98636</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2590</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9668,10 +9668,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>316894</v>
+        <v>316833</v>
       </c>
       <c r="R80" t="n">
-        <v>6550382</v>
+        <v>6550435</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9730,32 +9730,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128931869</v>
+        <v>128931857</v>
       </c>
       <c r="B81" t="n">
-        <v>96882</v>
+        <v>92798</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9768,7 +9768,7 @@
         <v>316962</v>
       </c>
       <c r="R81" t="n">
-        <v>6550379</v>
+        <v>6550668</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9827,32 +9827,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128931857</v>
+        <v>128931869</v>
       </c>
       <c r="B82" t="n">
-        <v>92798</v>
+        <v>96882</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9865,7 +9865,7 @@
         <v>316962</v>
       </c>
       <c r="R82" t="n">
-        <v>6550668</v>
+        <v>6550379</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9924,32 +9924,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128931878</v>
+        <v>128931825</v>
       </c>
       <c r="B83" t="n">
-        <v>96882</v>
+        <v>96918</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>53</v>
+        <v>2590</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9959,10 +9959,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>316896</v>
+        <v>316831</v>
       </c>
       <c r="R83" t="n">
-        <v>6550430</v>
+        <v>6550424</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -10021,7 +10021,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128931825</v>
+        <v>128931874</v>
       </c>
       <c r="B84" t="n">
         <v>96918</v>
@@ -10056,10 +10056,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>316831</v>
+        <v>316914</v>
       </c>
       <c r="R84" t="n">
-        <v>6550424</v>
+        <v>6550458</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -10118,32 +10118,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128931874</v>
+        <v>128931878</v>
       </c>
       <c r="B85" t="n">
-        <v>96918</v>
+        <v>96882</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2590</v>
+        <v>53</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10153,10 +10153,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>316914</v>
+        <v>316896</v>
       </c>
       <c r="R85" t="n">
-        <v>6550458</v>
+        <v>6550430</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -11944,32 +11944,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128931855</v>
+        <v>128931882</v>
       </c>
       <c r="B103" t="n">
-        <v>90286</v>
+        <v>96882</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1596</v>
+        <v>53</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11979,10 +11979,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>316943</v>
+        <v>316864</v>
       </c>
       <c r="R103" t="n">
-        <v>6550676</v>
+        <v>6550421</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -12041,10 +12041,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128931882</v>
+        <v>128931862</v>
       </c>
       <c r="B104" t="n">
-        <v>96882</v>
+        <v>92836</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12052,21 +12052,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>53</v>
+        <v>5966</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12076,10 +12076,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>316864</v>
+        <v>317008</v>
       </c>
       <c r="R104" t="n">
-        <v>6550421</v>
+        <v>6550497</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -12138,32 +12138,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128931862</v>
+        <v>128931855</v>
       </c>
       <c r="B105" t="n">
-        <v>92836</v>
+        <v>90286</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5966</v>
+        <v>1596</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12173,10 +12173,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>317008</v>
+        <v>316943</v>
       </c>
       <c r="R105" t="n">
-        <v>6550497</v>
+        <v>6550676</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>

--- a/artfynd/A 40826-2025 artfynd.xlsx
+++ b/artfynd/A 40826-2025 artfynd.xlsx
@@ -8914,50 +8914,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128931865</v>
+        <v>128931859</v>
       </c>
       <c r="B73" t="n">
-        <v>8450</v>
+        <v>90286</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>1596</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>317048</v>
+        <v>316972</v>
       </c>
       <c r="R73" t="n">
-        <v>6550340</v>
+        <v>6550656</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -9000,21 +8995,6 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -9031,45 +9011,50 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128931859</v>
+        <v>128931865</v>
       </c>
       <c r="B74" t="n">
-        <v>90286</v>
+        <v>8450</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1596</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>316972</v>
+        <v>317048</v>
       </c>
       <c r="R74" t="n">
-        <v>6550656</v>
+        <v>6550340</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9112,6 +9097,21 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -10215,10 +10215,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128931864</v>
+        <v>128931873</v>
       </c>
       <c r="B86" t="n">
-        <v>92836</v>
+        <v>96882</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10226,21 +10226,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5966</v>
+        <v>53</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10250,10 +10250,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>317043</v>
+        <v>316914</v>
       </c>
       <c r="R86" t="n">
-        <v>6550355</v>
+        <v>6550458</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10312,10 +10312,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128931873</v>
+        <v>128931864</v>
       </c>
       <c r="B87" t="n">
-        <v>96882</v>
+        <v>92836</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10323,21 +10323,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>53</v>
+        <v>5966</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10347,10 +10347,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>316914</v>
+        <v>317043</v>
       </c>
       <c r="R87" t="n">
-        <v>6550458</v>
+        <v>6550355</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -12041,32 +12041,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128931862</v>
+        <v>128931855</v>
       </c>
       <c r="B104" t="n">
-        <v>92836</v>
+        <v>90286</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5966</v>
+        <v>1596</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12076,10 +12076,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>317008</v>
+        <v>316943</v>
       </c>
       <c r="R104" t="n">
-        <v>6550497</v>
+        <v>6550676</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -12138,32 +12138,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128931855</v>
+        <v>128931862</v>
       </c>
       <c r="B105" t="n">
-        <v>90286</v>
+        <v>92836</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1596</v>
+        <v>5966</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12173,10 +12173,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>316943</v>
+        <v>317008</v>
       </c>
       <c r="R105" t="n">
-        <v>6550676</v>
+        <v>6550497</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>

--- a/artfynd/A 40826-2025 artfynd.xlsx
+++ b/artfynd/A 40826-2025 artfynd.xlsx
@@ -8720,32 +8720,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128931880</v>
+        <v>128931877</v>
       </c>
       <c r="B71" t="n">
-        <v>96882</v>
+        <v>91286</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>53</v>
+        <v>3215</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8755,10 +8755,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>316881</v>
+        <v>316908</v>
       </c>
       <c r="R71" t="n">
-        <v>6550407</v>
+        <v>6550462</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8817,10 +8817,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128931877</v>
+        <v>128931865</v>
       </c>
       <c r="B72" t="n">
-        <v>91281</v>
+        <v>8450</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8828,34 +8828,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3215</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>316908</v>
+        <v>317048</v>
       </c>
       <c r="R72" t="n">
-        <v>6550462</v>
+        <v>6550340</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8898,6 +8903,21 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -8914,32 +8934,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128931859</v>
+        <v>128931880</v>
       </c>
       <c r="B73" t="n">
-        <v>90286</v>
+        <v>96889</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1596</v>
+        <v>53</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8949,10 +8969,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>316972</v>
+        <v>316881</v>
       </c>
       <c r="R73" t="n">
-        <v>6550656</v>
+        <v>6550407</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -9011,50 +9031,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128931865</v>
+        <v>128931859</v>
       </c>
       <c r="B74" t="n">
-        <v>8450</v>
+        <v>90291</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>1596</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>317048</v>
+        <v>316972</v>
       </c>
       <c r="R74" t="n">
-        <v>6550340</v>
+        <v>6550656</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9097,21 +9112,6 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -9131,7 +9131,7 @@
         <v>128931870</v>
       </c>
       <c r="B75" t="n">
-        <v>96918</v>
+        <v>96925</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         <v>128931881</v>
       </c>
       <c r="B76" t="n">
-        <v>96918</v>
+        <v>96925</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         <v>128931883</v>
       </c>
       <c r="B77" t="n">
-        <v>96918</v>
+        <v>96925</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9422,7 +9422,7 @@
         <v>128931887</v>
       </c>
       <c r="B78" t="n">
-        <v>96918</v>
+        <v>96925</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>128931827</v>
       </c>
       <c r="B80" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9733,7 +9733,7 @@
         <v>128931857</v>
       </c>
       <c r="B81" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>128931869</v>
       </c>
       <c r="B82" t="n">
-        <v>96882</v>
+        <v>96889</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9924,32 +9924,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128931825</v>
+        <v>128931878</v>
       </c>
       <c r="B83" t="n">
-        <v>96918</v>
+        <v>96889</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2590</v>
+        <v>53</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9959,10 +9959,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>316831</v>
+        <v>316896</v>
       </c>
       <c r="R83" t="n">
-        <v>6550424</v>
+        <v>6550430</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -10021,10 +10021,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128931874</v>
+        <v>128931825</v>
       </c>
       <c r="B84" t="n">
-        <v>96918</v>
+        <v>96925</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10056,10 +10056,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>316914</v>
+        <v>316831</v>
       </c>
       <c r="R84" t="n">
-        <v>6550458</v>
+        <v>6550424</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -10118,32 +10118,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128931878</v>
+        <v>128931874</v>
       </c>
       <c r="B85" t="n">
-        <v>96882</v>
+        <v>96925</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>53</v>
+        <v>2590</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10153,10 +10153,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>316896</v>
+        <v>316914</v>
       </c>
       <c r="R85" t="n">
-        <v>6550430</v>
+        <v>6550458</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -10215,10 +10215,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128931873</v>
+        <v>128931864</v>
       </c>
       <c r="B86" t="n">
-        <v>96882</v>
+        <v>92841</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10226,21 +10226,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>53</v>
+        <v>5966</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10250,10 +10250,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>316914</v>
+        <v>317043</v>
       </c>
       <c r="R86" t="n">
-        <v>6550458</v>
+        <v>6550355</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10312,10 +10312,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128931864</v>
+        <v>128931873</v>
       </c>
       <c r="B87" t="n">
-        <v>92836</v>
+        <v>96889</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10323,21 +10323,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5966</v>
+        <v>53</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10347,10 +10347,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>317043</v>
+        <v>316914</v>
       </c>
       <c r="R87" t="n">
-        <v>6550355</v>
+        <v>6550458</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10412,7 +10412,7 @@
         <v>128931886</v>
       </c>
       <c r="B88" t="n">
-        <v>96882</v>
+        <v>96889</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>128931872</v>
       </c>
       <c r="B90" t="n">
-        <v>96918</v>
+        <v>96925</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10723,7 +10723,7 @@
         <v>128931856</v>
       </c>
       <c r="B91" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10820,7 +10820,7 @@
         <v>128931868</v>
       </c>
       <c r="B92" t="n">
-        <v>96918</v>
+        <v>96925</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11031,32 +11031,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128931879</v>
+        <v>128931826</v>
       </c>
       <c r="B94" t="n">
-        <v>96918</v>
+        <v>98643</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2590</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11066,10 +11066,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>316896</v>
+        <v>316835</v>
       </c>
       <c r="R94" t="n">
-        <v>6550430</v>
+        <v>6550425</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -11131,7 +11131,7 @@
         <v>128931828</v>
       </c>
       <c r="B95" t="n">
-        <v>96918</v>
+        <v>96925</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11225,32 +11225,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128931826</v>
+        <v>128931879</v>
       </c>
       <c r="B96" t="n">
-        <v>98636</v>
+        <v>96925</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>2590</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11260,10 +11260,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>316835</v>
+        <v>316896</v>
       </c>
       <c r="R96" t="n">
-        <v>6550425</v>
+        <v>6550430</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11325,7 +11325,7 @@
         <v>128931885</v>
       </c>
       <c r="B97" t="n">
-        <v>96882</v>
+        <v>96889</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>128931861</v>
       </c>
       <c r="B98" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11636,7 +11636,7 @@
         <v>128931884</v>
       </c>
       <c r="B100" t="n">
-        <v>96918</v>
+        <v>96925</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11850,7 +11850,7 @@
         <v>128931829</v>
       </c>
       <c r="B102" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>128931882</v>
       </c>
       <c r="B103" t="n">
-        <v>96882</v>
+        <v>96889</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>128931855</v>
       </c>
       <c r="B104" t="n">
-        <v>90286</v>
+        <v>90291</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>128931862</v>
       </c>
       <c r="B105" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>

--- a/artfynd/A 40826-2025 artfynd.xlsx
+++ b/artfynd/A 40826-2025 artfynd.xlsx
@@ -9730,32 +9730,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128931869</v>
+        <v>128931857</v>
       </c>
       <c r="B81" t="n">
-        <v>96897</v>
+        <v>92811</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9768,7 +9768,7 @@
         <v>316962</v>
       </c>
       <c r="R81" t="n">
-        <v>6550379</v>
+        <v>6550668</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9827,32 +9827,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128931857</v>
+        <v>128931869</v>
       </c>
       <c r="B82" t="n">
-        <v>92811</v>
+        <v>96897</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9865,7 +9865,7 @@
         <v>316962</v>
       </c>
       <c r="R82" t="n">
-        <v>6550668</v>
+        <v>6550379</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9924,32 +9924,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128931878</v>
+        <v>128931825</v>
       </c>
       <c r="B83" t="n">
-        <v>96897</v>
+        <v>96933</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>53</v>
+        <v>2590</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9959,10 +9959,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>316896</v>
+        <v>316831</v>
       </c>
       <c r="R83" t="n">
-        <v>6550430</v>
+        <v>6550424</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -10021,7 +10021,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128931825</v>
+        <v>128931874</v>
       </c>
       <c r="B84" t="n">
         <v>96933</v>
@@ -10056,10 +10056,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>316831</v>
+        <v>316914</v>
       </c>
       <c r="R84" t="n">
-        <v>6550424</v>
+        <v>6550458</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -10118,32 +10118,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128931874</v>
+        <v>128931878</v>
       </c>
       <c r="B85" t="n">
-        <v>96933</v>
+        <v>96897</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2590</v>
+        <v>53</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10153,10 +10153,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>316914</v>
+        <v>316896</v>
       </c>
       <c r="R85" t="n">
-        <v>6550458</v>
+        <v>6550430</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -10215,10 +10215,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128931864</v>
+        <v>128931873</v>
       </c>
       <c r="B86" t="n">
-        <v>92849</v>
+        <v>96897</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10226,21 +10226,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5966</v>
+        <v>53</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10250,10 +10250,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>317043</v>
+        <v>316914</v>
       </c>
       <c r="R86" t="n">
-        <v>6550355</v>
+        <v>6550458</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10312,10 +10312,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128931873</v>
+        <v>128931864</v>
       </c>
       <c r="B87" t="n">
-        <v>96897</v>
+        <v>92849</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10323,21 +10323,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>53</v>
+        <v>5966</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10347,10 +10347,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>316914</v>
+        <v>317043</v>
       </c>
       <c r="R87" t="n">
-        <v>6550458</v>
+        <v>6550355</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10623,10 +10623,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128931856</v>
+        <v>128931872</v>
       </c>
       <c r="B90" t="n">
-        <v>92811</v>
+        <v>96933</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10634,21 +10634,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4364</v>
+        <v>2590</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10658,10 +10658,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>316947</v>
+        <v>316937</v>
       </c>
       <c r="R90" t="n">
-        <v>6550667</v>
+        <v>6550476</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10720,10 +10720,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128931872</v>
+        <v>128931856</v>
       </c>
       <c r="B91" t="n">
-        <v>96933</v>
+        <v>92811</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10731,21 +10731,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2590</v>
+        <v>4364</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10755,10 +10755,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>316937</v>
+        <v>316947</v>
       </c>
       <c r="R91" t="n">
-        <v>6550476</v>
+        <v>6550667</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>

--- a/artfynd/A 40826-2025 artfynd.xlsx
+++ b/artfynd/A 40826-2025 artfynd.xlsx
@@ -8723,7 +8723,7 @@
         <v>128931859</v>
       </c>
       <c r="B71" t="n">
-        <v>90298</v>
+        <v>90301</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8817,32 +8817,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128931877</v>
+        <v>128931880</v>
       </c>
       <c r="B72" t="n">
-        <v>91293</v>
+        <v>96902</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3215</v>
+        <v>53</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8852,10 +8852,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>316908</v>
+        <v>316881</v>
       </c>
       <c r="R72" t="n">
-        <v>6550462</v>
+        <v>6550407</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8914,10 +8914,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128931865</v>
+        <v>128931877</v>
       </c>
       <c r="B73" t="n">
-        <v>8450</v>
+        <v>91296</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8925,39 +8925,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>3215</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>317048</v>
+        <v>316908</v>
       </c>
       <c r="R73" t="n">
-        <v>6550340</v>
+        <v>6550462</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -9000,21 +8995,6 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -9031,45 +9011,50 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128931880</v>
+        <v>128931865</v>
       </c>
       <c r="B74" t="n">
-        <v>96897</v>
+        <v>8450</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>316881</v>
+        <v>317048</v>
       </c>
       <c r="R74" t="n">
-        <v>6550407</v>
+        <v>6550340</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9112,6 +9097,21 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -9128,10 +9128,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128931870</v>
+        <v>128931881</v>
       </c>
       <c r="B75" t="n">
-        <v>96933</v>
+        <v>96938</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9163,10 +9163,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>316962</v>
+        <v>316881</v>
       </c>
       <c r="R75" t="n">
-        <v>6550379</v>
+        <v>6550407</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9225,10 +9225,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128931881</v>
+        <v>128931870</v>
       </c>
       <c r="B76" t="n">
-        <v>96933</v>
+        <v>96938</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9260,10 +9260,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>316881</v>
+        <v>316962</v>
       </c>
       <c r="R76" t="n">
-        <v>6550407</v>
+        <v>6550379</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9322,45 +9322,50 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128931827</v>
+        <v>128931860</v>
       </c>
       <c r="B77" t="n">
-        <v>98651</v>
+        <v>8450</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>316833</v>
+        <v>316968</v>
       </c>
       <c r="R77" t="n">
-        <v>6550435</v>
+        <v>6550604</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9403,6 +9408,21 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -9419,32 +9439,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128931883</v>
+        <v>128931827</v>
       </c>
       <c r="B78" t="n">
-        <v>96933</v>
+        <v>98656</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2590</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9454,10 +9474,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>316864</v>
+        <v>316833</v>
       </c>
       <c r="R78" t="n">
-        <v>6550421</v>
+        <v>6550435</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9519,7 +9539,7 @@
         <v>128931887</v>
       </c>
       <c r="B79" t="n">
-        <v>96933</v>
+        <v>96938</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9613,10 +9633,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128931860</v>
+        <v>128931883</v>
       </c>
       <c r="B80" t="n">
-        <v>8450</v>
+        <v>96938</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9624,39 +9644,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>316968</v>
+        <v>316864</v>
       </c>
       <c r="R80" t="n">
-        <v>6550604</v>
+        <v>6550421</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9699,21 +9714,6 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -9730,32 +9730,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128931857</v>
+        <v>128931869</v>
       </c>
       <c r="B81" t="n">
-        <v>92811</v>
+        <v>96902</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9768,7 +9768,7 @@
         <v>316962</v>
       </c>
       <c r="R81" t="n">
-        <v>6550668</v>
+        <v>6550379</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9827,32 +9827,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128931869</v>
+        <v>128931857</v>
       </c>
       <c r="B82" t="n">
-        <v>96897</v>
+        <v>92816</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9865,7 +9865,7 @@
         <v>316962</v>
       </c>
       <c r="R82" t="n">
-        <v>6550379</v>
+        <v>6550668</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9924,32 +9924,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128931825</v>
+        <v>128931878</v>
       </c>
       <c r="B83" t="n">
-        <v>96933</v>
+        <v>96902</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2590</v>
+        <v>53</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9959,10 +9959,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>316831</v>
+        <v>316896</v>
       </c>
       <c r="R83" t="n">
-        <v>6550424</v>
+        <v>6550430</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -10021,10 +10021,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128931874</v>
+        <v>128931825</v>
       </c>
       <c r="B84" t="n">
-        <v>96933</v>
+        <v>96938</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10056,10 +10056,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>316914</v>
+        <v>316831</v>
       </c>
       <c r="R84" t="n">
-        <v>6550458</v>
+        <v>6550424</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -10118,32 +10118,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128931878</v>
+        <v>128931874</v>
       </c>
       <c r="B85" t="n">
-        <v>96897</v>
+        <v>96938</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>53</v>
+        <v>2590</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10153,10 +10153,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>316896</v>
+        <v>316914</v>
       </c>
       <c r="R85" t="n">
-        <v>6550430</v>
+        <v>6550458</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -10215,10 +10215,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128931873</v>
+        <v>128931864</v>
       </c>
       <c r="B86" t="n">
-        <v>96897</v>
+        <v>92854</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10226,21 +10226,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>53</v>
+        <v>5966</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10250,10 +10250,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>316914</v>
+        <v>317043</v>
       </c>
       <c r="R86" t="n">
-        <v>6550458</v>
+        <v>6550355</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10312,10 +10312,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128931864</v>
+        <v>128931873</v>
       </c>
       <c r="B87" t="n">
-        <v>92849</v>
+        <v>96902</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10323,21 +10323,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5966</v>
+        <v>53</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10347,10 +10347,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>317043</v>
+        <v>316914</v>
       </c>
       <c r="R87" t="n">
-        <v>6550355</v>
+        <v>6550458</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10412,7 +10412,7 @@
         <v>128931886</v>
       </c>
       <c r="B88" t="n">
-        <v>96897</v>
+        <v>96902</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>128931872</v>
       </c>
       <c r="B90" t="n">
-        <v>96933</v>
+        <v>96938</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10723,7 +10723,7 @@
         <v>128931856</v>
       </c>
       <c r="B91" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10817,10 +10817,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128931868</v>
+        <v>128931863</v>
       </c>
       <c r="B92" t="n">
-        <v>96933</v>
+        <v>8450</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10828,34 +10828,39 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>317023</v>
+        <v>317035</v>
       </c>
       <c r="R92" t="n">
-        <v>6550315</v>
+        <v>6550369</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10898,6 +10903,21 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
@@ -10914,10 +10934,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128931863</v>
+        <v>128931868</v>
       </c>
       <c r="B93" t="n">
-        <v>8450</v>
+        <v>96938</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10925,39 +10945,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>317035</v>
+        <v>317023</v>
       </c>
       <c r="R93" t="n">
-        <v>6550369</v>
+        <v>6550315</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -11000,21 +11015,6 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ93" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK93" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO93" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
@@ -11031,10 +11031,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128931879</v>
+        <v>128931828</v>
       </c>
       <c r="B94" t="n">
-        <v>96933</v>
+        <v>96938</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11066,10 +11066,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>316896</v>
+        <v>316830</v>
       </c>
       <c r="R94" t="n">
-        <v>6550430</v>
+        <v>6550440</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -11128,10 +11128,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128931828</v>
+        <v>128931879</v>
       </c>
       <c r="B95" t="n">
-        <v>96933</v>
+        <v>96938</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11163,10 +11163,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>316830</v>
+        <v>316896</v>
       </c>
       <c r="R95" t="n">
-        <v>6550440</v>
+        <v>6550430</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -11228,7 +11228,7 @@
         <v>128931826</v>
       </c>
       <c r="B96" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>128931885</v>
       </c>
       <c r="B97" t="n">
-        <v>96897</v>
+        <v>96902</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11419,10 +11419,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128931876</v>
+        <v>128931861</v>
       </c>
       <c r="B98" t="n">
-        <v>4779</v>
+        <v>92816</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11430,39 +11430,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>102306</v>
+        <v>4364</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>316911</v>
+        <v>317004</v>
       </c>
       <c r="R98" t="n">
-        <v>6550465</v>
+        <v>6550507</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11505,21 +11500,6 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ98" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK98" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO98" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
@@ -11536,10 +11516,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128931861</v>
+        <v>128931876</v>
       </c>
       <c r="B99" t="n">
-        <v>92811</v>
+        <v>4779</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11547,34 +11527,39 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4364</v>
+        <v>102306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>317004</v>
+        <v>316911</v>
       </c>
       <c r="R99" t="n">
-        <v>6550507</v>
+        <v>6550465</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11617,6 +11602,21 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
@@ -11636,7 +11636,7 @@
         <v>128931884</v>
       </c>
       <c r="B100" t="n">
-        <v>96933</v>
+        <v>96938</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11850,7 +11850,7 @@
         <v>128931829</v>
       </c>
       <c r="B102" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11944,32 +11944,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128931855</v>
+        <v>128931882</v>
       </c>
       <c r="B103" t="n">
-        <v>90298</v>
+        <v>96902</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1596</v>
+        <v>53</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11979,10 +11979,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>316943</v>
+        <v>316864</v>
       </c>
       <c r="R103" t="n">
-        <v>6550676</v>
+        <v>6550421</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -12041,10 +12041,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128931882</v>
+        <v>128931862</v>
       </c>
       <c r="B104" t="n">
-        <v>96897</v>
+        <v>92854</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12052,21 +12052,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>53</v>
+        <v>5966</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12076,10 +12076,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>316864</v>
+        <v>317008</v>
       </c>
       <c r="R104" t="n">
-        <v>6550421</v>
+        <v>6550497</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -12138,32 +12138,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128931862</v>
+        <v>128931855</v>
       </c>
       <c r="B105" t="n">
-        <v>92849</v>
+        <v>90301</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5966</v>
+        <v>1596</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12173,10 +12173,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>317008</v>
+        <v>316943</v>
       </c>
       <c r="R105" t="n">
-        <v>6550497</v>
+        <v>6550676</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>

--- a/artfynd/A 40826-2025 artfynd.xlsx
+++ b/artfynd/A 40826-2025 artfynd.xlsx
@@ -8723,7 +8723,7 @@
         <v>128931859</v>
       </c>
       <c r="B71" t="n">
-        <v>90301</v>
+        <v>90304</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8817,32 +8817,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128931880</v>
+        <v>128931877</v>
       </c>
       <c r="B72" t="n">
-        <v>96902</v>
+        <v>91299</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>53</v>
+        <v>3215</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8852,10 +8852,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>316881</v>
+        <v>316908</v>
       </c>
       <c r="R72" t="n">
-        <v>6550407</v>
+        <v>6550462</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8914,32 +8914,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128931877</v>
+        <v>128931880</v>
       </c>
       <c r="B73" t="n">
-        <v>91296</v>
+        <v>96905</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>3215</v>
+        <v>53</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8949,10 +8949,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>316908</v>
+        <v>316881</v>
       </c>
       <c r="R73" t="n">
-        <v>6550462</v>
+        <v>6550407</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -9131,7 +9131,7 @@
         <v>128931881</v>
       </c>
       <c r="B75" t="n">
-        <v>96938</v>
+        <v>96941</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         <v>128931870</v>
       </c>
       <c r="B76" t="n">
-        <v>96938</v>
+        <v>96941</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9322,10 +9322,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128931860</v>
+        <v>128931887</v>
       </c>
       <c r="B77" t="n">
-        <v>8450</v>
+        <v>96941</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9333,39 +9333,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>316968</v>
+        <v>316894</v>
       </c>
       <c r="R77" t="n">
-        <v>6550604</v>
+        <v>6550382</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9408,21 +9403,6 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -9439,32 +9419,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128931827</v>
+        <v>128931883</v>
       </c>
       <c r="B78" t="n">
-        <v>98656</v>
+        <v>96941</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>2590</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9474,10 +9454,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>316833</v>
+        <v>316864</v>
       </c>
       <c r="R78" t="n">
-        <v>6550435</v>
+        <v>6550421</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9536,10 +9516,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128931887</v>
+        <v>128931860</v>
       </c>
       <c r="B79" t="n">
-        <v>96938</v>
+        <v>8450</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9547,34 +9527,39 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>316894</v>
+        <v>316968</v>
       </c>
       <c r="R79" t="n">
-        <v>6550382</v>
+        <v>6550604</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9617,6 +9602,21 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -9633,32 +9633,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128931883</v>
+        <v>128931827</v>
       </c>
       <c r="B80" t="n">
-        <v>96938</v>
+        <v>98659</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2590</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9668,10 +9668,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>316864</v>
+        <v>316833</v>
       </c>
       <c r="R80" t="n">
-        <v>6550421</v>
+        <v>6550435</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9730,32 +9730,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128931869</v>
+        <v>128931857</v>
       </c>
       <c r="B81" t="n">
-        <v>96902</v>
+        <v>92819</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9768,7 +9768,7 @@
         <v>316962</v>
       </c>
       <c r="R81" t="n">
-        <v>6550379</v>
+        <v>6550668</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9827,32 +9827,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128931857</v>
+        <v>128931869</v>
       </c>
       <c r="B82" t="n">
-        <v>92816</v>
+        <v>96905</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9865,7 +9865,7 @@
         <v>316962</v>
       </c>
       <c r="R82" t="n">
-        <v>6550668</v>
+        <v>6550379</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9927,7 +9927,7 @@
         <v>128931878</v>
       </c>
       <c r="B83" t="n">
-        <v>96902</v>
+        <v>96905</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>128931825</v>
       </c>
       <c r="B84" t="n">
-        <v>96938</v>
+        <v>96941</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
         <v>128931874</v>
       </c>
       <c r="B85" t="n">
-        <v>96938</v>
+        <v>96941</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10215,10 +10215,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128931864</v>
+        <v>128931873</v>
       </c>
       <c r="B86" t="n">
-        <v>92854</v>
+        <v>96905</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10226,21 +10226,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5966</v>
+        <v>53</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10250,10 +10250,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>317043</v>
+        <v>316914</v>
       </c>
       <c r="R86" t="n">
-        <v>6550355</v>
+        <v>6550458</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10312,10 +10312,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128931873</v>
+        <v>128931864</v>
       </c>
       <c r="B87" t="n">
-        <v>96902</v>
+        <v>92857</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10323,21 +10323,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>53</v>
+        <v>5966</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10347,10 +10347,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>316914</v>
+        <v>317043</v>
       </c>
       <c r="R87" t="n">
-        <v>6550458</v>
+        <v>6550355</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10412,7 +10412,7 @@
         <v>128931886</v>
       </c>
       <c r="B88" t="n">
-        <v>96902</v>
+        <v>96905</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>128931872</v>
       </c>
       <c r="B90" t="n">
-        <v>96938</v>
+        <v>96941</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10723,7 +10723,7 @@
         <v>128931856</v>
       </c>
       <c r="B91" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>128931868</v>
       </c>
       <c r="B93" t="n">
-        <v>96938</v>
+        <v>96941</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>128931828</v>
       </c>
       <c r="B94" t="n">
-        <v>96938</v>
+        <v>96941</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11131,7 +11131,7 @@
         <v>128931879</v>
       </c>
       <c r="B95" t="n">
-        <v>96938</v>
+        <v>96941</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>128931826</v>
       </c>
       <c r="B96" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>128931885</v>
       </c>
       <c r="B97" t="n">
-        <v>96902</v>
+        <v>96905</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11419,10 +11419,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128931861</v>
+        <v>128931876</v>
       </c>
       <c r="B98" t="n">
-        <v>92816</v>
+        <v>4779</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11430,34 +11430,39 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4364</v>
+        <v>102306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>317004</v>
+        <v>316911</v>
       </c>
       <c r="R98" t="n">
-        <v>6550507</v>
+        <v>6550465</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11500,6 +11505,21 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
@@ -11516,10 +11536,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128931876</v>
+        <v>128931861</v>
       </c>
       <c r="B99" t="n">
-        <v>4779</v>
+        <v>92819</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11527,39 +11547,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>102306</v>
+        <v>4364</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>316911</v>
+        <v>317004</v>
       </c>
       <c r="R99" t="n">
-        <v>6550465</v>
+        <v>6550507</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11602,21 +11617,6 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ99" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK99" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
@@ -11633,10 +11633,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128931884</v>
+        <v>128931866</v>
       </c>
       <c r="B100" t="n">
-        <v>96938</v>
+        <v>8450</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11644,34 +11644,39 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>316872</v>
+        <v>317035</v>
       </c>
       <c r="R100" t="n">
-        <v>6550383</v>
+        <v>6550330</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11714,6 +11719,21 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -11730,10 +11750,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128931866</v>
+        <v>128931884</v>
       </c>
       <c r="B101" t="n">
-        <v>8450</v>
+        <v>96941</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11741,39 +11761,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>317035</v>
+        <v>316872</v>
       </c>
       <c r="R101" t="n">
-        <v>6550330</v>
+        <v>6550383</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11816,21 +11831,6 @@
       </c>
       <c r="AG101" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ101" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK101" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO101" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
@@ -11850,7 +11850,7 @@
         <v>128931829</v>
       </c>
       <c r="B102" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>128931882</v>
       </c>
       <c r="B103" t="n">
-        <v>96902</v>
+        <v>96905</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12041,32 +12041,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128931862</v>
+        <v>128931855</v>
       </c>
       <c r="B104" t="n">
-        <v>92854</v>
+        <v>90304</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5966</v>
+        <v>1596</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12076,10 +12076,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>317008</v>
+        <v>316943</v>
       </c>
       <c r="R104" t="n">
-        <v>6550497</v>
+        <v>6550676</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -12138,32 +12138,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128931855</v>
+        <v>128931862</v>
       </c>
       <c r="B105" t="n">
-        <v>90301</v>
+        <v>92857</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1596</v>
+        <v>5966</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12173,10 +12173,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>316943</v>
+        <v>317008</v>
       </c>
       <c r="R105" t="n">
-        <v>6550676</v>
+        <v>6550497</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>

--- a/artfynd/A 40826-2025 artfynd.xlsx
+++ b/artfynd/A 40826-2025 artfynd.xlsx
@@ -8720,32 +8720,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128931859</v>
+        <v>128931880</v>
       </c>
       <c r="B71" t="n">
-        <v>90304</v>
+        <v>96905</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1596</v>
+        <v>53</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8755,10 +8755,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>316972</v>
+        <v>316881</v>
       </c>
       <c r="R71" t="n">
-        <v>6550656</v>
+        <v>6550407</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8914,32 +8914,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128931880</v>
+        <v>128931859</v>
       </c>
       <c r="B73" t="n">
-        <v>96905</v>
+        <v>90304</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>53</v>
+        <v>1596</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8949,10 +8949,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>316881</v>
+        <v>316972</v>
       </c>
       <c r="R73" t="n">
-        <v>6550407</v>
+        <v>6550656</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -9128,7 +9128,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128931881</v>
+        <v>128931870</v>
       </c>
       <c r="B75" t="n">
         <v>96941</v>
@@ -9163,10 +9163,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>316881</v>
+        <v>316962</v>
       </c>
       <c r="R75" t="n">
-        <v>6550407</v>
+        <v>6550379</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9225,7 +9225,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128931870</v>
+        <v>128931881</v>
       </c>
       <c r="B76" t="n">
         <v>96941</v>
@@ -9260,10 +9260,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>316962</v>
+        <v>316881</v>
       </c>
       <c r="R76" t="n">
-        <v>6550379</v>
+        <v>6550407</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9322,7 +9322,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128931887</v>
+        <v>128931883</v>
       </c>
       <c r="B77" t="n">
         <v>96941</v>
@@ -9357,10 +9357,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>316894</v>
+        <v>316864</v>
       </c>
       <c r="R77" t="n">
-        <v>6550382</v>
+        <v>6550421</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9419,7 +9419,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128931883</v>
+        <v>128931887</v>
       </c>
       <c r="B78" t="n">
         <v>96941</v>
@@ -9454,10 +9454,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>316864</v>
+        <v>316894</v>
       </c>
       <c r="R78" t="n">
-        <v>6550421</v>
+        <v>6550382</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -10817,10 +10817,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128931863</v>
+        <v>128931868</v>
       </c>
       <c r="B92" t="n">
-        <v>8450</v>
+        <v>96941</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10828,39 +10828,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>317035</v>
+        <v>317023</v>
       </c>
       <c r="R92" t="n">
-        <v>6550369</v>
+        <v>6550315</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10903,21 +10898,6 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ92" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK92" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO92" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
@@ -10934,10 +10914,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128931868</v>
+        <v>128931863</v>
       </c>
       <c r="B93" t="n">
-        <v>96941</v>
+        <v>8450</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10945,34 +10925,39 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>317023</v>
+        <v>317035</v>
       </c>
       <c r="R93" t="n">
-        <v>6550315</v>
+        <v>6550369</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -11015,6 +11000,21 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
@@ -11031,7 +11031,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128931828</v>
+        <v>128931879</v>
       </c>
       <c r="B94" t="n">
         <v>96941</v>
@@ -11066,10 +11066,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>316830</v>
+        <v>316896</v>
       </c>
       <c r="R94" t="n">
-        <v>6550440</v>
+        <v>6550430</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -11128,7 +11128,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128931879</v>
+        <v>128931828</v>
       </c>
       <c r="B95" t="n">
         <v>96941</v>
@@ -11163,10 +11163,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>316896</v>
+        <v>316830</v>
       </c>
       <c r="R95" t="n">
-        <v>6550430</v>
+        <v>6550440</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -11419,10 +11419,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128931876</v>
+        <v>128931861</v>
       </c>
       <c r="B98" t="n">
-        <v>4779</v>
+        <v>92819</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11430,39 +11430,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>102306</v>
+        <v>4364</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>316911</v>
+        <v>317004</v>
       </c>
       <c r="R98" t="n">
-        <v>6550465</v>
+        <v>6550507</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11505,21 +11500,6 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ98" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK98" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO98" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
@@ -11536,10 +11516,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128931861</v>
+        <v>128931876</v>
       </c>
       <c r="B99" t="n">
-        <v>92819</v>
+        <v>4779</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11547,34 +11527,39 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4364</v>
+        <v>102306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>317004</v>
+        <v>316911</v>
       </c>
       <c r="R99" t="n">
-        <v>6550507</v>
+        <v>6550465</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11617,6 +11602,21 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
@@ -11633,10 +11633,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128931866</v>
+        <v>128931884</v>
       </c>
       <c r="B100" t="n">
-        <v>8450</v>
+        <v>96941</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11644,39 +11644,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>317035</v>
+        <v>316872</v>
       </c>
       <c r="R100" t="n">
-        <v>6550330</v>
+        <v>6550383</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11719,21 +11714,6 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -11750,10 +11730,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128931884</v>
+        <v>128931866</v>
       </c>
       <c r="B101" t="n">
-        <v>96941</v>
+        <v>8450</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11761,34 +11741,39 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>316872</v>
+        <v>317035</v>
       </c>
       <c r="R101" t="n">
-        <v>6550383</v>
+        <v>6550330</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11831,6 +11816,21 @@
       </c>
       <c r="AG101" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">

--- a/artfynd/A 40826-2025 artfynd.xlsx
+++ b/artfynd/A 40826-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY105"/>
+  <dimension ref="A1:AY108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9730,32 +9730,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128931857</v>
+        <v>128931869</v>
       </c>
       <c r="B81" t="n">
-        <v>92819</v>
+        <v>96905</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9768,7 +9768,7 @@
         <v>316962</v>
       </c>
       <c r="R81" t="n">
-        <v>6550668</v>
+        <v>6550379</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9827,32 +9827,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128931869</v>
+        <v>128931857</v>
       </c>
       <c r="B82" t="n">
-        <v>96905</v>
+        <v>92819</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9865,7 +9865,7 @@
         <v>316962</v>
       </c>
       <c r="R82" t="n">
-        <v>6550379</v>
+        <v>6550668</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -10215,10 +10215,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128931873</v>
+        <v>128931864</v>
       </c>
       <c r="B86" t="n">
-        <v>96905</v>
+        <v>92857</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10226,21 +10226,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>53</v>
+        <v>5966</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10250,10 +10250,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>316914</v>
+        <v>317043</v>
       </c>
       <c r="R86" t="n">
-        <v>6550458</v>
+        <v>6550355</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10312,10 +10312,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128931864</v>
+        <v>128931873</v>
       </c>
       <c r="B87" t="n">
-        <v>92857</v>
+        <v>96905</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10323,21 +10323,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5966</v>
+        <v>53</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10347,10 +10347,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>317043</v>
+        <v>316914</v>
       </c>
       <c r="R87" t="n">
-        <v>6550355</v>
+        <v>6550458</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -12233,6 +12233,312 @@
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>129221408</v>
+      </c>
+      <c r="B106" t="n">
+        <v>96941</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Norra Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>316948</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6550332</v>
+      </c>
+      <c r="S106" t="n">
+        <v>5</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>129221407</v>
+      </c>
+      <c r="B107" t="n">
+        <v>78701</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>353</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Norra Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>317005</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6550347</v>
+      </c>
+      <c r="S107" t="n">
+        <v>5</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>129221406</v>
+      </c>
+      <c r="B108" t="n">
+        <v>96941</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Norra Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>316999</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6550362</v>
+      </c>
+      <c r="S108" t="n">
+        <v>5</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40826-2025 artfynd.xlsx
+++ b/artfynd/A 40826-2025 artfynd.xlsx
@@ -8720,45 +8720,50 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128931880</v>
+        <v>128931865</v>
       </c>
       <c r="B71" t="n">
-        <v>96905</v>
+        <v>8450</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>316881</v>
+        <v>317048</v>
       </c>
       <c r="R71" t="n">
-        <v>6550407</v>
+        <v>6550340</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8801,6 +8806,21 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -8817,32 +8837,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128931877</v>
+        <v>128931859</v>
       </c>
       <c r="B72" t="n">
-        <v>91299</v>
+        <v>90304</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3215</v>
+        <v>1596</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8852,10 +8872,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>316908</v>
+        <v>316972</v>
       </c>
       <c r="R72" t="n">
-        <v>6550462</v>
+        <v>6550656</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8914,32 +8934,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128931859</v>
+        <v>128931880</v>
       </c>
       <c r="B73" t="n">
-        <v>90304</v>
+        <v>96905</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1596</v>
+        <v>53</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8949,10 +8969,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>316972</v>
+        <v>316881</v>
       </c>
       <c r="R73" t="n">
-        <v>6550656</v>
+        <v>6550407</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -9011,10 +9031,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128931865</v>
+        <v>128931877</v>
       </c>
       <c r="B74" t="n">
-        <v>8450</v>
+        <v>91299</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9022,39 +9042,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>3215</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>317048</v>
+        <v>316908</v>
       </c>
       <c r="R74" t="n">
-        <v>6550340</v>
+        <v>6550462</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9097,21 +9112,6 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -10623,10 +10623,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128931872</v>
+        <v>128931856</v>
       </c>
       <c r="B90" t="n">
-        <v>96941</v>
+        <v>92819</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10634,21 +10634,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2590</v>
+        <v>4364</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10658,10 +10658,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>316937</v>
+        <v>316947</v>
       </c>
       <c r="R90" t="n">
-        <v>6550476</v>
+        <v>6550667</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10720,10 +10720,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128931856</v>
+        <v>128931872</v>
       </c>
       <c r="B91" t="n">
-        <v>92819</v>
+        <v>96941</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10731,21 +10731,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4364</v>
+        <v>2590</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10755,10 +10755,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>316947</v>
+        <v>316937</v>
       </c>
       <c r="R91" t="n">
-        <v>6550667</v>
+        <v>6550476</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10817,10 +10817,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128931868</v>
+        <v>128931863</v>
       </c>
       <c r="B92" t="n">
-        <v>96941</v>
+        <v>8450</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10828,34 +10828,39 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>317023</v>
+        <v>317035</v>
       </c>
       <c r="R92" t="n">
-        <v>6550315</v>
+        <v>6550369</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10898,6 +10903,21 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
@@ -10914,10 +10934,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128931863</v>
+        <v>128931868</v>
       </c>
       <c r="B93" t="n">
-        <v>8450</v>
+        <v>96941</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10925,39 +10945,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>317035</v>
+        <v>317023</v>
       </c>
       <c r="R93" t="n">
-        <v>6550369</v>
+        <v>6550315</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -11000,21 +11015,6 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ93" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK93" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO93" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
@@ -11419,10 +11419,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128931861</v>
+        <v>128931876</v>
       </c>
       <c r="B98" t="n">
-        <v>92819</v>
+        <v>4779</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11430,34 +11430,39 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4364</v>
+        <v>102306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>317004</v>
+        <v>316911</v>
       </c>
       <c r="R98" t="n">
-        <v>6550507</v>
+        <v>6550465</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11500,6 +11505,21 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
@@ -11516,10 +11536,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128931876</v>
+        <v>128931861</v>
       </c>
       <c r="B99" t="n">
-        <v>4779</v>
+        <v>92819</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11527,39 +11547,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>102306</v>
+        <v>4364</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>316911</v>
+        <v>317004</v>
       </c>
       <c r="R99" t="n">
-        <v>6550465</v>
+        <v>6550507</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11602,21 +11617,6 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ99" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK99" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
@@ -11633,10 +11633,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128931884</v>
+        <v>128931866</v>
       </c>
       <c r="B100" t="n">
-        <v>96941</v>
+        <v>8450</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11644,34 +11644,39 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>316872</v>
+        <v>317035</v>
       </c>
       <c r="R100" t="n">
-        <v>6550383</v>
+        <v>6550330</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11714,6 +11719,21 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -11730,10 +11750,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128931866</v>
+        <v>128931884</v>
       </c>
       <c r="B101" t="n">
-        <v>8450</v>
+        <v>96941</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11741,39 +11761,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>317035</v>
+        <v>316872</v>
       </c>
       <c r="R101" t="n">
-        <v>6550330</v>
+        <v>6550383</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11816,21 +11831,6 @@
       </c>
       <c r="AG101" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ101" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK101" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO101" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
@@ -12041,32 +12041,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128931855</v>
+        <v>128931862</v>
       </c>
       <c r="B104" t="n">
-        <v>90304</v>
+        <v>92857</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1596</v>
+        <v>5966</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12076,10 +12076,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>316943</v>
+        <v>317008</v>
       </c>
       <c r="R104" t="n">
-        <v>6550676</v>
+        <v>6550497</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -12138,32 +12138,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128931862</v>
+        <v>128931855</v>
       </c>
       <c r="B105" t="n">
-        <v>92857</v>
+        <v>90304</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5966</v>
+        <v>1596</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12173,10 +12173,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>317008</v>
+        <v>316943</v>
       </c>
       <c r="R105" t="n">
-        <v>6550497</v>
+        <v>6550676</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>

--- a/artfynd/A 40826-2025 artfynd.xlsx
+++ b/artfynd/A 40826-2025 artfynd.xlsx
@@ -8720,10 +8720,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128931865</v>
+        <v>128931877</v>
       </c>
       <c r="B71" t="n">
-        <v>8450</v>
+        <v>91305</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8731,39 +8731,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>3215</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>317048</v>
+        <v>316908</v>
       </c>
       <c r="R71" t="n">
-        <v>6550340</v>
+        <v>6550462</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8806,21 +8801,6 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -8837,32 +8817,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128931859</v>
+        <v>128931880</v>
       </c>
       <c r="B72" t="n">
-        <v>90304</v>
+        <v>96915</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1596</v>
+        <v>53</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8872,10 +8852,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>316972</v>
+        <v>316881</v>
       </c>
       <c r="R72" t="n">
-        <v>6550656</v>
+        <v>6550407</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8934,32 +8914,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128931880</v>
+        <v>128931859</v>
       </c>
       <c r="B73" t="n">
-        <v>96905</v>
+        <v>90308</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>53</v>
+        <v>1596</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8969,10 +8949,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>316881</v>
+        <v>316972</v>
       </c>
       <c r="R73" t="n">
-        <v>6550407</v>
+        <v>6550656</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -9031,10 +9011,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128931877</v>
+        <v>128931865</v>
       </c>
       <c r="B74" t="n">
-        <v>91299</v>
+        <v>8450</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9042,34 +9022,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3215</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>316908</v>
+        <v>317048</v>
       </c>
       <c r="R74" t="n">
-        <v>6550462</v>
+        <v>6550340</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9112,6 +9097,21 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -9131,7 +9131,7 @@
         <v>128931870</v>
       </c>
       <c r="B75" t="n">
-        <v>96941</v>
+        <v>96951</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         <v>128931881</v>
       </c>
       <c r="B76" t="n">
-        <v>96941</v>
+        <v>96951</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         <v>128931883</v>
       </c>
       <c r="B77" t="n">
-        <v>96941</v>
+        <v>96951</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9422,7 +9422,7 @@
         <v>128931887</v>
       </c>
       <c r="B78" t="n">
-        <v>96941</v>
+        <v>96951</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>128931827</v>
       </c>
       <c r="B80" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9730,32 +9730,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128931869</v>
+        <v>128931857</v>
       </c>
       <c r="B81" t="n">
-        <v>96905</v>
+        <v>92826</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9768,7 +9768,7 @@
         <v>316962</v>
       </c>
       <c r="R81" t="n">
-        <v>6550379</v>
+        <v>6550668</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9827,32 +9827,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128931857</v>
+        <v>128931869</v>
       </c>
       <c r="B82" t="n">
-        <v>92819</v>
+        <v>96915</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9865,7 +9865,7 @@
         <v>316962</v>
       </c>
       <c r="R82" t="n">
-        <v>6550668</v>
+        <v>6550379</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9927,7 +9927,7 @@
         <v>128931878</v>
       </c>
       <c r="B83" t="n">
-        <v>96905</v>
+        <v>96915</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>128931825</v>
       </c>
       <c r="B84" t="n">
-        <v>96941</v>
+        <v>96951</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
         <v>128931874</v>
       </c>
       <c r="B85" t="n">
-        <v>96941</v>
+        <v>96951</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10215,10 +10215,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128931864</v>
+        <v>128931873</v>
       </c>
       <c r="B86" t="n">
-        <v>92857</v>
+        <v>96915</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10226,21 +10226,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5966</v>
+        <v>53</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10250,10 +10250,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>317043</v>
+        <v>316914</v>
       </c>
       <c r="R86" t="n">
-        <v>6550355</v>
+        <v>6550458</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10312,10 +10312,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128931873</v>
+        <v>128931864</v>
       </c>
       <c r="B87" t="n">
-        <v>96905</v>
+        <v>92864</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10323,21 +10323,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>53</v>
+        <v>5966</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10347,10 +10347,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>316914</v>
+        <v>317043</v>
       </c>
       <c r="R87" t="n">
-        <v>6550458</v>
+        <v>6550355</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10412,7 +10412,7 @@
         <v>128931886</v>
       </c>
       <c r="B88" t="n">
-        <v>96905</v>
+        <v>96915</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10623,10 +10623,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128931856</v>
+        <v>128931872</v>
       </c>
       <c r="B90" t="n">
-        <v>92819</v>
+        <v>96951</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10634,21 +10634,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4364</v>
+        <v>2590</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10658,10 +10658,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>316947</v>
+        <v>316937</v>
       </c>
       <c r="R90" t="n">
-        <v>6550667</v>
+        <v>6550476</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10720,10 +10720,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128931872</v>
+        <v>128931856</v>
       </c>
       <c r="B91" t="n">
-        <v>96941</v>
+        <v>92826</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10731,21 +10731,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2590</v>
+        <v>4364</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10755,10 +10755,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>316937</v>
+        <v>316947</v>
       </c>
       <c r="R91" t="n">
-        <v>6550476</v>
+        <v>6550667</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10817,10 +10817,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128931863</v>
+        <v>128931868</v>
       </c>
       <c r="B92" t="n">
-        <v>8450</v>
+        <v>96951</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10828,39 +10828,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>317035</v>
+        <v>317023</v>
       </c>
       <c r="R92" t="n">
-        <v>6550369</v>
+        <v>6550315</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10903,21 +10898,6 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ92" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK92" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO92" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
@@ -10934,10 +10914,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128931868</v>
+        <v>128931863</v>
       </c>
       <c r="B93" t="n">
-        <v>96941</v>
+        <v>8450</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10945,34 +10925,39 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>317023</v>
+        <v>317035</v>
       </c>
       <c r="R93" t="n">
-        <v>6550315</v>
+        <v>6550369</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -11015,6 +11000,21 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
@@ -11034,7 +11034,7 @@
         <v>128931879</v>
       </c>
       <c r="B94" t="n">
-        <v>96941</v>
+        <v>96951</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11131,7 +11131,7 @@
         <v>128931828</v>
       </c>
       <c r="B95" t="n">
-        <v>96941</v>
+        <v>96951</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>128931826</v>
       </c>
       <c r="B96" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>128931885</v>
       </c>
       <c r="B97" t="n">
-        <v>96905</v>
+        <v>96915</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11419,10 +11419,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128931876</v>
+        <v>128931861</v>
       </c>
       <c r="B98" t="n">
-        <v>4779</v>
+        <v>92826</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11430,39 +11430,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>102306</v>
+        <v>4364</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>316911</v>
+        <v>317004</v>
       </c>
       <c r="R98" t="n">
-        <v>6550465</v>
+        <v>6550507</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11505,21 +11500,6 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ98" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK98" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO98" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
@@ -11536,10 +11516,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128931861</v>
+        <v>128931876</v>
       </c>
       <c r="B99" t="n">
-        <v>92819</v>
+        <v>4779</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11547,34 +11527,39 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4364</v>
+        <v>102306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>317004</v>
+        <v>316911</v>
       </c>
       <c r="R99" t="n">
-        <v>6550507</v>
+        <v>6550465</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11617,6 +11602,21 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
@@ -11633,10 +11633,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128931866</v>
+        <v>128931884</v>
       </c>
       <c r="B100" t="n">
-        <v>8450</v>
+        <v>96951</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11644,39 +11644,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>317035</v>
+        <v>316872</v>
       </c>
       <c r="R100" t="n">
-        <v>6550330</v>
+        <v>6550383</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11719,21 +11714,6 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -11750,10 +11730,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128931884</v>
+        <v>128931866</v>
       </c>
       <c r="B101" t="n">
-        <v>96941</v>
+        <v>8450</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11761,34 +11741,39 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>316872</v>
+        <v>317035</v>
       </c>
       <c r="R101" t="n">
-        <v>6550383</v>
+        <v>6550330</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11831,6 +11816,21 @@
       </c>
       <c r="AG101" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
@@ -11850,7 +11850,7 @@
         <v>128931829</v>
       </c>
       <c r="B102" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11944,32 +11944,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128931882</v>
+        <v>128931855</v>
       </c>
       <c r="B103" t="n">
-        <v>96905</v>
+        <v>90308</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>53</v>
+        <v>1596</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11979,10 +11979,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>316864</v>
+        <v>316943</v>
       </c>
       <c r="R103" t="n">
-        <v>6550421</v>
+        <v>6550676</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -12044,7 +12044,7 @@
         <v>128931862</v>
       </c>
       <c r="B104" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12138,32 +12138,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128931855</v>
+        <v>128931882</v>
       </c>
       <c r="B105" t="n">
-        <v>90304</v>
+        <v>96915</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1596</v>
+        <v>53</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12173,10 +12173,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>316943</v>
+        <v>316864</v>
       </c>
       <c r="R105" t="n">
-        <v>6550676</v>
+        <v>6550421</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -12238,7 +12238,7 @@
         <v>129221408</v>
       </c>
       <c r="B106" t="n">
-        <v>96941</v>
+        <v>96951</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
         <v>129221407</v>
       </c>
       <c r="B107" t="n">
-        <v>78701</v>
+        <v>78705</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12447,7 +12447,7 @@
         <v>129221406</v>
       </c>
       <c r="B108" t="n">
-        <v>96941</v>
+        <v>96951</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>

--- a/artfynd/A 40826-2025 artfynd.xlsx
+++ b/artfynd/A 40826-2025 artfynd.xlsx
@@ -9730,32 +9730,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128931857</v>
+        <v>128931869</v>
       </c>
       <c r="B81" t="n">
-        <v>92826</v>
+        <v>96915</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9768,7 +9768,7 @@
         <v>316962</v>
       </c>
       <c r="R81" t="n">
-        <v>6550668</v>
+        <v>6550379</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9827,32 +9827,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128931869</v>
+        <v>128931857</v>
       </c>
       <c r="B82" t="n">
-        <v>96915</v>
+        <v>92826</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9865,7 +9865,7 @@
         <v>316962</v>
       </c>
       <c r="R82" t="n">
-        <v>6550379</v>
+        <v>6550668</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -12041,10 +12041,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128931862</v>
+        <v>128931882</v>
       </c>
       <c r="B104" t="n">
-        <v>92864</v>
+        <v>96915</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12052,21 +12052,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5966</v>
+        <v>53</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12076,10 +12076,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>317008</v>
+        <v>316864</v>
       </c>
       <c r="R104" t="n">
-        <v>6550497</v>
+        <v>6550421</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -12138,10 +12138,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128931882</v>
+        <v>128931862</v>
       </c>
       <c r="B105" t="n">
-        <v>96915</v>
+        <v>92864</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12149,21 +12149,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>53</v>
+        <v>5966</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12173,10 +12173,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>316864</v>
+        <v>317008</v>
       </c>
       <c r="R105" t="n">
-        <v>6550421</v>
+        <v>6550497</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>

--- a/artfynd/A 40826-2025 artfynd.xlsx
+++ b/artfynd/A 40826-2025 artfynd.xlsx
@@ -8720,32 +8720,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128931877</v>
+        <v>128931880</v>
       </c>
       <c r="B71" t="n">
-        <v>91305</v>
+        <v>96922</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3215</v>
+        <v>53</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8755,10 +8755,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>316908</v>
+        <v>316881</v>
       </c>
       <c r="R71" t="n">
-        <v>6550462</v>
+        <v>6550407</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8817,32 +8817,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128931880</v>
+        <v>128931859</v>
       </c>
       <c r="B72" t="n">
-        <v>96915</v>
+        <v>90315</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>53</v>
+        <v>1596</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8852,10 +8852,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>316881</v>
+        <v>316972</v>
       </c>
       <c r="R72" t="n">
-        <v>6550407</v>
+        <v>6550656</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8914,32 +8914,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128931859</v>
+        <v>128931877</v>
       </c>
       <c r="B73" t="n">
-        <v>90308</v>
+        <v>91312</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1596</v>
+        <v>3215</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8949,10 +8949,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>316972</v>
+        <v>316908</v>
       </c>
       <c r="R73" t="n">
-        <v>6550656</v>
+        <v>6550462</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -9131,7 +9131,7 @@
         <v>128931870</v>
       </c>
       <c r="B75" t="n">
-        <v>96951</v>
+        <v>96958</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         <v>128931881</v>
       </c>
       <c r="B76" t="n">
-        <v>96951</v>
+        <v>96958</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9322,10 +9322,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128931883</v>
+        <v>128931860</v>
       </c>
       <c r="B77" t="n">
-        <v>96951</v>
+        <v>8450</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9333,34 +9333,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>316864</v>
+        <v>316968</v>
       </c>
       <c r="R77" t="n">
-        <v>6550421</v>
+        <v>6550604</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9403,6 +9408,21 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -9419,32 +9439,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128931887</v>
+        <v>128931827</v>
       </c>
       <c r="B78" t="n">
-        <v>96951</v>
+        <v>98676</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2590</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9454,10 +9474,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>316894</v>
+        <v>316833</v>
       </c>
       <c r="R78" t="n">
-        <v>6550382</v>
+        <v>6550435</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9516,10 +9536,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128931860</v>
+        <v>128931883</v>
       </c>
       <c r="B79" t="n">
-        <v>8450</v>
+        <v>96958</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9527,39 +9547,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>316968</v>
+        <v>316864</v>
       </c>
       <c r="R79" t="n">
-        <v>6550604</v>
+        <v>6550421</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9602,21 +9617,6 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -9633,32 +9633,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128931827</v>
+        <v>128931887</v>
       </c>
       <c r="B80" t="n">
-        <v>98669</v>
+        <v>96958</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>2590</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9668,10 +9668,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>316833</v>
+        <v>316894</v>
       </c>
       <c r="R80" t="n">
-        <v>6550435</v>
+        <v>6550382</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9733,7 +9733,7 @@
         <v>128931869</v>
       </c>
       <c r="B81" t="n">
-        <v>96915</v>
+        <v>96922</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>128931857</v>
       </c>
       <c r="B82" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>128931878</v>
       </c>
       <c r="B83" t="n">
-        <v>96915</v>
+        <v>96922</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>128931825</v>
       </c>
       <c r="B84" t="n">
-        <v>96951</v>
+        <v>96958</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
         <v>128931874</v>
       </c>
       <c r="B85" t="n">
-        <v>96951</v>
+        <v>96958</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10218,7 +10218,7 @@
         <v>128931873</v>
       </c>
       <c r="B86" t="n">
-        <v>96915</v>
+        <v>96922</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10315,7 +10315,7 @@
         <v>128931864</v>
       </c>
       <c r="B87" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10412,7 +10412,7 @@
         <v>128931886</v>
       </c>
       <c r="B88" t="n">
-        <v>96915</v>
+        <v>96922</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>128931872</v>
       </c>
       <c r="B90" t="n">
-        <v>96951</v>
+        <v>96958</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10723,7 +10723,7 @@
         <v>128931856</v>
       </c>
       <c r="B91" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10820,7 +10820,7 @@
         <v>128931868</v>
       </c>
       <c r="B92" t="n">
-        <v>96951</v>
+        <v>96958</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>128931879</v>
       </c>
       <c r="B94" t="n">
-        <v>96951</v>
+        <v>96958</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11131,7 +11131,7 @@
         <v>128931828</v>
       </c>
       <c r="B95" t="n">
-        <v>96951</v>
+        <v>96958</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>128931826</v>
       </c>
       <c r="B96" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>128931885</v>
       </c>
       <c r="B97" t="n">
-        <v>96915</v>
+        <v>96922</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>128931861</v>
       </c>
       <c r="B98" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11636,7 +11636,7 @@
         <v>128931884</v>
       </c>
       <c r="B100" t="n">
-        <v>96951</v>
+        <v>96958</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11850,7 +11850,7 @@
         <v>128931829</v>
       </c>
       <c r="B102" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11944,32 +11944,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128931855</v>
+        <v>128931882</v>
       </c>
       <c r="B103" t="n">
-        <v>90308</v>
+        <v>96922</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1596</v>
+        <v>53</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11979,10 +11979,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>316943</v>
+        <v>316864</v>
       </c>
       <c r="R103" t="n">
-        <v>6550676</v>
+        <v>6550421</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -12041,32 +12041,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128931882</v>
+        <v>128931855</v>
       </c>
       <c r="B104" t="n">
-        <v>96915</v>
+        <v>90315</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>53</v>
+        <v>1596</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12076,10 +12076,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>316864</v>
+        <v>316943</v>
       </c>
       <c r="R104" t="n">
-        <v>6550421</v>
+        <v>6550676</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -12141,7 +12141,7 @@
         <v>128931862</v>
       </c>
       <c r="B105" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12238,7 +12238,7 @@
         <v>129221408</v>
       </c>
       <c r="B106" t="n">
-        <v>96951</v>
+        <v>96958</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12447,7 +12447,7 @@
         <v>129221406</v>
       </c>
       <c r="B108" t="n">
-        <v>96951</v>
+        <v>96958</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>

--- a/artfynd/A 40826-2025 artfynd.xlsx
+++ b/artfynd/A 40826-2025 artfynd.xlsx
@@ -8720,45 +8720,50 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128931880</v>
+        <v>128931865</v>
       </c>
       <c r="B71" t="n">
-        <v>96922</v>
+        <v>8450</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>316881</v>
+        <v>317048</v>
       </c>
       <c r="R71" t="n">
-        <v>6550407</v>
+        <v>6550340</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8801,6 +8806,21 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -8817,32 +8837,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128931859</v>
+        <v>128931877</v>
       </c>
       <c r="B72" t="n">
-        <v>90315</v>
+        <v>91314</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1596</v>
+        <v>3215</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8852,10 +8872,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>316972</v>
+        <v>316908</v>
       </c>
       <c r="R72" t="n">
-        <v>6550656</v>
+        <v>6550462</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8914,32 +8934,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128931877</v>
+        <v>128931859</v>
       </c>
       <c r="B73" t="n">
-        <v>91312</v>
+        <v>90317</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>3215</v>
+        <v>1596</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8949,10 +8969,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>316908</v>
+        <v>316972</v>
       </c>
       <c r="R73" t="n">
-        <v>6550462</v>
+        <v>6550656</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -9011,50 +9031,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128931865</v>
+        <v>128931880</v>
       </c>
       <c r="B74" t="n">
-        <v>8450</v>
+        <v>96924</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>317048</v>
+        <v>316881</v>
       </c>
       <c r="R74" t="n">
-        <v>6550340</v>
+        <v>6550407</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9097,21 +9112,6 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -9131,7 +9131,7 @@
         <v>128931870</v>
       </c>
       <c r="B75" t="n">
-        <v>96958</v>
+        <v>96960</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         <v>128931881</v>
       </c>
       <c r="B76" t="n">
-        <v>96958</v>
+        <v>96960</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9322,10 +9322,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128931860</v>
+        <v>128931883</v>
       </c>
       <c r="B77" t="n">
-        <v>8450</v>
+        <v>96960</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9333,39 +9333,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>316968</v>
+        <v>316864</v>
       </c>
       <c r="R77" t="n">
-        <v>6550604</v>
+        <v>6550421</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9408,21 +9403,6 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -9439,32 +9419,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128931827</v>
+        <v>128931887</v>
       </c>
       <c r="B78" t="n">
-        <v>98676</v>
+        <v>96960</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>2590</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9474,10 +9454,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>316833</v>
+        <v>316894</v>
       </c>
       <c r="R78" t="n">
-        <v>6550435</v>
+        <v>6550382</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9536,10 +9516,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128931883</v>
+        <v>128931860</v>
       </c>
       <c r="B79" t="n">
-        <v>96958</v>
+        <v>8450</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9547,34 +9527,39 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>316864</v>
+        <v>316968</v>
       </c>
       <c r="R79" t="n">
-        <v>6550421</v>
+        <v>6550604</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9617,6 +9602,21 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -9633,32 +9633,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128931887</v>
+        <v>128931827</v>
       </c>
       <c r="B80" t="n">
-        <v>96958</v>
+        <v>98678</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2590</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9668,10 +9668,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>316894</v>
+        <v>316833</v>
       </c>
       <c r="R80" t="n">
-        <v>6550382</v>
+        <v>6550435</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9730,32 +9730,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128931869</v>
+        <v>128931857</v>
       </c>
       <c r="B81" t="n">
-        <v>96922</v>
+        <v>92835</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9768,7 +9768,7 @@
         <v>316962</v>
       </c>
       <c r="R81" t="n">
-        <v>6550379</v>
+        <v>6550668</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9827,32 +9827,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128931857</v>
+        <v>128931869</v>
       </c>
       <c r="B82" t="n">
-        <v>92833</v>
+        <v>96924</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9865,7 +9865,7 @@
         <v>316962</v>
       </c>
       <c r="R82" t="n">
-        <v>6550668</v>
+        <v>6550379</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9924,32 +9924,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128931878</v>
+        <v>128931825</v>
       </c>
       <c r="B83" t="n">
-        <v>96922</v>
+        <v>96960</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>53</v>
+        <v>2590</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9959,10 +9959,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>316896</v>
+        <v>316831</v>
       </c>
       <c r="R83" t="n">
-        <v>6550430</v>
+        <v>6550424</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -10021,10 +10021,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128931825</v>
+        <v>128931874</v>
       </c>
       <c r="B84" t="n">
-        <v>96958</v>
+        <v>96960</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10056,10 +10056,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>316831</v>
+        <v>316914</v>
       </c>
       <c r="R84" t="n">
-        <v>6550424</v>
+        <v>6550458</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -10118,32 +10118,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128931874</v>
+        <v>128931878</v>
       </c>
       <c r="B85" t="n">
-        <v>96958</v>
+        <v>96924</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2590</v>
+        <v>53</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10153,10 +10153,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>316914</v>
+        <v>316896</v>
       </c>
       <c r="R85" t="n">
-        <v>6550458</v>
+        <v>6550430</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -10215,10 +10215,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128931873</v>
+        <v>128931864</v>
       </c>
       <c r="B86" t="n">
-        <v>96922</v>
+        <v>92873</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10226,21 +10226,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>53</v>
+        <v>5966</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10250,10 +10250,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>316914</v>
+        <v>317043</v>
       </c>
       <c r="R86" t="n">
-        <v>6550458</v>
+        <v>6550355</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10312,10 +10312,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128931864</v>
+        <v>128931873</v>
       </c>
       <c r="B87" t="n">
-        <v>92871</v>
+        <v>96924</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10323,21 +10323,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5966</v>
+        <v>53</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10347,10 +10347,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>317043</v>
+        <v>316914</v>
       </c>
       <c r="R87" t="n">
-        <v>6550355</v>
+        <v>6550458</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10412,7 +10412,7 @@
         <v>128931886</v>
       </c>
       <c r="B88" t="n">
-        <v>96922</v>
+        <v>96924</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10623,10 +10623,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128931872</v>
+        <v>128931856</v>
       </c>
       <c r="B90" t="n">
-        <v>96958</v>
+        <v>92835</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10634,21 +10634,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2590</v>
+        <v>4364</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10658,10 +10658,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>316937</v>
+        <v>316947</v>
       </c>
       <c r="R90" t="n">
-        <v>6550476</v>
+        <v>6550667</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10720,10 +10720,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128931856</v>
+        <v>128931872</v>
       </c>
       <c r="B91" t="n">
-        <v>92833</v>
+        <v>96960</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10731,21 +10731,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4364</v>
+        <v>2590</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10755,10 +10755,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>316947</v>
+        <v>316937</v>
       </c>
       <c r="R91" t="n">
-        <v>6550667</v>
+        <v>6550476</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10820,7 +10820,7 @@
         <v>128931868</v>
       </c>
       <c r="B92" t="n">
-        <v>96958</v>
+        <v>96960</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>128931879</v>
       </c>
       <c r="B94" t="n">
-        <v>96958</v>
+        <v>96960</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11131,7 +11131,7 @@
         <v>128931828</v>
       </c>
       <c r="B95" t="n">
-        <v>96958</v>
+        <v>96960</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>128931826</v>
       </c>
       <c r="B96" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>128931885</v>
       </c>
       <c r="B97" t="n">
-        <v>96922</v>
+        <v>96924</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>128931861</v>
       </c>
       <c r="B98" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11633,10 +11633,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128931884</v>
+        <v>128931866</v>
       </c>
       <c r="B100" t="n">
-        <v>96958</v>
+        <v>8450</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11644,34 +11644,39 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>316872</v>
+        <v>317035</v>
       </c>
       <c r="R100" t="n">
-        <v>6550383</v>
+        <v>6550330</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11714,6 +11719,21 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -11730,10 +11750,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128931866</v>
+        <v>128931884</v>
       </c>
       <c r="B101" t="n">
-        <v>8450</v>
+        <v>96960</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11741,39 +11761,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>317035</v>
+        <v>316872</v>
       </c>
       <c r="R101" t="n">
-        <v>6550330</v>
+        <v>6550383</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11816,21 +11831,6 @@
       </c>
       <c r="AG101" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ101" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK101" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO101" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
@@ -11850,7 +11850,7 @@
         <v>128931829</v>
       </c>
       <c r="B102" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11944,32 +11944,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128931882</v>
+        <v>128931855</v>
       </c>
       <c r="B103" t="n">
-        <v>96922</v>
+        <v>90317</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>53</v>
+        <v>1596</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11979,10 +11979,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>316864</v>
+        <v>316943</v>
       </c>
       <c r="R103" t="n">
-        <v>6550421</v>
+        <v>6550676</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -12041,32 +12041,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128931855</v>
+        <v>128931862</v>
       </c>
       <c r="B104" t="n">
-        <v>90315</v>
+        <v>92873</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1596</v>
+        <v>5966</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12076,10 +12076,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>316943</v>
+        <v>317008</v>
       </c>
       <c r="R104" t="n">
-        <v>6550676</v>
+        <v>6550497</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -12138,10 +12138,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128931862</v>
+        <v>128931882</v>
       </c>
       <c r="B105" t="n">
-        <v>92871</v>
+        <v>96924</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12149,21 +12149,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5966</v>
+        <v>53</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12173,10 +12173,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>317008</v>
+        <v>316864</v>
       </c>
       <c r="R105" t="n">
-        <v>6550497</v>
+        <v>6550421</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -12238,7 +12238,7 @@
         <v>129221408</v>
       </c>
       <c r="B106" t="n">
-        <v>96958</v>
+        <v>96960</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
         <v>129221407</v>
       </c>
       <c r="B107" t="n">
-        <v>78705</v>
+        <v>78707</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12447,7 +12447,7 @@
         <v>129221406</v>
       </c>
       <c r="B108" t="n">
-        <v>96958</v>
+        <v>96960</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>

--- a/artfynd/A 40826-2025 artfynd.xlsx
+++ b/artfynd/A 40826-2025 artfynd.xlsx
@@ -8720,50 +8720,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128931865</v>
+        <v>128931880</v>
       </c>
       <c r="B71" t="n">
-        <v>8450</v>
+        <v>96924</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>317048</v>
+        <v>316881</v>
       </c>
       <c r="R71" t="n">
-        <v>6550340</v>
+        <v>6550407</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8806,21 +8801,6 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -9031,45 +9011,50 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128931880</v>
+        <v>128931865</v>
       </c>
       <c r="B74" t="n">
-        <v>96924</v>
+        <v>8450</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>316881</v>
+        <v>317048</v>
       </c>
       <c r="R74" t="n">
-        <v>6550407</v>
+        <v>6550340</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9112,6 +9097,21 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -9322,32 +9322,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128931883</v>
+        <v>128931827</v>
       </c>
       <c r="B77" t="n">
-        <v>96960</v>
+        <v>98678</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2590</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9357,10 +9357,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>316864</v>
+        <v>316833</v>
       </c>
       <c r="R77" t="n">
-        <v>6550421</v>
+        <v>6550435</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9419,10 +9419,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128931887</v>
+        <v>128931860</v>
       </c>
       <c r="B78" t="n">
-        <v>96960</v>
+        <v>8450</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9430,34 +9430,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>316894</v>
+        <v>316968</v>
       </c>
       <c r="R78" t="n">
-        <v>6550382</v>
+        <v>6550604</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9500,6 +9505,21 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -9516,10 +9536,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128931860</v>
+        <v>128931883</v>
       </c>
       <c r="B79" t="n">
-        <v>8450</v>
+        <v>96960</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9527,39 +9547,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>316968</v>
+        <v>316864</v>
       </c>
       <c r="R79" t="n">
-        <v>6550604</v>
+        <v>6550421</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9602,21 +9617,6 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -9633,32 +9633,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128931827</v>
+        <v>128931887</v>
       </c>
       <c r="B80" t="n">
-        <v>98678</v>
+        <v>96960</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>2590</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9668,10 +9668,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>316833</v>
+        <v>316894</v>
       </c>
       <c r="R80" t="n">
-        <v>6550435</v>
+        <v>6550382</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9730,32 +9730,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128931857</v>
+        <v>128931869</v>
       </c>
       <c r="B81" t="n">
-        <v>92835</v>
+        <v>96924</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9768,7 +9768,7 @@
         <v>316962</v>
       </c>
       <c r="R81" t="n">
-        <v>6550668</v>
+        <v>6550379</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9827,32 +9827,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128931869</v>
+        <v>128931857</v>
       </c>
       <c r="B82" t="n">
-        <v>96924</v>
+        <v>92835</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9865,7 +9865,7 @@
         <v>316962</v>
       </c>
       <c r="R82" t="n">
-        <v>6550379</v>
+        <v>6550668</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -10215,10 +10215,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128931864</v>
+        <v>128931873</v>
       </c>
       <c r="B86" t="n">
-        <v>92873</v>
+        <v>96924</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10226,21 +10226,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5966</v>
+        <v>53</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10250,10 +10250,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>317043</v>
+        <v>316914</v>
       </c>
       <c r="R86" t="n">
-        <v>6550355</v>
+        <v>6550458</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10312,10 +10312,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128931873</v>
+        <v>128931864</v>
       </c>
       <c r="B87" t="n">
-        <v>96924</v>
+        <v>92873</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10323,21 +10323,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>53</v>
+        <v>5966</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10347,10 +10347,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>316914</v>
+        <v>317043</v>
       </c>
       <c r="R87" t="n">
-        <v>6550458</v>
+        <v>6550355</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10623,10 +10623,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128931856</v>
+        <v>128931872</v>
       </c>
       <c r="B90" t="n">
-        <v>92835</v>
+        <v>96960</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10634,21 +10634,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4364</v>
+        <v>2590</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10658,10 +10658,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>316947</v>
+        <v>316937</v>
       </c>
       <c r="R90" t="n">
-        <v>6550667</v>
+        <v>6550476</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10720,10 +10720,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128931872</v>
+        <v>128931856</v>
       </c>
       <c r="B91" t="n">
-        <v>96960</v>
+        <v>92835</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10731,21 +10731,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2590</v>
+        <v>4364</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10755,10 +10755,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>316937</v>
+        <v>316947</v>
       </c>
       <c r="R91" t="n">
-        <v>6550476</v>
+        <v>6550667</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10817,10 +10817,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128931868</v>
+        <v>128931863</v>
       </c>
       <c r="B92" t="n">
-        <v>96960</v>
+        <v>8450</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10828,34 +10828,39 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>317023</v>
+        <v>317035</v>
       </c>
       <c r="R92" t="n">
-        <v>6550315</v>
+        <v>6550369</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10898,6 +10903,21 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
@@ -10914,10 +10934,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128931863</v>
+        <v>128931868</v>
       </c>
       <c r="B93" t="n">
-        <v>8450</v>
+        <v>96960</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10925,39 +10945,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>317035</v>
+        <v>317023</v>
       </c>
       <c r="R93" t="n">
-        <v>6550369</v>
+        <v>6550315</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -11000,21 +11015,6 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ93" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK93" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO93" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
@@ -11031,32 +11031,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128931879</v>
+        <v>128931826</v>
       </c>
       <c r="B94" t="n">
-        <v>96960</v>
+        <v>98678</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2590</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11066,10 +11066,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>316896</v>
+        <v>316835</v>
       </c>
       <c r="R94" t="n">
-        <v>6550430</v>
+        <v>6550425</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -11128,7 +11128,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128931828</v>
+        <v>128931879</v>
       </c>
       <c r="B95" t="n">
         <v>96960</v>
@@ -11163,10 +11163,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>316830</v>
+        <v>316896</v>
       </c>
       <c r="R95" t="n">
-        <v>6550440</v>
+        <v>6550430</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -11225,32 +11225,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128931826</v>
+        <v>128931828</v>
       </c>
       <c r="B96" t="n">
-        <v>98678</v>
+        <v>96960</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>2590</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11260,10 +11260,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>316835</v>
+        <v>316830</v>
       </c>
       <c r="R96" t="n">
-        <v>6550425</v>
+        <v>6550440</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11419,10 +11419,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128931861</v>
+        <v>128931876</v>
       </c>
       <c r="B98" t="n">
-        <v>92835</v>
+        <v>4779</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11430,34 +11430,39 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4364</v>
+        <v>102306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>317004</v>
+        <v>316911</v>
       </c>
       <c r="R98" t="n">
-        <v>6550507</v>
+        <v>6550465</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11500,6 +11505,21 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
@@ -11516,10 +11536,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128931876</v>
+        <v>128931861</v>
       </c>
       <c r="B99" t="n">
-        <v>4779</v>
+        <v>92835</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11527,39 +11547,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>102306</v>
+        <v>4364</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>316911</v>
+        <v>317004</v>
       </c>
       <c r="R99" t="n">
-        <v>6550465</v>
+        <v>6550507</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11602,21 +11617,6 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ99" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK99" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
@@ -11633,10 +11633,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128931866</v>
+        <v>128931884</v>
       </c>
       <c r="B100" t="n">
-        <v>8450</v>
+        <v>96960</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11644,39 +11644,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>317035</v>
+        <v>316872</v>
       </c>
       <c r="R100" t="n">
-        <v>6550330</v>
+        <v>6550383</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11719,21 +11714,6 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -11750,10 +11730,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128931884</v>
+        <v>128931866</v>
       </c>
       <c r="B101" t="n">
-        <v>96960</v>
+        <v>8450</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11761,34 +11741,39 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>316872</v>
+        <v>317035</v>
       </c>
       <c r="R101" t="n">
-        <v>6550383</v>
+        <v>6550330</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11831,6 +11816,21 @@
       </c>
       <c r="AG101" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
@@ -11944,32 +11944,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128931855</v>
+        <v>128931882</v>
       </c>
       <c r="B103" t="n">
-        <v>90317</v>
+        <v>96924</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1596</v>
+        <v>53</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11979,10 +11979,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>316943</v>
+        <v>316864</v>
       </c>
       <c r="R103" t="n">
-        <v>6550676</v>
+        <v>6550421</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -12041,32 +12041,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128931862</v>
+        <v>128931855</v>
       </c>
       <c r="B104" t="n">
-        <v>92873</v>
+        <v>90317</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5966</v>
+        <v>1596</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12076,10 +12076,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>317008</v>
+        <v>316943</v>
       </c>
       <c r="R104" t="n">
-        <v>6550497</v>
+        <v>6550676</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -12138,10 +12138,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128931882</v>
+        <v>128931862</v>
       </c>
       <c r="B105" t="n">
-        <v>96924</v>
+        <v>92873</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12149,21 +12149,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>53</v>
+        <v>5966</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12173,10 +12173,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>316864</v>
+        <v>317008</v>
       </c>
       <c r="R105" t="n">
-        <v>6550421</v>
+        <v>6550497</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>

--- a/artfynd/A 40826-2025 artfynd.xlsx
+++ b/artfynd/A 40826-2025 artfynd.xlsx
@@ -8720,45 +8720,50 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128931880</v>
+        <v>128931865</v>
       </c>
       <c r="B71" t="n">
-        <v>96924</v>
+        <v>8450</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>316881</v>
+        <v>317048</v>
       </c>
       <c r="R71" t="n">
-        <v>6550407</v>
+        <v>6550340</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8801,6 +8806,21 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -8817,32 +8837,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128931877</v>
+        <v>128931880</v>
       </c>
       <c r="B72" t="n">
-        <v>91314</v>
+        <v>96924</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3215</v>
+        <v>53</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8852,10 +8872,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>316908</v>
+        <v>316881</v>
       </c>
       <c r="R72" t="n">
-        <v>6550462</v>
+        <v>6550407</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8914,32 +8934,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128931859</v>
+        <v>128931877</v>
       </c>
       <c r="B73" t="n">
-        <v>90317</v>
+        <v>91314</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1596</v>
+        <v>3215</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8949,10 +8969,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>316972</v>
+        <v>316908</v>
       </c>
       <c r="R73" t="n">
-        <v>6550656</v>
+        <v>6550462</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -9011,50 +9031,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128931865</v>
+        <v>128931859</v>
       </c>
       <c r="B74" t="n">
-        <v>8450</v>
+        <v>90317</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>1596</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>317048</v>
+        <v>316972</v>
       </c>
       <c r="R74" t="n">
-        <v>6550340</v>
+        <v>6550656</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9097,21 +9112,6 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -9322,32 +9322,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128931827</v>
+        <v>128931883</v>
       </c>
       <c r="B77" t="n">
-        <v>98678</v>
+        <v>96960</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>2590</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9357,10 +9357,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>316833</v>
+        <v>316864</v>
       </c>
       <c r="R77" t="n">
-        <v>6550435</v>
+        <v>6550421</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9419,10 +9419,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128931860</v>
+        <v>128931887</v>
       </c>
       <c r="B78" t="n">
-        <v>8450</v>
+        <v>96960</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9430,39 +9430,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>316968</v>
+        <v>316894</v>
       </c>
       <c r="R78" t="n">
-        <v>6550604</v>
+        <v>6550382</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9505,21 +9500,6 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -9536,32 +9516,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128931883</v>
+        <v>128931827</v>
       </c>
       <c r="B79" t="n">
-        <v>96960</v>
+        <v>98678</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2590</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9571,10 +9551,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>316864</v>
+        <v>316833</v>
       </c>
       <c r="R79" t="n">
-        <v>6550421</v>
+        <v>6550435</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9633,10 +9613,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128931887</v>
+        <v>128931860</v>
       </c>
       <c r="B80" t="n">
-        <v>96960</v>
+        <v>8450</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9644,34 +9624,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>316894</v>
+        <v>316968</v>
       </c>
       <c r="R80" t="n">
-        <v>6550382</v>
+        <v>6550604</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9714,6 +9699,21 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">

--- a/artfynd/A 40826-2025 artfynd.xlsx
+++ b/artfynd/A 40826-2025 artfynd.xlsx
@@ -8720,50 +8720,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128931865</v>
+        <v>128931880</v>
       </c>
       <c r="B71" t="n">
-        <v>8450</v>
+        <v>96950</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>317048</v>
+        <v>316881</v>
       </c>
       <c r="R71" t="n">
-        <v>6550340</v>
+        <v>6550407</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8806,21 +8801,6 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -8837,32 +8817,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128931880</v>
+        <v>128931859</v>
       </c>
       <c r="B72" t="n">
-        <v>96924</v>
+        <v>90318</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>53</v>
+        <v>1596</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8872,10 +8852,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>316881</v>
+        <v>316972</v>
       </c>
       <c r="R72" t="n">
-        <v>6550407</v>
+        <v>6550656</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8937,7 +8917,7 @@
         <v>128931877</v>
       </c>
       <c r="B73" t="n">
-        <v>91314</v>
+        <v>91313</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9031,45 +9011,50 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128931859</v>
+        <v>128931865</v>
       </c>
       <c r="B74" t="n">
-        <v>90317</v>
+        <v>8450</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1596</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>316972</v>
+        <v>317048</v>
       </c>
       <c r="R74" t="n">
-        <v>6550656</v>
+        <v>6550340</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9112,6 +9097,21 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -9128,10 +9128,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128931870</v>
+        <v>128931881</v>
       </c>
       <c r="B75" t="n">
-        <v>96960</v>
+        <v>96986</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9163,10 +9163,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>316962</v>
+        <v>316881</v>
       </c>
       <c r="R75" t="n">
-        <v>6550379</v>
+        <v>6550407</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9225,10 +9225,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128931881</v>
+        <v>128931870</v>
       </c>
       <c r="B76" t="n">
-        <v>96960</v>
+        <v>96986</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9260,10 +9260,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>316881</v>
+        <v>316962</v>
       </c>
       <c r="R76" t="n">
-        <v>6550407</v>
+        <v>6550379</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9322,10 +9322,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128931883</v>
+        <v>128931887</v>
       </c>
       <c r="B77" t="n">
-        <v>96960</v>
+        <v>96986</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9357,10 +9357,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>316864</v>
+        <v>316894</v>
       </c>
       <c r="R77" t="n">
-        <v>6550421</v>
+        <v>6550382</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9419,10 +9419,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128931887</v>
+        <v>128931883</v>
       </c>
       <c r="B78" t="n">
-        <v>96960</v>
+        <v>96986</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9454,10 +9454,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>316894</v>
+        <v>316864</v>
       </c>
       <c r="R78" t="n">
-        <v>6550382</v>
+        <v>6550421</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9516,45 +9516,50 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128931827</v>
+        <v>128931860</v>
       </c>
       <c r="B79" t="n">
-        <v>98678</v>
+        <v>8450</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>316833</v>
+        <v>316968</v>
       </c>
       <c r="R79" t="n">
-        <v>6550435</v>
+        <v>6550604</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9597,6 +9602,21 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -9613,50 +9633,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128931860</v>
+        <v>128931827</v>
       </c>
       <c r="B80" t="n">
-        <v>8450</v>
+        <v>98704</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>316968</v>
+        <v>316833</v>
       </c>
       <c r="R80" t="n">
-        <v>6550604</v>
+        <v>6550435</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9699,21 +9714,6 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -9730,32 +9730,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128931869</v>
+        <v>128931857</v>
       </c>
       <c r="B81" t="n">
-        <v>96924</v>
+        <v>92821</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9768,7 +9768,7 @@
         <v>316962</v>
       </c>
       <c r="R81" t="n">
-        <v>6550379</v>
+        <v>6550668</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9827,32 +9827,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128931857</v>
+        <v>128931869</v>
       </c>
       <c r="B82" t="n">
-        <v>92835</v>
+        <v>96950</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9865,7 +9865,7 @@
         <v>316962</v>
       </c>
       <c r="R82" t="n">
-        <v>6550668</v>
+        <v>6550379</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9924,32 +9924,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128931825</v>
+        <v>128931878</v>
       </c>
       <c r="B83" t="n">
-        <v>96960</v>
+        <v>96950</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2590</v>
+        <v>53</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9959,10 +9959,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>316831</v>
+        <v>316896</v>
       </c>
       <c r="R83" t="n">
-        <v>6550424</v>
+        <v>6550430</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -10021,10 +10021,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128931874</v>
+        <v>128931825</v>
       </c>
       <c r="B84" t="n">
-        <v>96960</v>
+        <v>96986</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10056,10 +10056,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>316914</v>
+        <v>316831</v>
       </c>
       <c r="R84" t="n">
-        <v>6550458</v>
+        <v>6550424</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -10118,32 +10118,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128931878</v>
+        <v>128931874</v>
       </c>
       <c r="B85" t="n">
-        <v>96924</v>
+        <v>96986</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>53</v>
+        <v>2590</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10153,10 +10153,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>316896</v>
+        <v>316914</v>
       </c>
       <c r="R85" t="n">
-        <v>6550430</v>
+        <v>6550458</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -10218,7 +10218,7 @@
         <v>128931873</v>
       </c>
       <c r="B86" t="n">
-        <v>96924</v>
+        <v>96950</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10315,7 +10315,7 @@
         <v>128931864</v>
       </c>
       <c r="B87" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10412,7 +10412,7 @@
         <v>128931886</v>
       </c>
       <c r="B88" t="n">
-        <v>96924</v>
+        <v>96950</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10623,10 +10623,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128931872</v>
+        <v>128931856</v>
       </c>
       <c r="B90" t="n">
-        <v>96960</v>
+        <v>92821</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10634,21 +10634,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2590</v>
+        <v>4364</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10658,10 +10658,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>316937</v>
+        <v>316947</v>
       </c>
       <c r="R90" t="n">
-        <v>6550476</v>
+        <v>6550667</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10720,10 +10720,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128931856</v>
+        <v>128931872</v>
       </c>
       <c r="B91" t="n">
-        <v>92835</v>
+        <v>96986</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10731,21 +10731,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4364</v>
+        <v>2590</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10755,10 +10755,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>316947</v>
+        <v>316937</v>
       </c>
       <c r="R91" t="n">
-        <v>6550667</v>
+        <v>6550476</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10817,10 +10817,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128931863</v>
+        <v>128931868</v>
       </c>
       <c r="B92" t="n">
-        <v>8450</v>
+        <v>96986</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10828,39 +10828,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>317035</v>
+        <v>317023</v>
       </c>
       <c r="R92" t="n">
-        <v>6550369</v>
+        <v>6550315</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10903,21 +10898,6 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ92" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK92" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO92" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
@@ -10934,10 +10914,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128931868</v>
+        <v>128931863</v>
       </c>
       <c r="B93" t="n">
-        <v>96960</v>
+        <v>8450</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10945,34 +10925,39 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>317023</v>
+        <v>317035</v>
       </c>
       <c r="R93" t="n">
-        <v>6550315</v>
+        <v>6550369</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -11015,6 +11000,21 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
@@ -11034,7 +11034,7 @@
         <v>128931826</v>
       </c>
       <c r="B94" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11128,10 +11128,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128931879</v>
+        <v>128931828</v>
       </c>
       <c r="B95" t="n">
-        <v>96960</v>
+        <v>96986</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11163,10 +11163,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>316896</v>
+        <v>316830</v>
       </c>
       <c r="R95" t="n">
-        <v>6550430</v>
+        <v>6550440</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -11225,10 +11225,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128931828</v>
+        <v>128931879</v>
       </c>
       <c r="B96" t="n">
-        <v>96960</v>
+        <v>96986</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11260,10 +11260,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>316830</v>
+        <v>316896</v>
       </c>
       <c r="R96" t="n">
-        <v>6550440</v>
+        <v>6550430</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11325,7 +11325,7 @@
         <v>128931885</v>
       </c>
       <c r="B97" t="n">
-        <v>96924</v>
+        <v>96950</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11419,10 +11419,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128931876</v>
+        <v>128931861</v>
       </c>
       <c r="B98" t="n">
-        <v>4779</v>
+        <v>92821</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11430,39 +11430,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>102306</v>
+        <v>4364</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>316911</v>
+        <v>317004</v>
       </c>
       <c r="R98" t="n">
-        <v>6550465</v>
+        <v>6550507</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11505,21 +11500,6 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ98" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK98" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO98" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
@@ -11536,10 +11516,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128931861</v>
+        <v>128931876</v>
       </c>
       <c r="B99" t="n">
-        <v>92835</v>
+        <v>4779</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11547,34 +11527,39 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4364</v>
+        <v>102306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>317004</v>
+        <v>316911</v>
       </c>
       <c r="R99" t="n">
-        <v>6550507</v>
+        <v>6550465</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11617,6 +11602,21 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
@@ -11633,10 +11633,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128931884</v>
+        <v>128931866</v>
       </c>
       <c r="B100" t="n">
-        <v>96960</v>
+        <v>8450</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11644,34 +11644,39 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>316872</v>
+        <v>317035</v>
       </c>
       <c r="R100" t="n">
-        <v>6550383</v>
+        <v>6550330</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11714,6 +11719,21 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -11730,10 +11750,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128931866</v>
+        <v>128931884</v>
       </c>
       <c r="B101" t="n">
-        <v>8450</v>
+        <v>96986</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11741,39 +11761,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>317035</v>
+        <v>316872</v>
       </c>
       <c r="R101" t="n">
-        <v>6550330</v>
+        <v>6550383</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11816,21 +11831,6 @@
       </c>
       <c r="AG101" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ101" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK101" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO101" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
@@ -11850,7 +11850,7 @@
         <v>128931829</v>
       </c>
       <c r="B102" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>128931882</v>
       </c>
       <c r="B103" t="n">
-        <v>96924</v>
+        <v>96950</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12041,32 +12041,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128931855</v>
+        <v>128931862</v>
       </c>
       <c r="B104" t="n">
-        <v>90317</v>
+        <v>92859</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1596</v>
+        <v>5966</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12076,10 +12076,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>316943</v>
+        <v>317008</v>
       </c>
       <c r="R104" t="n">
-        <v>6550676</v>
+        <v>6550497</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -12138,32 +12138,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128931862</v>
+        <v>128931855</v>
       </c>
       <c r="B105" t="n">
-        <v>92873</v>
+        <v>90318</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5966</v>
+        <v>1596</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12173,10 +12173,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>317008</v>
+        <v>316943</v>
       </c>
       <c r="R105" t="n">
-        <v>6550497</v>
+        <v>6550676</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -12238,7 +12238,7 @@
         <v>129221408</v>
       </c>
       <c r="B106" t="n">
-        <v>96960</v>
+        <v>96986</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12447,7 +12447,7 @@
         <v>129221406</v>
       </c>
       <c r="B108" t="n">
-        <v>96960</v>
+        <v>96986</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>

--- a/artfynd/A 40826-2025 artfynd.xlsx
+++ b/artfynd/A 40826-2025 artfynd.xlsx
@@ -8720,45 +8720,50 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128931880</v>
+        <v>128931865</v>
       </c>
       <c r="B71" t="n">
-        <v>96950</v>
+        <v>8450</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>316881</v>
+        <v>317048</v>
       </c>
       <c r="R71" t="n">
-        <v>6550407</v>
+        <v>6550340</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8801,6 +8806,21 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -8817,32 +8837,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128931859</v>
+        <v>128931877</v>
       </c>
       <c r="B72" t="n">
-        <v>90318</v>
+        <v>91313</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1596</v>
+        <v>3215</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8852,10 +8872,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>316972</v>
+        <v>316908</v>
       </c>
       <c r="R72" t="n">
-        <v>6550656</v>
+        <v>6550462</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8914,32 +8934,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128931877</v>
+        <v>128931859</v>
       </c>
       <c r="B73" t="n">
-        <v>91313</v>
+        <v>90318</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>3215</v>
+        <v>1596</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8949,10 +8969,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>316908</v>
+        <v>316972</v>
       </c>
       <c r="R73" t="n">
-        <v>6550462</v>
+        <v>6550656</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -9011,50 +9031,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128931865</v>
+        <v>128931880</v>
       </c>
       <c r="B74" t="n">
-        <v>8450</v>
+        <v>96951</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>317048</v>
+        <v>316881</v>
       </c>
       <c r="R74" t="n">
-        <v>6550340</v>
+        <v>6550407</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9097,21 +9112,6 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -9128,10 +9128,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128931881</v>
+        <v>128931870</v>
       </c>
       <c r="B75" t="n">
-        <v>96986</v>
+        <v>96987</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9163,10 +9163,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>316881</v>
+        <v>316962</v>
       </c>
       <c r="R75" t="n">
-        <v>6550407</v>
+        <v>6550379</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9225,10 +9225,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128931870</v>
+        <v>128931881</v>
       </c>
       <c r="B76" t="n">
-        <v>96986</v>
+        <v>96987</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9260,10 +9260,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>316962</v>
+        <v>316881</v>
       </c>
       <c r="R76" t="n">
-        <v>6550379</v>
+        <v>6550407</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9322,10 +9322,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128931887</v>
+        <v>128931883</v>
       </c>
       <c r="B77" t="n">
-        <v>96986</v>
+        <v>96987</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9357,10 +9357,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>316894</v>
+        <v>316864</v>
       </c>
       <c r="R77" t="n">
-        <v>6550382</v>
+        <v>6550421</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9419,10 +9419,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128931883</v>
+        <v>128931887</v>
       </c>
       <c r="B78" t="n">
-        <v>96986</v>
+        <v>96987</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9454,10 +9454,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>316864</v>
+        <v>316894</v>
       </c>
       <c r="R78" t="n">
-        <v>6550421</v>
+        <v>6550382</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9636,7 +9636,7 @@
         <v>128931827</v>
       </c>
       <c r="B80" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9733,7 +9733,7 @@
         <v>128931857</v>
       </c>
       <c r="B81" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>128931869</v>
       </c>
       <c r="B82" t="n">
-        <v>96950</v>
+        <v>96951</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9924,32 +9924,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128931878</v>
+        <v>128931825</v>
       </c>
       <c r="B83" t="n">
-        <v>96950</v>
+        <v>96987</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>53</v>
+        <v>2590</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9959,10 +9959,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>316896</v>
+        <v>316831</v>
       </c>
       <c r="R83" t="n">
-        <v>6550430</v>
+        <v>6550424</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -10021,10 +10021,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128931825</v>
+        <v>128931874</v>
       </c>
       <c r="B84" t="n">
-        <v>96986</v>
+        <v>96987</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10056,10 +10056,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>316831</v>
+        <v>316914</v>
       </c>
       <c r="R84" t="n">
-        <v>6550424</v>
+        <v>6550458</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -10118,32 +10118,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128931874</v>
+        <v>128931878</v>
       </c>
       <c r="B85" t="n">
-        <v>96986</v>
+        <v>96951</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2590</v>
+        <v>53</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10153,10 +10153,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>316914</v>
+        <v>316896</v>
       </c>
       <c r="R85" t="n">
-        <v>6550458</v>
+        <v>6550430</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -10218,7 +10218,7 @@
         <v>128931873</v>
       </c>
       <c r="B86" t="n">
-        <v>96950</v>
+        <v>96951</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10315,7 +10315,7 @@
         <v>128931864</v>
       </c>
       <c r="B87" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10412,7 +10412,7 @@
         <v>128931886</v>
       </c>
       <c r="B88" t="n">
-        <v>96950</v>
+        <v>96951</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>128931856</v>
       </c>
       <c r="B90" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10723,7 +10723,7 @@
         <v>128931872</v>
       </c>
       <c r="B91" t="n">
-        <v>96986</v>
+        <v>96987</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10817,10 +10817,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128931868</v>
+        <v>128931863</v>
       </c>
       <c r="B92" t="n">
-        <v>96986</v>
+        <v>8450</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10828,34 +10828,39 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>317023</v>
+        <v>317035</v>
       </c>
       <c r="R92" t="n">
-        <v>6550315</v>
+        <v>6550369</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10898,6 +10903,21 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
@@ -10914,10 +10934,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128931863</v>
+        <v>128931868</v>
       </c>
       <c r="B93" t="n">
-        <v>8450</v>
+        <v>96987</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10925,39 +10945,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>317035</v>
+        <v>317023</v>
       </c>
       <c r="R93" t="n">
-        <v>6550369</v>
+        <v>6550315</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -11000,21 +11015,6 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ93" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK93" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO93" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
@@ -11031,32 +11031,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128931826</v>
+        <v>128931879</v>
       </c>
       <c r="B94" t="n">
-        <v>98704</v>
+        <v>96987</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>2590</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11066,10 +11066,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>316835</v>
+        <v>316896</v>
       </c>
       <c r="R94" t="n">
-        <v>6550425</v>
+        <v>6550430</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -11131,7 +11131,7 @@
         <v>128931828</v>
       </c>
       <c r="B95" t="n">
-        <v>96986</v>
+        <v>96987</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11225,32 +11225,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128931879</v>
+        <v>128931826</v>
       </c>
       <c r="B96" t="n">
-        <v>96986</v>
+        <v>98705</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2590</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11260,10 +11260,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>316896</v>
+        <v>316835</v>
       </c>
       <c r="R96" t="n">
-        <v>6550430</v>
+        <v>6550425</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11325,7 +11325,7 @@
         <v>128931885</v>
       </c>
       <c r="B97" t="n">
-        <v>96950</v>
+        <v>96951</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>128931861</v>
       </c>
       <c r="B98" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11633,10 +11633,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128931866</v>
+        <v>128931884</v>
       </c>
       <c r="B100" t="n">
-        <v>8450</v>
+        <v>96987</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11644,39 +11644,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>317035</v>
+        <v>316872</v>
       </c>
       <c r="R100" t="n">
-        <v>6550330</v>
+        <v>6550383</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11719,21 +11714,6 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -11750,10 +11730,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128931884</v>
+        <v>128931866</v>
       </c>
       <c r="B101" t="n">
-        <v>96986</v>
+        <v>8450</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11761,34 +11741,39 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>316872</v>
+        <v>317035</v>
       </c>
       <c r="R101" t="n">
-        <v>6550383</v>
+        <v>6550330</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11831,6 +11816,21 @@
       </c>
       <c r="AG101" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
@@ -11850,7 +11850,7 @@
         <v>128931829</v>
       </c>
       <c r="B102" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11944,32 +11944,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128931882</v>
+        <v>128931855</v>
       </c>
       <c r="B103" t="n">
-        <v>96950</v>
+        <v>90318</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>53</v>
+        <v>1596</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11979,10 +11979,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>316864</v>
+        <v>316943</v>
       </c>
       <c r="R103" t="n">
-        <v>6550421</v>
+        <v>6550676</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -12041,10 +12041,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128931862</v>
+        <v>128931882</v>
       </c>
       <c r="B104" t="n">
-        <v>92859</v>
+        <v>96951</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12052,21 +12052,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5966</v>
+        <v>53</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12076,10 +12076,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>317008</v>
+        <v>316864</v>
       </c>
       <c r="R104" t="n">
-        <v>6550497</v>
+        <v>6550421</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -12138,32 +12138,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128931855</v>
+        <v>128931862</v>
       </c>
       <c r="B105" t="n">
-        <v>90318</v>
+        <v>92860</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1596</v>
+        <v>5966</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12173,10 +12173,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>316943</v>
+        <v>317008</v>
       </c>
       <c r="R105" t="n">
-        <v>6550676</v>
+        <v>6550497</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -12238,7 +12238,7 @@
         <v>129221408</v>
       </c>
       <c r="B106" t="n">
-        <v>96986</v>
+        <v>96987</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12447,7 +12447,7 @@
         <v>129221406</v>
       </c>
       <c r="B108" t="n">
-        <v>96986</v>
+        <v>96987</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>

--- a/artfynd/A 40826-2025 artfynd.xlsx
+++ b/artfynd/A 40826-2025 artfynd.xlsx
@@ -8720,50 +8720,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128931865</v>
+        <v>128931880</v>
       </c>
       <c r="B71" t="n">
-        <v>8450</v>
+        <v>96952</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>317048</v>
+        <v>316881</v>
       </c>
       <c r="R71" t="n">
-        <v>6550340</v>
+        <v>6550407</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8806,21 +8801,6 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -8837,32 +8817,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128931877</v>
+        <v>128931859</v>
       </c>
       <c r="B72" t="n">
-        <v>91313</v>
+        <v>90318</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3215</v>
+        <v>1596</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8872,10 +8852,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>316908</v>
+        <v>316972</v>
       </c>
       <c r="R72" t="n">
-        <v>6550462</v>
+        <v>6550656</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8934,45 +8914,50 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128931859</v>
+        <v>128931865</v>
       </c>
       <c r="B73" t="n">
-        <v>90318</v>
+        <v>8450</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1596</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>316972</v>
+        <v>317048</v>
       </c>
       <c r="R73" t="n">
-        <v>6550656</v>
+        <v>6550340</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -9015,6 +9000,21 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -9031,32 +9031,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128931880</v>
+        <v>128931877</v>
       </c>
       <c r="B74" t="n">
-        <v>96951</v>
+        <v>91313</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>53</v>
+        <v>3215</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9066,10 +9066,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>316881</v>
+        <v>316908</v>
       </c>
       <c r="R74" t="n">
-        <v>6550407</v>
+        <v>6550462</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9131,7 +9131,7 @@
         <v>128931870</v>
       </c>
       <c r="B75" t="n">
-        <v>96987</v>
+        <v>96988</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         <v>128931881</v>
       </c>
       <c r="B76" t="n">
-        <v>96987</v>
+        <v>96988</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         <v>128931883</v>
       </c>
       <c r="B77" t="n">
-        <v>96987</v>
+        <v>96988</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9422,7 +9422,7 @@
         <v>128931887</v>
       </c>
       <c r="B78" t="n">
-        <v>96987</v>
+        <v>96988</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>128931827</v>
       </c>
       <c r="B80" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9730,32 +9730,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128931857</v>
+        <v>128931869</v>
       </c>
       <c r="B81" t="n">
-        <v>92822</v>
+        <v>96952</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9768,7 +9768,7 @@
         <v>316962</v>
       </c>
       <c r="R81" t="n">
-        <v>6550668</v>
+        <v>6550379</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9827,32 +9827,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128931869</v>
+        <v>128931857</v>
       </c>
       <c r="B82" t="n">
-        <v>96951</v>
+        <v>92822</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9865,7 +9865,7 @@
         <v>316962</v>
       </c>
       <c r="R82" t="n">
-        <v>6550379</v>
+        <v>6550668</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9927,7 +9927,7 @@
         <v>128931825</v>
       </c>
       <c r="B83" t="n">
-        <v>96987</v>
+        <v>96988</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>128931874</v>
       </c>
       <c r="B84" t="n">
-        <v>96987</v>
+        <v>96988</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
         <v>128931878</v>
       </c>
       <c r="B85" t="n">
-        <v>96951</v>
+        <v>96952</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10218,7 +10218,7 @@
         <v>128931873</v>
       </c>
       <c r="B86" t="n">
-        <v>96951</v>
+        <v>96952</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10412,7 +10412,7 @@
         <v>128931886</v>
       </c>
       <c r="B88" t="n">
-        <v>96951</v>
+        <v>96952</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10623,10 +10623,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128931856</v>
+        <v>128931872</v>
       </c>
       <c r="B90" t="n">
-        <v>92822</v>
+        <v>96988</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10634,21 +10634,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4364</v>
+        <v>2590</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10658,10 +10658,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>316947</v>
+        <v>316937</v>
       </c>
       <c r="R90" t="n">
-        <v>6550667</v>
+        <v>6550476</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10720,10 +10720,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128931872</v>
+        <v>128931856</v>
       </c>
       <c r="B91" t="n">
-        <v>96987</v>
+        <v>92822</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10731,21 +10731,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2590</v>
+        <v>4364</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10755,10 +10755,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>316937</v>
+        <v>316947</v>
       </c>
       <c r="R91" t="n">
-        <v>6550476</v>
+        <v>6550667</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10817,10 +10817,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128931863</v>
+        <v>128931868</v>
       </c>
       <c r="B92" t="n">
-        <v>8450</v>
+        <v>96988</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10828,39 +10828,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>317035</v>
+        <v>317023</v>
       </c>
       <c r="R92" t="n">
-        <v>6550369</v>
+        <v>6550315</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10903,21 +10898,6 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ92" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK92" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO92" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
@@ -10934,10 +10914,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128931868</v>
+        <v>128931863</v>
       </c>
       <c r="B93" t="n">
-        <v>96987</v>
+        <v>8450</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10945,34 +10925,39 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>317023</v>
+        <v>317035</v>
       </c>
       <c r="R93" t="n">
-        <v>6550315</v>
+        <v>6550369</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -11015,6 +11000,21 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
@@ -11031,32 +11031,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128931879</v>
+        <v>128931826</v>
       </c>
       <c r="B94" t="n">
-        <v>96987</v>
+        <v>98706</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2590</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11066,10 +11066,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>316896</v>
+        <v>316835</v>
       </c>
       <c r="R94" t="n">
-        <v>6550430</v>
+        <v>6550425</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -11128,10 +11128,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128931828</v>
+        <v>128931879</v>
       </c>
       <c r="B95" t="n">
-        <v>96987</v>
+        <v>96988</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11163,10 +11163,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>316830</v>
+        <v>316896</v>
       </c>
       <c r="R95" t="n">
-        <v>6550440</v>
+        <v>6550430</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -11225,32 +11225,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128931826</v>
+        <v>128931828</v>
       </c>
       <c r="B96" t="n">
-        <v>98705</v>
+        <v>96988</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>2590</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11260,10 +11260,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>316835</v>
+        <v>316830</v>
       </c>
       <c r="R96" t="n">
-        <v>6550425</v>
+        <v>6550440</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11325,7 +11325,7 @@
         <v>128931885</v>
       </c>
       <c r="B97" t="n">
-        <v>96951</v>
+        <v>96952</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11633,10 +11633,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128931884</v>
+        <v>128931866</v>
       </c>
       <c r="B100" t="n">
-        <v>96987</v>
+        <v>8450</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11644,34 +11644,39 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>316872</v>
+        <v>317035</v>
       </c>
       <c r="R100" t="n">
-        <v>6550383</v>
+        <v>6550330</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11714,6 +11719,21 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -11730,10 +11750,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128931866</v>
+        <v>128931884</v>
       </c>
       <c r="B101" t="n">
-        <v>8450</v>
+        <v>96988</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11741,39 +11761,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>317035</v>
+        <v>316872</v>
       </c>
       <c r="R101" t="n">
-        <v>6550330</v>
+        <v>6550383</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11816,21 +11831,6 @@
       </c>
       <c r="AG101" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ101" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK101" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO101" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
@@ -11850,7 +11850,7 @@
         <v>128931829</v>
       </c>
       <c r="B102" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11944,32 +11944,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128931855</v>
+        <v>128931882</v>
       </c>
       <c r="B103" t="n">
-        <v>90318</v>
+        <v>96952</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1596</v>
+        <v>53</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11979,10 +11979,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>316943</v>
+        <v>316864</v>
       </c>
       <c r="R103" t="n">
-        <v>6550676</v>
+        <v>6550421</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -12041,10 +12041,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128931882</v>
+        <v>128931862</v>
       </c>
       <c r="B104" t="n">
-        <v>96951</v>
+        <v>92860</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12052,21 +12052,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>53</v>
+        <v>5966</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12076,10 +12076,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>316864</v>
+        <v>317008</v>
       </c>
       <c r="R104" t="n">
-        <v>6550421</v>
+        <v>6550497</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -12138,32 +12138,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128931862</v>
+        <v>128931855</v>
       </c>
       <c r="B105" t="n">
-        <v>92860</v>
+        <v>90318</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5966</v>
+        <v>1596</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12173,10 +12173,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>317008</v>
+        <v>316943</v>
       </c>
       <c r="R105" t="n">
-        <v>6550497</v>
+        <v>6550676</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -12238,7 +12238,7 @@
         <v>129221408</v>
       </c>
       <c r="B106" t="n">
-        <v>96987</v>
+        <v>96988</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12447,7 +12447,7 @@
         <v>129221406</v>
       </c>
       <c r="B108" t="n">
-        <v>96987</v>
+        <v>96988</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>

--- a/artfynd/A 40826-2025 artfynd.xlsx
+++ b/artfynd/A 40826-2025 artfynd.xlsx
@@ -8723,7 +8723,7 @@
         <v>128931880</v>
       </c>
       <c r="B71" t="n">
-        <v>96952</v>
+        <v>96956</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8817,32 +8817,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128931859</v>
+        <v>128931877</v>
       </c>
       <c r="B72" t="n">
-        <v>90318</v>
+        <v>91316</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1596</v>
+        <v>3215</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8852,10 +8852,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>316972</v>
+        <v>316908</v>
       </c>
       <c r="R72" t="n">
-        <v>6550656</v>
+        <v>6550462</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8914,50 +8914,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128931865</v>
+        <v>128931859</v>
       </c>
       <c r="B73" t="n">
-        <v>8450</v>
+        <v>90321</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>1596</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>317048</v>
+        <v>316972</v>
       </c>
       <c r="R73" t="n">
-        <v>6550340</v>
+        <v>6550656</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -9000,21 +8995,6 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -9031,10 +9011,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128931877</v>
+        <v>128931865</v>
       </c>
       <c r="B74" t="n">
-        <v>91313</v>
+        <v>8450</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9042,34 +9022,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3215</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>316908</v>
+        <v>317048</v>
       </c>
       <c r="R74" t="n">
-        <v>6550462</v>
+        <v>6550340</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9112,6 +9097,21 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -9131,7 +9131,7 @@
         <v>128931870</v>
       </c>
       <c r="B75" t="n">
-        <v>96988</v>
+        <v>96992</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         <v>128931881</v>
       </c>
       <c r="B76" t="n">
-        <v>96988</v>
+        <v>96992</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         <v>128931883</v>
       </c>
       <c r="B77" t="n">
-        <v>96988</v>
+        <v>96992</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9422,7 +9422,7 @@
         <v>128931887</v>
       </c>
       <c r="B78" t="n">
-        <v>96988</v>
+        <v>96992</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>128931827</v>
       </c>
       <c r="B80" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9733,7 +9733,7 @@
         <v>128931869</v>
       </c>
       <c r="B81" t="n">
-        <v>96952</v>
+        <v>96956</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>128931857</v>
       </c>
       <c r="B82" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>128931825</v>
       </c>
       <c r="B83" t="n">
-        <v>96988</v>
+        <v>96992</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>128931874</v>
       </c>
       <c r="B84" t="n">
-        <v>96988</v>
+        <v>96992</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
         <v>128931878</v>
       </c>
       <c r="B85" t="n">
-        <v>96952</v>
+        <v>96956</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10218,7 +10218,7 @@
         <v>128931873</v>
       </c>
       <c r="B86" t="n">
-        <v>96952</v>
+        <v>96956</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10315,7 +10315,7 @@
         <v>128931864</v>
       </c>
       <c r="B87" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10412,7 +10412,7 @@
         <v>128931886</v>
       </c>
       <c r="B88" t="n">
-        <v>96952</v>
+        <v>96956</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10623,10 +10623,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128931872</v>
+        <v>128931856</v>
       </c>
       <c r="B90" t="n">
-        <v>96988</v>
+        <v>92825</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10634,21 +10634,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2590</v>
+        <v>4364</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10658,10 +10658,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>316937</v>
+        <v>316947</v>
       </c>
       <c r="R90" t="n">
-        <v>6550476</v>
+        <v>6550667</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10720,10 +10720,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128931856</v>
+        <v>128931872</v>
       </c>
       <c r="B91" t="n">
-        <v>92822</v>
+        <v>96992</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10731,21 +10731,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4364</v>
+        <v>2590</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10755,10 +10755,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>316947</v>
+        <v>316937</v>
       </c>
       <c r="R91" t="n">
-        <v>6550667</v>
+        <v>6550476</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10817,10 +10817,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128931868</v>
+        <v>128931863</v>
       </c>
       <c r="B92" t="n">
-        <v>96988</v>
+        <v>8450</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10828,34 +10828,39 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>317023</v>
+        <v>317035</v>
       </c>
       <c r="R92" t="n">
-        <v>6550315</v>
+        <v>6550369</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10898,6 +10903,21 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
@@ -10914,10 +10934,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128931863</v>
+        <v>128931868</v>
       </c>
       <c r="B93" t="n">
-        <v>8450</v>
+        <v>96992</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10925,39 +10945,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>317035</v>
+        <v>317023</v>
       </c>
       <c r="R93" t="n">
-        <v>6550369</v>
+        <v>6550315</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -11000,21 +11015,6 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ93" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK93" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO93" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
@@ -11031,32 +11031,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128931826</v>
+        <v>128931879</v>
       </c>
       <c r="B94" t="n">
-        <v>98706</v>
+        <v>96992</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>2590</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11066,10 +11066,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>316835</v>
+        <v>316896</v>
       </c>
       <c r="R94" t="n">
-        <v>6550425</v>
+        <v>6550430</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -11128,10 +11128,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128931879</v>
+        <v>128931828</v>
       </c>
       <c r="B95" t="n">
-        <v>96988</v>
+        <v>96992</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11163,10 +11163,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>316896</v>
+        <v>316830</v>
       </c>
       <c r="R95" t="n">
-        <v>6550430</v>
+        <v>6550440</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -11225,32 +11225,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128931828</v>
+        <v>128931826</v>
       </c>
       <c r="B96" t="n">
-        <v>96988</v>
+        <v>98710</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2590</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11260,10 +11260,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>316830</v>
+        <v>316835</v>
       </c>
       <c r="R96" t="n">
-        <v>6550440</v>
+        <v>6550425</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11325,7 +11325,7 @@
         <v>128931885</v>
       </c>
       <c r="B97" t="n">
-        <v>96952</v>
+        <v>96956</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>128931861</v>
       </c>
       <c r="B98" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11633,10 +11633,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128931866</v>
+        <v>128931884</v>
       </c>
       <c r="B100" t="n">
-        <v>8450</v>
+        <v>96992</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11644,39 +11644,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>317035</v>
+        <v>316872</v>
       </c>
       <c r="R100" t="n">
-        <v>6550330</v>
+        <v>6550383</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11719,21 +11714,6 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -11750,10 +11730,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128931884</v>
+        <v>128931866</v>
       </c>
       <c r="B101" t="n">
-        <v>96988</v>
+        <v>8450</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11761,34 +11741,39 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>316872</v>
+        <v>317035</v>
       </c>
       <c r="R101" t="n">
-        <v>6550383</v>
+        <v>6550330</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11831,6 +11816,21 @@
       </c>
       <c r="AG101" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
@@ -11850,7 +11850,7 @@
         <v>128931829</v>
       </c>
       <c r="B102" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11944,10 +11944,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128931882</v>
+        <v>128931862</v>
       </c>
       <c r="B103" t="n">
-        <v>96952</v>
+        <v>92863</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11955,21 +11955,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>53</v>
+        <v>5966</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11979,10 +11979,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>316864</v>
+        <v>317008</v>
       </c>
       <c r="R103" t="n">
-        <v>6550421</v>
+        <v>6550497</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -12041,10 +12041,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128931862</v>
+        <v>128931882</v>
       </c>
       <c r="B104" t="n">
-        <v>92860</v>
+        <v>96956</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12052,21 +12052,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5966</v>
+        <v>53</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12076,10 +12076,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>317008</v>
+        <v>316864</v>
       </c>
       <c r="R104" t="n">
-        <v>6550497</v>
+        <v>6550421</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -12141,7 +12141,7 @@
         <v>128931855</v>
       </c>
       <c r="B105" t="n">
-        <v>90318</v>
+        <v>90321</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12238,7 +12238,7 @@
         <v>129221408</v>
       </c>
       <c r="B106" t="n">
-        <v>96988</v>
+        <v>96992</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
         <v>129221407</v>
       </c>
       <c r="B107" t="n">
-        <v>78707</v>
+        <v>78709</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12447,7 +12447,7 @@
         <v>129221406</v>
       </c>
       <c r="B108" t="n">
-        <v>96988</v>
+        <v>96992</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>

--- a/artfynd/A 40826-2025 artfynd.xlsx
+++ b/artfynd/A 40826-2025 artfynd.xlsx
@@ -9730,32 +9730,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128931869</v>
+        <v>128931857</v>
       </c>
       <c r="B81" t="n">
-        <v>96956</v>
+        <v>92825</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9768,7 +9768,7 @@
         <v>316962</v>
       </c>
       <c r="R81" t="n">
-        <v>6550379</v>
+        <v>6550668</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9827,32 +9827,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128931857</v>
+        <v>128931869</v>
       </c>
       <c r="B82" t="n">
-        <v>92825</v>
+        <v>96956</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9865,7 +9865,7 @@
         <v>316962</v>
       </c>
       <c r="R82" t="n">
-        <v>6550668</v>
+        <v>6550379</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>

--- a/artfynd/A 40826-2025 artfynd.xlsx
+++ b/artfynd/A 40826-2025 artfynd.xlsx
@@ -8723,7 +8723,7 @@
         <v>128931880</v>
       </c>
       <c r="B71" t="n">
-        <v>96956</v>
+        <v>96958</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8817,10 +8817,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128931877</v>
+        <v>128931865</v>
       </c>
       <c r="B72" t="n">
-        <v>91316</v>
+        <v>8450</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8828,34 +8828,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3215</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>316908</v>
+        <v>317048</v>
       </c>
       <c r="R72" t="n">
-        <v>6550462</v>
+        <v>6550340</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8898,6 +8903,21 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -8917,7 +8937,7 @@
         <v>128931859</v>
       </c>
       <c r="B73" t="n">
-        <v>90321</v>
+        <v>90323</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9011,10 +9031,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128931865</v>
+        <v>128931877</v>
       </c>
       <c r="B74" t="n">
-        <v>8450</v>
+        <v>91318</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9022,39 +9042,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>3215</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>317048</v>
+        <v>316908</v>
       </c>
       <c r="R74" t="n">
-        <v>6550340</v>
+        <v>6550462</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9097,21 +9112,6 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -9128,10 +9128,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128931870</v>
+        <v>128931881</v>
       </c>
       <c r="B75" t="n">
-        <v>96992</v>
+        <v>96994</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9163,10 +9163,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>316962</v>
+        <v>316881</v>
       </c>
       <c r="R75" t="n">
-        <v>6550379</v>
+        <v>6550407</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9225,10 +9225,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128931881</v>
+        <v>128931870</v>
       </c>
       <c r="B76" t="n">
-        <v>96992</v>
+        <v>96994</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9260,10 +9260,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>316881</v>
+        <v>316962</v>
       </c>
       <c r="R76" t="n">
-        <v>6550407</v>
+        <v>6550379</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9322,10 +9322,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128931883</v>
+        <v>128931860</v>
       </c>
       <c r="B77" t="n">
-        <v>96992</v>
+        <v>8450</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9333,34 +9333,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>316864</v>
+        <v>316968</v>
       </c>
       <c r="R77" t="n">
-        <v>6550421</v>
+        <v>6550604</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9403,6 +9408,21 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -9419,32 +9439,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128931887</v>
+        <v>128931827</v>
       </c>
       <c r="B78" t="n">
-        <v>96992</v>
+        <v>98712</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2590</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9454,10 +9474,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>316894</v>
+        <v>316833</v>
       </c>
       <c r="R78" t="n">
-        <v>6550382</v>
+        <v>6550435</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9516,10 +9536,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128931860</v>
+        <v>128931883</v>
       </c>
       <c r="B79" t="n">
-        <v>8450</v>
+        <v>96994</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9527,39 +9547,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>316968</v>
+        <v>316864</v>
       </c>
       <c r="R79" t="n">
-        <v>6550604</v>
+        <v>6550421</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9602,21 +9617,6 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -9633,32 +9633,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128931827</v>
+        <v>128931887</v>
       </c>
       <c r="B80" t="n">
-        <v>98710</v>
+        <v>96994</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>2590</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9668,10 +9668,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>316833</v>
+        <v>316894</v>
       </c>
       <c r="R80" t="n">
-        <v>6550435</v>
+        <v>6550382</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9733,7 +9733,7 @@
         <v>128931857</v>
       </c>
       <c r="B81" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>128931869</v>
       </c>
       <c r="B82" t="n">
-        <v>96956</v>
+        <v>96958</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>128931825</v>
       </c>
       <c r="B83" t="n">
-        <v>96992</v>
+        <v>96994</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>128931874</v>
       </c>
       <c r="B84" t="n">
-        <v>96992</v>
+        <v>96994</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
         <v>128931878</v>
       </c>
       <c r="B85" t="n">
-        <v>96956</v>
+        <v>96958</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10218,7 +10218,7 @@
         <v>128931873</v>
       </c>
       <c r="B86" t="n">
-        <v>96956</v>
+        <v>96958</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10315,7 +10315,7 @@
         <v>128931864</v>
       </c>
       <c r="B87" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10412,7 +10412,7 @@
         <v>128931886</v>
       </c>
       <c r="B88" t="n">
-        <v>96956</v>
+        <v>96958</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10623,10 +10623,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128931856</v>
+        <v>128931872</v>
       </c>
       <c r="B90" t="n">
-        <v>92825</v>
+        <v>96994</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10634,21 +10634,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4364</v>
+        <v>2590</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10658,10 +10658,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>316947</v>
+        <v>316937</v>
       </c>
       <c r="R90" t="n">
-        <v>6550667</v>
+        <v>6550476</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10720,10 +10720,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128931872</v>
+        <v>128931856</v>
       </c>
       <c r="B91" t="n">
-        <v>96992</v>
+        <v>92827</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10731,21 +10731,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2590</v>
+        <v>4364</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10755,10 +10755,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>316937</v>
+        <v>316947</v>
       </c>
       <c r="R91" t="n">
-        <v>6550476</v>
+        <v>6550667</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10817,10 +10817,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128931863</v>
+        <v>128931868</v>
       </c>
       <c r="B92" t="n">
-        <v>8450</v>
+        <v>96994</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10828,39 +10828,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>317035</v>
+        <v>317023</v>
       </c>
       <c r="R92" t="n">
-        <v>6550369</v>
+        <v>6550315</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10903,21 +10898,6 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ92" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK92" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO92" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
@@ -10934,10 +10914,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128931868</v>
+        <v>128931863</v>
       </c>
       <c r="B93" t="n">
-        <v>96992</v>
+        <v>8450</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10945,34 +10925,39 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>317023</v>
+        <v>317035</v>
       </c>
       <c r="R93" t="n">
-        <v>6550315</v>
+        <v>6550369</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -11015,6 +11000,21 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
@@ -11034,7 +11034,7 @@
         <v>128931879</v>
       </c>
       <c r="B94" t="n">
-        <v>96992</v>
+        <v>96994</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11131,7 +11131,7 @@
         <v>128931828</v>
       </c>
       <c r="B95" t="n">
-        <v>96992</v>
+        <v>96994</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>128931826</v>
       </c>
       <c r="B96" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>128931885</v>
       </c>
       <c r="B97" t="n">
-        <v>96956</v>
+        <v>96958</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>128931861</v>
       </c>
       <c r="B98" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11636,7 +11636,7 @@
         <v>128931884</v>
       </c>
       <c r="B100" t="n">
-        <v>96992</v>
+        <v>96994</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11850,7 +11850,7 @@
         <v>128931829</v>
       </c>
       <c r="B102" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11944,32 +11944,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128931862</v>
+        <v>128931855</v>
       </c>
       <c r="B103" t="n">
-        <v>92863</v>
+        <v>90323</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5966</v>
+        <v>1596</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11979,10 +11979,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>317008</v>
+        <v>316943</v>
       </c>
       <c r="R103" t="n">
-        <v>6550497</v>
+        <v>6550676</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -12044,7 +12044,7 @@
         <v>128931882</v>
       </c>
       <c r="B104" t="n">
-        <v>96956</v>
+        <v>96958</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12138,32 +12138,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128931855</v>
+        <v>128931862</v>
       </c>
       <c r="B105" t="n">
-        <v>90321</v>
+        <v>92865</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1596</v>
+        <v>5966</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12173,10 +12173,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>316943</v>
+        <v>317008</v>
       </c>
       <c r="R105" t="n">
-        <v>6550676</v>
+        <v>6550497</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -12238,7 +12238,7 @@
         <v>129221408</v>
       </c>
       <c r="B106" t="n">
-        <v>96992</v>
+        <v>96994</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
         <v>129221407</v>
       </c>
       <c r="B107" t="n">
-        <v>78709</v>
+        <v>78710</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12447,7 +12447,7 @@
         <v>129221406</v>
       </c>
       <c r="B108" t="n">
-        <v>96992</v>
+        <v>96994</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>

--- a/artfynd/A 40826-2025 artfynd.xlsx
+++ b/artfynd/A 40826-2025 artfynd.xlsx
@@ -8720,32 +8720,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128931880</v>
+        <v>128931859</v>
       </c>
       <c r="B71" t="n">
-        <v>96958</v>
+        <v>90327</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>53</v>
+        <v>1596</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8755,10 +8755,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>316881</v>
+        <v>316972</v>
       </c>
       <c r="R71" t="n">
-        <v>6550407</v>
+        <v>6550656</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8817,50 +8817,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128931865</v>
+        <v>128931880</v>
       </c>
       <c r="B72" t="n">
-        <v>8450</v>
+        <v>96962</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>317048</v>
+        <v>316881</v>
       </c>
       <c r="R72" t="n">
-        <v>6550340</v>
+        <v>6550407</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8903,21 +8898,6 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -8934,32 +8914,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128931859</v>
+        <v>128931877</v>
       </c>
       <c r="B73" t="n">
-        <v>90323</v>
+        <v>91322</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1596</v>
+        <v>3215</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8969,10 +8949,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>316972</v>
+        <v>316908</v>
       </c>
       <c r="R73" t="n">
-        <v>6550656</v>
+        <v>6550462</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -9031,10 +9011,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128931877</v>
+        <v>128931865</v>
       </c>
       <c r="B74" t="n">
-        <v>91318</v>
+        <v>8450</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9042,34 +9022,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3215</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>316908</v>
+        <v>317048</v>
       </c>
       <c r="R74" t="n">
-        <v>6550462</v>
+        <v>6550340</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9112,6 +9097,21 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -9128,10 +9128,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128931881</v>
+        <v>128931870</v>
       </c>
       <c r="B75" t="n">
-        <v>96994</v>
+        <v>96998</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9163,10 +9163,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>316881</v>
+        <v>316962</v>
       </c>
       <c r="R75" t="n">
-        <v>6550407</v>
+        <v>6550379</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9225,10 +9225,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128931870</v>
+        <v>128931881</v>
       </c>
       <c r="B76" t="n">
-        <v>96994</v>
+        <v>96998</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9260,10 +9260,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>316962</v>
+        <v>316881</v>
       </c>
       <c r="R76" t="n">
-        <v>6550379</v>
+        <v>6550407</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9322,10 +9322,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128931860</v>
+        <v>128931883</v>
       </c>
       <c r="B77" t="n">
-        <v>8450</v>
+        <v>96998</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9333,39 +9333,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>316968</v>
+        <v>316864</v>
       </c>
       <c r="R77" t="n">
-        <v>6550604</v>
+        <v>6550421</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9408,21 +9403,6 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -9439,32 +9419,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128931827</v>
+        <v>128931887</v>
       </c>
       <c r="B78" t="n">
-        <v>98712</v>
+        <v>96998</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>2590</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9474,10 +9454,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>316833</v>
+        <v>316894</v>
       </c>
       <c r="R78" t="n">
-        <v>6550435</v>
+        <v>6550382</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9536,10 +9516,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128931883</v>
+        <v>128931860</v>
       </c>
       <c r="B79" t="n">
-        <v>96994</v>
+        <v>8450</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9547,34 +9527,39 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>316864</v>
+        <v>316968</v>
       </c>
       <c r="R79" t="n">
-        <v>6550421</v>
+        <v>6550604</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9617,6 +9602,21 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -9633,32 +9633,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128931887</v>
+        <v>128931827</v>
       </c>
       <c r="B80" t="n">
-        <v>96994</v>
+        <v>98716</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2590</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9668,10 +9668,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>316894</v>
+        <v>316833</v>
       </c>
       <c r="R80" t="n">
-        <v>6550382</v>
+        <v>6550435</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9730,32 +9730,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128931857</v>
+        <v>128931869</v>
       </c>
       <c r="B81" t="n">
-        <v>92827</v>
+        <v>96962</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9768,7 +9768,7 @@
         <v>316962</v>
       </c>
       <c r="R81" t="n">
-        <v>6550668</v>
+        <v>6550379</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9827,32 +9827,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128931869</v>
+        <v>128931857</v>
       </c>
       <c r="B82" t="n">
-        <v>96958</v>
+        <v>92831</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9865,7 +9865,7 @@
         <v>316962</v>
       </c>
       <c r="R82" t="n">
-        <v>6550379</v>
+        <v>6550668</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9924,32 +9924,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128931825</v>
+        <v>128931878</v>
       </c>
       <c r="B83" t="n">
-        <v>96994</v>
+        <v>96962</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2590</v>
+        <v>53</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9959,10 +9959,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>316831</v>
+        <v>316896</v>
       </c>
       <c r="R83" t="n">
-        <v>6550424</v>
+        <v>6550430</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -10021,10 +10021,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128931874</v>
+        <v>128931825</v>
       </c>
       <c r="B84" t="n">
-        <v>96994</v>
+        <v>96998</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10056,10 +10056,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>316914</v>
+        <v>316831</v>
       </c>
       <c r="R84" t="n">
-        <v>6550458</v>
+        <v>6550424</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -10118,32 +10118,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128931878</v>
+        <v>128931874</v>
       </c>
       <c r="B85" t="n">
-        <v>96958</v>
+        <v>96998</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>53</v>
+        <v>2590</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10153,10 +10153,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>316896</v>
+        <v>316914</v>
       </c>
       <c r="R85" t="n">
-        <v>6550430</v>
+        <v>6550458</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -10218,7 +10218,7 @@
         <v>128931873</v>
       </c>
       <c r="B86" t="n">
-        <v>96958</v>
+        <v>96962</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10315,7 +10315,7 @@
         <v>128931864</v>
       </c>
       <c r="B87" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10412,7 +10412,7 @@
         <v>128931886</v>
       </c>
       <c r="B88" t="n">
-        <v>96958</v>
+        <v>96962</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>128931872</v>
       </c>
       <c r="B90" t="n">
-        <v>96994</v>
+        <v>96998</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10723,7 +10723,7 @@
         <v>128931856</v>
       </c>
       <c r="B91" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10820,7 +10820,7 @@
         <v>128931868</v>
       </c>
       <c r="B92" t="n">
-        <v>96994</v>
+        <v>96998</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11031,32 +11031,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128931879</v>
+        <v>128931826</v>
       </c>
       <c r="B94" t="n">
-        <v>96994</v>
+        <v>98716</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2590</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11066,10 +11066,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>316896</v>
+        <v>316835</v>
       </c>
       <c r="R94" t="n">
-        <v>6550430</v>
+        <v>6550425</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -11128,10 +11128,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128931828</v>
+        <v>128931879</v>
       </c>
       <c r="B95" t="n">
-        <v>96994</v>
+        <v>96998</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11163,10 +11163,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>316830</v>
+        <v>316896</v>
       </c>
       <c r="R95" t="n">
-        <v>6550440</v>
+        <v>6550430</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -11225,32 +11225,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128931826</v>
+        <v>128931828</v>
       </c>
       <c r="B96" t="n">
-        <v>98712</v>
+        <v>96998</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>2590</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11260,10 +11260,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>316835</v>
+        <v>316830</v>
       </c>
       <c r="R96" t="n">
-        <v>6550425</v>
+        <v>6550440</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11325,7 +11325,7 @@
         <v>128931885</v>
       </c>
       <c r="B97" t="n">
-        <v>96958</v>
+        <v>96962</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>128931861</v>
       </c>
       <c r="B98" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11633,10 +11633,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128931884</v>
+        <v>128931866</v>
       </c>
       <c r="B100" t="n">
-        <v>96994</v>
+        <v>8450</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11644,34 +11644,39 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>316872</v>
+        <v>317035</v>
       </c>
       <c r="R100" t="n">
-        <v>6550383</v>
+        <v>6550330</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11714,6 +11719,21 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -11730,10 +11750,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128931866</v>
+        <v>128931884</v>
       </c>
       <c r="B101" t="n">
-        <v>8450</v>
+        <v>96998</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11741,39 +11761,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>317035</v>
+        <v>316872</v>
       </c>
       <c r="R101" t="n">
-        <v>6550330</v>
+        <v>6550383</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11816,21 +11831,6 @@
       </c>
       <c r="AG101" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ101" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK101" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO101" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
@@ -11850,7 +11850,7 @@
         <v>128931829</v>
       </c>
       <c r="B102" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>128931855</v>
       </c>
       <c r="B103" t="n">
-        <v>90323</v>
+        <v>90327</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12041,10 +12041,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128931882</v>
+        <v>128931862</v>
       </c>
       <c r="B104" t="n">
-        <v>96958</v>
+        <v>92869</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12052,21 +12052,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>53</v>
+        <v>5966</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12076,10 +12076,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>316864</v>
+        <v>317008</v>
       </c>
       <c r="R104" t="n">
-        <v>6550421</v>
+        <v>6550497</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -12138,10 +12138,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128931862</v>
+        <v>128931882</v>
       </c>
       <c r="B105" t="n">
-        <v>92865</v>
+        <v>96962</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12149,21 +12149,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5966</v>
+        <v>53</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12173,10 +12173,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>317008</v>
+        <v>316864</v>
       </c>
       <c r="R105" t="n">
-        <v>6550497</v>
+        <v>6550421</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -12238,7 +12238,7 @@
         <v>129221408</v>
       </c>
       <c r="B106" t="n">
-        <v>96994</v>
+        <v>96998</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12447,7 +12447,7 @@
         <v>129221406</v>
       </c>
       <c r="B108" t="n">
-        <v>96994</v>
+        <v>96998</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>

--- a/artfynd/A 40826-2025 artfynd.xlsx
+++ b/artfynd/A 40826-2025 artfynd.xlsx
@@ -8720,32 +8720,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128931859</v>
+        <v>128931880</v>
       </c>
       <c r="B71" t="n">
-        <v>90327</v>
+        <v>96970</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1596</v>
+        <v>53</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8755,10 +8755,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>316972</v>
+        <v>316881</v>
       </c>
       <c r="R71" t="n">
-        <v>6550656</v>
+        <v>6550407</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8817,32 +8817,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128931880</v>
+        <v>128931877</v>
       </c>
       <c r="B72" t="n">
-        <v>96962</v>
+        <v>91323</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>53</v>
+        <v>3215</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8852,10 +8852,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>316881</v>
+        <v>316908</v>
       </c>
       <c r="R72" t="n">
-        <v>6550407</v>
+        <v>6550462</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8914,32 +8914,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128931877</v>
+        <v>128931859</v>
       </c>
       <c r="B73" t="n">
-        <v>91322</v>
+        <v>90328</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>3215</v>
+        <v>1596</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8949,10 +8949,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>316908</v>
+        <v>316972</v>
       </c>
       <c r="R73" t="n">
-        <v>6550462</v>
+        <v>6550656</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -9131,7 +9131,7 @@
         <v>128931870</v>
       </c>
       <c r="B75" t="n">
-        <v>96998</v>
+        <v>97006</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         <v>128931881</v>
       </c>
       <c r="B76" t="n">
-        <v>96998</v>
+        <v>97006</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         <v>128931883</v>
       </c>
       <c r="B77" t="n">
-        <v>96998</v>
+        <v>97006</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9422,7 +9422,7 @@
         <v>128931887</v>
       </c>
       <c r="B78" t="n">
-        <v>96998</v>
+        <v>97006</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>128931827</v>
       </c>
       <c r="B80" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9733,7 +9733,7 @@
         <v>128931869</v>
       </c>
       <c r="B81" t="n">
-        <v>96962</v>
+        <v>96970</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>128931857</v>
       </c>
       <c r="B82" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>128931878</v>
       </c>
       <c r="B83" t="n">
-        <v>96962</v>
+        <v>96970</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>128931825</v>
       </c>
       <c r="B84" t="n">
-        <v>96998</v>
+        <v>97006</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
         <v>128931874</v>
       </c>
       <c r="B85" t="n">
-        <v>96998</v>
+        <v>97006</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10218,7 +10218,7 @@
         <v>128931873</v>
       </c>
       <c r="B86" t="n">
-        <v>96962</v>
+        <v>96970</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10315,7 +10315,7 @@
         <v>128931864</v>
       </c>
       <c r="B87" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10412,7 +10412,7 @@
         <v>128931886</v>
       </c>
       <c r="B88" t="n">
-        <v>96962</v>
+        <v>96970</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10623,10 +10623,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128931872</v>
+        <v>128931856</v>
       </c>
       <c r="B90" t="n">
-        <v>96998</v>
+        <v>92832</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10634,21 +10634,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2590</v>
+        <v>4364</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10658,10 +10658,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>316937</v>
+        <v>316947</v>
       </c>
       <c r="R90" t="n">
-        <v>6550476</v>
+        <v>6550667</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10720,10 +10720,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128931856</v>
+        <v>128931872</v>
       </c>
       <c r="B91" t="n">
-        <v>92831</v>
+        <v>97006</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10731,21 +10731,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4364</v>
+        <v>2590</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10755,10 +10755,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>316947</v>
+        <v>316937</v>
       </c>
       <c r="R91" t="n">
-        <v>6550667</v>
+        <v>6550476</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10820,7 +10820,7 @@
         <v>128931868</v>
       </c>
       <c r="B92" t="n">
-        <v>96998</v>
+        <v>97006</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11031,32 +11031,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128931826</v>
+        <v>128931879</v>
       </c>
       <c r="B94" t="n">
-        <v>98716</v>
+        <v>97006</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>2590</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11066,10 +11066,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>316835</v>
+        <v>316896</v>
       </c>
       <c r="R94" t="n">
-        <v>6550425</v>
+        <v>6550430</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -11128,10 +11128,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128931879</v>
+        <v>128931828</v>
       </c>
       <c r="B95" t="n">
-        <v>96998</v>
+        <v>97006</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11163,10 +11163,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>316896</v>
+        <v>316830</v>
       </c>
       <c r="R95" t="n">
-        <v>6550430</v>
+        <v>6550440</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -11225,32 +11225,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128931828</v>
+        <v>128931826</v>
       </c>
       <c r="B96" t="n">
-        <v>96998</v>
+        <v>98724</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2590</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11260,10 +11260,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>316830</v>
+        <v>316835</v>
       </c>
       <c r="R96" t="n">
-        <v>6550440</v>
+        <v>6550425</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11325,7 +11325,7 @@
         <v>128931885</v>
       </c>
       <c r="B97" t="n">
-        <v>96962</v>
+        <v>96970</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>128931861</v>
       </c>
       <c r="B98" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11633,10 +11633,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128931866</v>
+        <v>128931884</v>
       </c>
       <c r="B100" t="n">
-        <v>8450</v>
+        <v>97006</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11644,39 +11644,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>317035</v>
+        <v>316872</v>
       </c>
       <c r="R100" t="n">
-        <v>6550330</v>
+        <v>6550383</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11719,21 +11714,6 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -11750,10 +11730,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128931884</v>
+        <v>128931866</v>
       </c>
       <c r="B101" t="n">
-        <v>96998</v>
+        <v>8450</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11761,34 +11741,39 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>316872</v>
+        <v>317035</v>
       </c>
       <c r="R101" t="n">
-        <v>6550383</v>
+        <v>6550330</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11831,6 +11816,21 @@
       </c>
       <c r="AG101" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
@@ -11850,7 +11850,7 @@
         <v>128931829</v>
       </c>
       <c r="B102" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11944,32 +11944,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128931855</v>
+        <v>128931882</v>
       </c>
       <c r="B103" t="n">
-        <v>90327</v>
+        <v>96970</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1596</v>
+        <v>53</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11979,10 +11979,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>316943</v>
+        <v>316864</v>
       </c>
       <c r="R103" t="n">
-        <v>6550676</v>
+        <v>6550421</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -12044,7 +12044,7 @@
         <v>128931862</v>
       </c>
       <c r="B104" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12138,32 +12138,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128931882</v>
+        <v>128931855</v>
       </c>
       <c r="B105" t="n">
-        <v>96962</v>
+        <v>90328</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>53</v>
+        <v>1596</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12173,10 +12173,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>316864</v>
+        <v>316943</v>
       </c>
       <c r="R105" t="n">
-        <v>6550421</v>
+        <v>6550676</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -12238,7 +12238,7 @@
         <v>129221408</v>
       </c>
       <c r="B106" t="n">
-        <v>96998</v>
+        <v>97006</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12447,7 +12447,7 @@
         <v>129221406</v>
       </c>
       <c r="B108" t="n">
-        <v>96998</v>
+        <v>97006</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>

--- a/artfynd/A 40826-2025 artfynd.xlsx
+++ b/artfynd/A 40826-2025 artfynd.xlsx
@@ -12238,7 +12238,7 @@
         <v>129221408</v>
       </c>
       <c r="B106" t="n">
-        <v>97006</v>
+        <v>97009</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12447,7 +12447,7 @@
         <v>129221406</v>
       </c>
       <c r="B108" t="n">
-        <v>97006</v>
+        <v>97009</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>

--- a/artfynd/A 40826-2025 artfynd.xlsx
+++ b/artfynd/A 40826-2025 artfynd.xlsx
@@ -12238,7 +12238,7 @@
         <v>129221408</v>
       </c>
       <c r="B106" t="n">
-        <v>97009</v>
+        <v>97038</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
         <v>129221407</v>
       </c>
       <c r="B107" t="n">
-        <v>78710</v>
+        <v>78736</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12447,7 +12447,7 @@
         <v>129221406</v>
       </c>
       <c r="B108" t="n">
-        <v>97009</v>
+        <v>97038</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>

--- a/artfynd/A 40826-2025 artfynd.xlsx
+++ b/artfynd/A 40826-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY118"/>
+  <dimension ref="A1:AZ118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128931869</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128931873</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128931878</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128931880</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128931882</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128931885</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128931886</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1476,6 +1516,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121071479</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1588,6 +1633,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129221407</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1685,6 +1735,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128931854</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1782,6 +1837,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128931855</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1879,6 +1939,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128931859</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1994,6 +2059,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121071363</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2119,6 +2189,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121072107</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2244,6 +2319,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128085294</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2341,6 +2421,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124322056</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2438,6 +2523,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124322058</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2535,6 +2625,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124322122</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2632,6 +2727,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128931825</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2729,6 +2829,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128931828</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2826,6 +2931,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128931868</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2923,6 +3033,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128931870</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3020,6 +3135,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128931872</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3117,6 +3237,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128931874</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3214,6 +3339,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128931879</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3311,6 +3441,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128931881</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3408,6 +3543,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128931883</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3505,6 +3645,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128931884</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3602,6 +3747,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128931887</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3714,6 +3864,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128931888</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3811,6 +3966,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129221406</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3908,6 +4068,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129221408</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4005,6 +4170,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128931889</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4102,6 +4272,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128931877</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4216,6 +4391,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120211115</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4313,6 +4493,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128931853</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4410,6 +4595,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128931856</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4507,6 +4697,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128931857</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4604,6 +4799,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128931861</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4733,6 +4933,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128085493</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4858,6 +5063,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121071209</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4979,6 +5189,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120210821</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5104,6 +5319,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121071003</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5219,6 +5439,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121071291</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5344,6 +5569,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121071436</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5469,6 +5699,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121071693</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5594,6 +5829,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128085551</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5719,6 +5959,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128085583</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5844,6 +6089,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128085650</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5969,6 +6219,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128085763</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6094,6 +6349,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121071088</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6191,6 +6451,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128931862</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6288,6 +6553,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128931864</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6385,6 +6655,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128931867</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6510,6 +6785,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128084972</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6622,6 +6902,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124322118</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6744,6 +7029,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120284199</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6866,6 +7156,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120284127</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6968,6 +7263,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124322121</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7085,6 +7385,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128931876</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7202,6 +7507,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124322119</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7329,6 +7639,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120426118</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7446,6 +7761,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124322114</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7563,6 +7883,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124322115</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7680,6 +8005,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124322120</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7807,6 +8137,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128084637</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7934,6 +8269,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128084871</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8061,6 +8401,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128084900</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8188,6 +8533,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128084916</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8315,6 +8665,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128085525</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8432,6 +8787,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128931831</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8549,6 +8909,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128931860</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8666,6 +9031,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128931863</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8783,6 +9153,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128931865</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8900,6 +9275,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128931866</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9017,6 +9397,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128931871</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9134,6 +9519,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128931891</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9249,6 +9639,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120425951</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9355,6 +9750,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121071258</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9466,6 +9866,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121071405</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9563,6 +9968,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124322054</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9660,6 +10070,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124322055</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9761,6 +10176,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124322057</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9889,6 +10309,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124341498</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10000,6 +10425,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128086155</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10111,6 +10541,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128086358</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10222,6 +10657,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128086406</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10333,6 +10773,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128086451</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10444,6 +10889,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128086469</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10555,6 +11005,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128086518</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10666,6 +11121,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128086546</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10777,6 +11237,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128086622</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10888,6 +11353,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128086654</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10999,6 +11469,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128086692</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11110,6 +11585,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128086710</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11221,6 +11701,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128086718</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11332,6 +11817,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128086734</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11443,6 +11933,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128086772</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11554,6 +12049,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128086825</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11665,6 +12165,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128086910</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11776,6 +12281,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128086988</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11887,6 +12397,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128086997</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11998,6 +12513,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128087033</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12109,6 +12629,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128087074</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12220,6 +12745,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128087244</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12331,6 +12861,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128087295</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12442,6 +12977,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128087374</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12553,6 +13093,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128087411</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12664,6 +13209,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128087465</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12775,6 +13325,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128087506</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12886,6 +13441,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128087606</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12997,6 +13557,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128087641</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13108,6 +13673,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128087681</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13205,6 +13775,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128931826</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13302,6 +13877,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128931827</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13399,6 +13979,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128931829</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13506,8 +14091,132 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128085956</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>